--- a/docs/qa/Capitol-RTM.xlsx
+++ b/docs/qa/Capitol-RTM.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$U$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RTM'!$A$1:$O$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Findings'!$A$1:$L$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Findings'!$A$1:$L$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -820,7 +820,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RTM → Verdict is computed: No coverage · Not run · In progress · Fail (any linked case failed) · Pass (all linked cases passed or N/A).</t>
+          <t>RTM → Verdict is computed: No coverage · Not run · In progress (some cases still Not Run or Blocked) · Fail (any linked case failed) · Pass (all linked cases passed or N/A). Executed % counts Pass, Fail and N/A only; Blocked is not executed.</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -950,7 +950,7 @@
         <v/>
       </c>
       <c r="H4" s="10">
-        <f>IF(B4=0,0,(B4-G4)/B4)</f>
+        <f>IF(B4=0,0,(C4+D4+F4)/B4)</f>
         <v/>
       </c>
       <c r="I4" s="10">
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H5" s="10">
-        <f>IF(B5=0,0,(B5-G5)/B5)</f>
+        <f>IF(B5=0,0,(C5+D5+F5)/B5)</f>
         <v/>
       </c>
       <c r="I5" s="10">
@@ -1028,7 +1028,7 @@
         <v/>
       </c>
       <c r="H6" s="10">
-        <f>IF(B6=0,0,(B6-G6)/B6)</f>
+        <f>IF(B6=0,0,(C6+D6+F6)/B6)</f>
         <v/>
       </c>
       <c r="I6" s="10">
@@ -1067,7 +1067,7 @@
         <v/>
       </c>
       <c r="H7" s="10">
-        <f>IF(B7=0,0,(B7-G7)/B7)</f>
+        <f>IF(B7=0,0,(C7+D7+F7)/B7)</f>
         <v/>
       </c>
       <c r="I7" s="10">
@@ -1106,7 +1106,7 @@
         <v/>
       </c>
       <c r="H8" s="10">
-        <f>IF(B8=0,0,(B8-G8)/B8)</f>
+        <f>IF(B8=0,0,(C8+D8+F8)/B8)</f>
         <v/>
       </c>
       <c r="I8" s="10">
@@ -1145,7 +1145,7 @@
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>IF(B9=0,0,(B9-G9)/B9)</f>
+        <f>IF(B9=0,0,(C9+D9+F9)/B9)</f>
         <v/>
       </c>
       <c r="I9" s="12">
@@ -1280,180 +1280,172 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Executed</t>
+          <t>Executed (Pass/Fail/N/A)</t>
         </is>
       </c>
       <c r="B18" s="9">
-        <f>COUNTIFS('Test Cases'!$M$2:$M$155,"Y",'Test Cases'!$N$2:$N$155,"&lt;&gt;Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$M$2:$M$155,"Y",'Test Cases'!$N$2:$N$155,"Pass")+COUNTIFS('Test Cases'!$M$2:$M$155,"Y",'Test Cases'!$N$2:$N$155,"Fail")+COUNTIFS('Test Cases'!$M$2:$M$155,"Y",'Test Cases'!$N$2:$N$155,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B19" s="9">
+        <f>COUNTIFS('Test Cases'!$M$2:$M$155,"Y",'Test Cases'!$N$2:$N$155,"Blocked")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B19" s="9">
+      <c r="B20" s="9">
         <f>COUNTIFS('Test Cases'!$M$2:$M$155,"Y",'Test Cases'!$N$2:$N$155,"Fail")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Requirement coverage</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Requirements traced</t>
-        </is>
-      </c>
-      <c r="B22" s="9">
-        <f>COUNTA(RTM!$A$2:$A$41)</f>
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>With ≥ 1 test case</t>
+          <t>Requirements traced</t>
         </is>
       </c>
       <c r="B23" s="9">
-        <f>COUNTIF(RTM!$H$2:$H$41,"&gt;0")</f>
+        <f>COUNTA(RTM!$A$2:$A$41)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Coverage %</t>
-        </is>
-      </c>
-      <c r="B24" s="10">
-        <f>IF(B22=0,0,B23/B22)</f>
+          <t>With ≥ 1 test case</t>
+        </is>
+      </c>
+      <c r="B24" s="9">
+        <f>COUNTIF(RTM!$H$2:$H$41,"&gt;0")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Verdict: Pass</t>
-        </is>
-      </c>
-      <c r="B25" s="9">
-        <f>COUNTIF(RTM!$O$2:$O$41,"Pass")</f>
+          <t>Coverage %</t>
+        </is>
+      </c>
+      <c r="B25" s="10">
+        <f>IF(B23=0,0,B24/B23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Verdict: Fail</t>
+          <t>Verdict: Pass</t>
         </is>
       </c>
       <c r="B26" s="9">
-        <f>COUNTIF(RTM!$O$2:$O$41,"Fail")</f>
+        <f>COUNTIF(RTM!$O$2:$O$41,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Verdict: In progress</t>
+          <t>Verdict: Fail</t>
         </is>
       </c>
       <c r="B27" s="9">
-        <f>COUNTIF(RTM!$O$2:$O$41,"In progress")</f>
+        <f>COUNTIF(RTM!$O$2:$O$41,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Verdict: Not run</t>
+          <t>Verdict: In progress</t>
         </is>
       </c>
       <c r="B28" s="9">
-        <f>COUNTIF(RTM!$O$2:$O$41,"Not run")</f>
+        <f>COUNTIF(RTM!$O$2:$O$41,"In progress")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>Verdict: Not run</t>
+        </is>
+      </c>
+      <c r="B29" s="9">
+        <f>COUNTIF(RTM!$O$2:$O$41,"Not run")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
           <t>Verdict: No coverage</t>
         </is>
       </c>
-      <c r="B29" s="9">
+      <c r="B30" s="9">
         <f>COUNTIF(RTM!$O$2:$O$41,"No coverage")</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B33" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A33,Findings!$B$2:$B$33,"P1*")</f>
-        <v/>
-      </c>
-      <c r="C33" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A33,Findings!$B$2:$B$33,"P2*")</f>
-        <v/>
-      </c>
-      <c r="D33" s="9">
-        <f>B33+C33</f>
-        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="B34" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A34,Findings!$B$2:$B$33,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A34,Findings!$B$2:$B$34,"P1*")</f>
         <v/>
       </c>
       <c r="C34" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A34,Findings!$B$2:$B$33,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A34,Findings!$B$2:$B$34,"P2*")</f>
         <v/>
       </c>
       <c r="D34" s="9">
@@ -1464,15 +1456,15 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="B35" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A35,Findings!$B$2:$B$33,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A35,Findings!$B$2:$B$34,"P1*")</f>
         <v/>
       </c>
       <c r="C35" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A35,Findings!$B$2:$B$33,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A35,Findings!$B$2:$B$34,"P2*")</f>
         <v/>
       </c>
       <c r="D35" s="9">
@@ -1483,15 +1475,15 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="B36" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A36,Findings!$B$2:$B$33,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A36,Findings!$B$2:$B$34,"P1*")</f>
         <v/>
       </c>
       <c r="C36" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A36,Findings!$B$2:$B$33,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A36,Findings!$B$2:$B$34,"P2*")</f>
         <v/>
       </c>
       <c r="D36" s="9">
@@ -1502,15 +1494,15 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Won't fix</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="B37" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A37,Findings!$B$2:$B$33,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A37,Findings!$B$2:$B$34,"P1*")</f>
         <v/>
       </c>
       <c r="C37" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A37,Findings!$B$2:$B$33,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A37,Findings!$B$2:$B$34,"P2*")</f>
         <v/>
       </c>
       <c r="D37" s="9">
@@ -1521,19 +1513,38 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>SRS to update</t>
+          <t>Won't fix</t>
         </is>
       </c>
       <c r="B38" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A38,Findings!$B$2:$B$33,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A38,Findings!$B$2:$B$34,"P1*")</f>
         <v/>
       </c>
       <c r="C38" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$33,A38,Findings!$B$2:$B$33,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$34,A38,Findings!$B$2:$B$34,"P2*")</f>
         <v/>
       </c>
       <c r="D38" s="9">
         <f>B38+C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>SRS to update</t>
+        </is>
+      </c>
+      <c r="B39" s="9">
+        <f>COUNTIFS(Findings!$I$2:$I$34,A39,Findings!$B$2:$B$34,"P1*")</f>
+        <v/>
+      </c>
+      <c r="C39" s="9">
+        <f>COUNTIFS(Findings!$I$2:$I$34,A39,Findings!$B$2:$B$34,"P2*")</f>
+        <v/>
+      </c>
+      <c r="D39" s="9">
+        <f>B39+C39</f>
         <v/>
       </c>
     </row>
@@ -1838,16 +1849,42 @@
       </c>
       <c r="N3" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O3" s="17" t="n"/>
-      <c r="P3" s="17" t="n"/>
-      <c r="Q3" s="17" t="n"/>
-      <c r="R3" s="18" t="n"/>
-      <c r="S3" s="16" t="n"/>
-      <c r="T3" s="17" t="n"/>
-      <c r="U3" s="17" t="n"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O3" s="17" t="inlineStr">
+        <is>
+          <t>Blank page in Chrome: the site's own assets return 403 'This website origin is not allowed.' (/assets/index-Cva6tJ4s.css, /assets/index-Bq1AsZVl.js)</t>
+        </is>
+      </c>
+      <c r="P3" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
+      <c r="Q3" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R3" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S3" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T3" s="17" t="inlineStr">
+        <is>
+          <t>Real browser, no workaround. Header links and Sign In / Log In render correctly once the workaround is applied</t>
+        </is>
+      </c>
+      <c r="U3" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -1913,16 +1950,38 @@
       </c>
       <c r="N4" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O4" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O4" s="17" t="inlineStr">
+        <is>
+          <t>/operations as guest → /; staff UI shown: false</t>
+        </is>
+      </c>
       <c r="P4" s="17" t="n"/>
-      <c r="Q4" s="17" t="n"/>
-      <c r="R4" s="18" t="n"/>
-      <c r="S4" s="16" t="n"/>
-      <c r="T4" s="17" t="n"/>
-      <c r="U4" s="17" t="n"/>
+      <c r="Q4" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R4" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S4" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U4" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -1988,16 +2047,38 @@
       </c>
       <c r="N5" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O5" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O5" s="17" t="inlineStr">
+        <is>
+          <t>'Done · 1 selected' → 'Place order · ₱260' → Sign In modal: true; order stored: false</t>
+        </is>
+      </c>
       <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="18" t="n"/>
-      <c r="S5" s="16" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
+      <c r="Q5" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R5" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S5" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T5" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U5" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -2063,15 +2144,23 @@
       </c>
       <c r="N6" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O6" s="17" t="n"/>
-      <c r="P6" s="17" t="n"/>
+      <c r="P6" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q6" s="17" t="n"/>
       <c r="R6" s="18" t="n"/>
       <c r="S6" s="16" t="n"/>
-      <c r="T6" s="17" t="n"/>
+      <c r="T6" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U6" s="17" t="n"/>
     </row>
     <row r="7">
@@ -2138,15 +2227,23 @@
       </c>
       <c r="N7" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O7" s="17" t="n"/>
-      <c r="P7" s="17" t="n"/>
+      <c r="P7" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q7" s="17" t="n"/>
       <c r="R7" s="18" t="n"/>
       <c r="S7" s="16" t="n"/>
-      <c r="T7" s="17" t="n"/>
+      <c r="T7" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U7" s="17" t="n"/>
     </row>
     <row r="8">
@@ -2213,15 +2310,23 @@
       </c>
       <c r="N8" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O8" s="17" t="n"/>
-      <c r="P8" s="17" t="n"/>
+      <c r="P8" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q8" s="17" t="n"/>
       <c r="R8" s="18" t="n"/>
       <c r="S8" s="16" t="n"/>
-      <c r="T8" s="17" t="n"/>
+      <c r="T8" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U8" s="17" t="n"/>
     </row>
     <row r="9">
@@ -2288,15 +2393,23 @@
       </c>
       <c r="N9" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O9" s="17" t="n"/>
-      <c r="P9" s="17" t="n"/>
+      <c r="P9" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q9" s="17" t="n"/>
       <c r="R9" s="18" t="n"/>
       <c r="S9" s="16" t="n"/>
-      <c r="T9" s="17" t="n"/>
+      <c r="T9" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U9" s="17" t="n"/>
     </row>
     <row r="10">
@@ -2363,15 +2476,23 @@
       </c>
       <c r="N10" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O10" s="17" t="n"/>
-      <c r="P10" s="17" t="n"/>
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q10" s="17" t="n"/>
       <c r="R10" s="18" t="n"/>
       <c r="S10" s="16" t="n"/>
-      <c r="T10" s="17" t="n"/>
+      <c r="T10" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U10" s="17" t="n"/>
     </row>
     <row r="11">
@@ -2438,15 +2559,23 @@
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O11" s="17" t="n"/>
-      <c r="P11" s="17" t="n"/>
+      <c r="P11" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q11" s="17" t="n"/>
       <c r="R11" s="18" t="n"/>
       <c r="S11" s="16" t="n"/>
-      <c r="T11" s="17" t="n"/>
+      <c r="T11" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U11" s="17" t="n"/>
     </row>
     <row r="12">
@@ -2513,15 +2642,23 @@
       </c>
       <c r="N12" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O12" s="17" t="n"/>
-      <c r="P12" s="17" t="n"/>
+      <c r="P12" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q12" s="17" t="n"/>
       <c r="R12" s="18" t="n"/>
       <c r="S12" s="16" t="n"/>
-      <c r="T12" s="17" t="n"/>
+      <c r="T12" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U12" s="17" t="n"/>
     </row>
     <row r="13">
@@ -2588,15 +2725,23 @@
       </c>
       <c r="N13" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O13" s="17" t="n"/>
-      <c r="P13" s="17" t="n"/>
+      <c r="P13" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q13" s="17" t="n"/>
       <c r="R13" s="18" t="n"/>
       <c r="S13" s="16" t="n"/>
-      <c r="T13" s="17" t="n"/>
+      <c r="T13" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U13" s="17" t="n"/>
     </row>
     <row r="14">
@@ -2663,15 +2808,23 @@
       </c>
       <c r="N14" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O14" s="17" t="n"/>
-      <c r="P14" s="17" t="n"/>
+      <c r="P14" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q14" s="17" t="n"/>
       <c r="R14" s="18" t="n"/>
       <c r="S14" s="16" t="n"/>
-      <c r="T14" s="17" t="n"/>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U14" s="17" t="n"/>
     </row>
     <row r="15">
@@ -2742,15 +2895,23 @@
       </c>
       <c r="N15" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O15" s="17" t="n"/>
-      <c r="P15" s="17" t="n"/>
+      <c r="P15" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q15" s="17" t="n"/>
       <c r="R15" s="18" t="n"/>
       <c r="S15" s="16" t="n"/>
-      <c r="T15" s="17" t="n"/>
+      <c r="T15" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U15" s="17" t="n"/>
     </row>
     <row r="16">
@@ -2817,15 +2978,23 @@
       </c>
       <c r="N16" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O16" s="17" t="n"/>
-      <c r="P16" s="17" t="n"/>
+      <c r="P16" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q16" s="17" t="n"/>
       <c r="R16" s="18" t="n"/>
       <c r="S16" s="16" t="n"/>
-      <c r="T16" s="17" t="n"/>
+      <c r="T16" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U16" s="17" t="n"/>
     </row>
     <row r="17">
@@ -2892,15 +3061,23 @@
       </c>
       <c r="N17" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O17" s="17" t="n"/>
-      <c r="P17" s="17" t="n"/>
+      <c r="P17" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q17" s="17" t="n"/>
       <c r="R17" s="18" t="n"/>
       <c r="S17" s="16" t="n"/>
-      <c r="T17" s="17" t="n"/>
+      <c r="T17" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U17" s="17" t="n"/>
     </row>
     <row r="18">
@@ -2967,15 +3144,23 @@
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O18" s="17" t="n"/>
-      <c r="P18" s="17" t="n"/>
+      <c r="P18" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q18" s="17" t="n"/>
       <c r="R18" s="18" t="n"/>
       <c r="S18" s="16" t="n"/>
-      <c r="T18" s="17" t="n"/>
+      <c r="T18" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U18" s="17" t="n"/>
     </row>
     <row r="19">
@@ -3046,15 +3231,23 @@
       </c>
       <c r="N19" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O19" s="17" t="n"/>
-      <c r="P19" s="17" t="n"/>
+      <c r="P19" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q19" s="17" t="n"/>
       <c r="R19" s="18" t="n"/>
       <c r="S19" s="16" t="n"/>
-      <c r="T19" s="17" t="n"/>
+      <c r="T19" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U19" s="17" t="n"/>
     </row>
     <row r="20">
@@ -3121,15 +3314,23 @@
       </c>
       <c r="N20" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O20" s="17" t="n"/>
-      <c r="P20" s="17" t="n"/>
+      <c r="P20" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q20" s="17" t="n"/>
       <c r="R20" s="18" t="n"/>
       <c r="S20" s="16" t="n"/>
-      <c r="T20" s="17" t="n"/>
+      <c r="T20" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U20" s="17" t="n"/>
     </row>
     <row r="21">
@@ -3289,15 +3490,23 @@
       </c>
       <c r="N22" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O22" s="17" t="n"/>
-      <c r="P22" s="17" t="n"/>
+      <c r="P22" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q22" s="17" t="n"/>
       <c r="R22" s="18" t="n"/>
       <c r="S22" s="16" t="n"/>
-      <c r="T22" s="17" t="n"/>
+      <c r="T22" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U22" s="17" t="n"/>
     </row>
     <row r="23">
@@ -3364,16 +3573,38 @@
       </c>
       <c r="N23" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O23" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O23" s="17" t="inlineStr">
+        <is>
+          <t>Inline error: 'Invalid login credentials'; modal stays open: true</t>
+        </is>
+      </c>
       <c r="P23" s="17" t="n"/>
-      <c r="Q23" s="17" t="n"/>
-      <c r="R23" s="18" t="n"/>
-      <c r="S23" s="16" t="n"/>
-      <c r="T23" s="17" t="n"/>
-      <c r="U23" s="17" t="n"/>
+      <c r="Q23" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R23" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S23" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T23" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Used a non-existent email because CUST does not exist yet; Supabase returns the same message for a wrong password</t>
+        </is>
+      </c>
+      <c r="U23" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -3439,15 +3670,23 @@
       </c>
       <c r="N24" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O24" s="17" t="n"/>
-      <c r="P24" s="17" t="n"/>
+      <c r="P24" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q24" s="17" t="n"/>
       <c r="R24" s="18" t="n"/>
       <c r="S24" s="16" t="n"/>
-      <c r="T24" s="17" t="n"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U24" s="17" t="n"/>
     </row>
     <row r="25">
@@ -3483,7 +3722,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>"Enter your email address", then an inline error from Supabase. Not signed in</t>
+          <t>The browser's own validation blocks both ("Please fill out this field.", "Please enter a part following '@'…") because the field is type=email and required; no login request is sent. Not signed in</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -3514,16 +3753,38 @@
       </c>
       <c r="N25" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O25" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O25" s="17" t="inlineStr">
+        <is>
+          <t>Blank → browser validation 'Please fill out this field.'; 'juan@' → browser validation 'Please enter a part following '@'. 'juan@' is incomplete.'; auth requests sent: 0; still signed out: true</t>
+        </is>
+      </c>
       <c r="P25" s="17" t="n"/>
-      <c r="Q25" s="17" t="n"/>
-      <c r="R25" s="18" t="n"/>
-      <c r="S25" s="16" t="n"/>
-      <c r="T25" s="17" t="n"/>
-      <c r="U25" s="17" t="n"/>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R25" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S25" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). The field is type=email + required, so the browser's own validation fires before the app's 'Enter your email address' and before Supabase; suite expectation corrected</t>
+        </is>
+      </c>
+      <c r="U25" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -3589,15 +3850,23 @@
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O26" s="17" t="n"/>
-      <c r="P26" s="17" t="n"/>
+      <c r="P26" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q26" s="17" t="n"/>
       <c r="R26" s="18" t="n"/>
       <c r="S26" s="16" t="n"/>
-      <c r="T26" s="17" t="n"/>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U26" s="17" t="n"/>
     </row>
     <row r="27">
@@ -3664,15 +3933,23 @@
       </c>
       <c r="N27" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O27" s="17" t="n"/>
-      <c r="P27" s="17" t="n"/>
+      <c r="P27" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q27" s="17" t="n"/>
       <c r="R27" s="18" t="n"/>
       <c r="S27" s="16" t="n"/>
-      <c r="T27" s="17" t="n"/>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U27" s="17" t="n"/>
     </row>
     <row r="28">
@@ -3739,15 +4016,23 @@
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O28" s="17" t="n"/>
-      <c r="P28" s="17" t="n"/>
+      <c r="P28" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q28" s="17" t="n"/>
       <c r="R28" s="18" t="n"/>
       <c r="S28" s="16" t="n"/>
-      <c r="T28" s="17" t="n"/>
+      <c r="T28" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U28" s="17" t="n"/>
     </row>
     <row r="29">
@@ -3814,15 +4099,23 @@
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O29" s="17" t="n"/>
-      <c r="P29" s="17" t="n"/>
+      <c r="P29" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q29" s="17" t="n"/>
       <c r="R29" s="18" t="n"/>
       <c r="S29" s="16" t="n"/>
-      <c r="T29" s="17" t="n"/>
+      <c r="T29" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U29" s="17" t="n"/>
     </row>
     <row r="30">
@@ -3889,15 +4182,23 @@
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O30" s="17" t="n"/>
-      <c r="P30" s="17" t="n"/>
+      <c r="P30" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q30" s="17" t="n"/>
       <c r="R30" s="18" t="n"/>
       <c r="S30" s="16" t="n"/>
-      <c r="T30" s="17" t="n"/>
+      <c r="T30" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U30" s="17" t="n"/>
     </row>
     <row r="31">
@@ -3964,15 +4265,23 @@
       </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O31" s="17" t="n"/>
-      <c r="P31" s="17" t="n"/>
+      <c r="P31" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q31" s="17" t="n"/>
       <c r="R31" s="18" t="n"/>
       <c r="S31" s="16" t="n"/>
-      <c r="T31" s="17" t="n"/>
+      <c r="T31" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U31" s="17" t="n"/>
     </row>
     <row r="32">
@@ -4039,15 +4348,23 @@
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O32" s="17" t="n"/>
-      <c r="P32" s="17" t="n"/>
+      <c r="P32" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q32" s="17" t="n"/>
       <c r="R32" s="18" t="n"/>
       <c r="S32" s="16" t="n"/>
-      <c r="T32" s="17" t="n"/>
+      <c r="T32" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U32" s="17" t="n"/>
     </row>
     <row r="33">
@@ -4114,16 +4431,38 @@
       </c>
       <c r="N33" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O33" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t>Sign In modal: true; calendar opened: false</t>
+        </is>
+      </c>
       <c r="P33" s="17" t="n"/>
-      <c r="Q33" s="17" t="n"/>
-      <c r="R33" s="18" t="n"/>
-      <c r="S33" s="16" t="n"/>
-      <c r="T33" s="17" t="n"/>
-      <c r="U33" s="17" t="n"/>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R33" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S33" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T33" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U33" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -4189,16 +4528,38 @@
       </c>
       <c r="N34" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O34" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O34" s="17" t="inlineStr">
+        <is>
+          <t>Proceed disabled: true; prompt shown: true</t>
+        </is>
+      </c>
       <c r="P34" s="17" t="n"/>
-      <c r="Q34" s="17" t="n"/>
-      <c r="R34" s="18" t="n"/>
-      <c r="S34" s="16" t="n"/>
-      <c r="T34" s="17" t="n"/>
-      <c r="U34" s="17" t="n"/>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R34" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S34" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T34" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U34" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -4264,15 +4625,23 @@
       </c>
       <c r="N35" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O35" s="17" t="n"/>
-      <c r="P35" s="17" t="n"/>
+      <c r="P35" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q35" s="17" t="n"/>
       <c r="R35" s="18" t="n"/>
       <c r="S35" s="16" t="n"/>
-      <c r="T35" s="17" t="n"/>
+      <c r="T35" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U35" s="17" t="n"/>
     </row>
     <row r="36">
@@ -4339,15 +4708,23 @@
       </c>
       <c r="N36" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O36" s="17" t="n"/>
-      <c r="P36" s="17" t="n"/>
+      <c r="P36" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q36" s="17" t="n"/>
       <c r="R36" s="18" t="n"/>
       <c r="S36" s="16" t="n"/>
-      <c r="T36" s="17" t="n"/>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U36" s="17" t="n"/>
     </row>
     <row r="37">
@@ -4414,15 +4791,23 @@
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O37" s="17" t="n"/>
-      <c r="P37" s="17" t="n"/>
+      <c r="P37" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q37" s="17" t="n"/>
       <c r="R37" s="18" t="n"/>
       <c r="S37" s="16" t="n"/>
-      <c r="T37" s="17" t="n"/>
+      <c r="T37" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U37" s="17" t="n"/>
     </row>
     <row r="38">
@@ -4489,15 +4874,23 @@
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O38" s="17" t="n"/>
-      <c r="P38" s="17" t="n"/>
+      <c r="P38" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q38" s="17" t="n"/>
       <c r="R38" s="18" t="n"/>
       <c r="S38" s="16" t="n"/>
-      <c r="T38" s="17" t="n"/>
+      <c r="T38" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U38" s="17" t="n"/>
     </row>
     <row r="39">
@@ -4564,16 +4957,38 @@
       </c>
       <c r="N39" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O39" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O39" s="17" t="inlineStr">
+        <is>
+          <t>At 9 packs: error shown true, Proceed disabled true; back at 10: Proceed enabled true</t>
+        </is>
+      </c>
       <c r="P39" s="17" t="n"/>
-      <c r="Q39" s="17" t="n"/>
-      <c r="R39" s="18" t="n"/>
-      <c r="S39" s="16" t="n"/>
-      <c r="T39" s="17" t="n"/>
-      <c r="U39" s="17" t="n"/>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R39" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S39" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T39" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U39" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -4639,16 +5054,38 @@
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O40" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O40" s="17" t="inlineStr">
+        <is>
+          <t>Summary: Your order Adobong Manok Solo Meals · 10 packs ₱1200 10 Lechon Kawali Solo Meals · 10 packs ₱1450 10 Subtotal ₱2650 Delivery fee ₱0 Total ₱2650</t>
+        </is>
+      </c>
       <c r="P40" s="17" t="n"/>
-      <c r="Q40" s="17" t="n"/>
-      <c r="R40" s="18" t="n"/>
-      <c r="S40" s="16" t="n"/>
-      <c r="T40" s="17" t="n"/>
-      <c r="U40" s="17" t="n"/>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R40" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S40" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T40" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U40" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -4714,15 +5151,23 @@
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O41" s="17" t="n"/>
-      <c r="P41" s="17" t="n"/>
+      <c r="P41" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q41" s="17" t="n"/>
       <c r="R41" s="18" t="n"/>
       <c r="S41" s="16" t="n"/>
-      <c r="T41" s="17" t="n"/>
+      <c r="T41" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U41" s="17" t="n"/>
     </row>
     <row r="42">
@@ -4789,15 +5234,23 @@
       </c>
       <c r="N42" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O42" s="17" t="n"/>
-      <c r="P42" s="17" t="n"/>
+      <c r="P42" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q42" s="17" t="n"/>
       <c r="R42" s="18" t="n"/>
       <c r="S42" s="16" t="n"/>
-      <c r="T42" s="17" t="n"/>
+      <c r="T42" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U42" s="17" t="n"/>
     </row>
     <row r="43">
@@ -4864,15 +5317,23 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O43" s="17" t="n"/>
-      <c r="P43" s="17" t="n"/>
+      <c r="P43" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q43" s="17" t="n"/>
       <c r="R43" s="18" t="n"/>
       <c r="S43" s="16" t="n"/>
-      <c r="T43" s="17" t="n"/>
+      <c r="T43" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U43" s="17" t="n"/>
     </row>
     <row r="44">
@@ -4939,15 +5400,23 @@
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O44" s="17" t="n"/>
-      <c r="P44" s="17" t="n"/>
+      <c r="P44" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q44" s="17" t="n"/>
       <c r="R44" s="18" t="n"/>
       <c r="S44" s="16" t="n"/>
-      <c r="T44" s="17" t="n"/>
+      <c r="T44" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U44" s="17" t="n"/>
     </row>
     <row r="45">
@@ -5014,16 +5483,38 @@
       </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O45" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t>5 errors: Letters only, min. 3 characters (e.g. Juan dela Cruz) / Enter a valid PH mobile number (e.g. 09XX XXX XXXX) / Enter a valid email address (e.g. juan@example.com) / Enter a whole-number guest count / Please select an even; calendar/sign-in opened: false</t>
+        </is>
+      </c>
       <c r="P45" s="17" t="n"/>
-      <c r="Q45" s="17" t="n"/>
-      <c r="R45" s="18" t="n"/>
-      <c r="S45" s="16" t="n"/>
-      <c r="T45" s="17" t="n"/>
-      <c r="U45" s="17" t="n"/>
+      <c r="Q45" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R45" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S45" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T45" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U45" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -5098,7 +5589,7 @@
       </c>
       <c r="O46" s="17" t="inlineStr">
         <is>
-          <t>Deployed validation accepts any whole number ≥ 1 ('Enter a whole-number guest count' only below 1), so 9 guests is accepted</t>
+          <t>9: accepted</t>
         </is>
       </c>
       <c r="P46" s="17" t="inlineStr">
@@ -5108,7 +5599,7 @@
       </c>
       <c r="Q46" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, guest)</t>
         </is>
       </c>
       <c r="R46" s="18" t="n">
@@ -5116,17 +5607,17 @@
       </c>
       <c r="S46" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T46" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
         </is>
       </c>
       <c r="U46" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5694,7 @@
       </c>
       <c r="O47" s="17" t="inlineStr">
         <is>
-          <t>Deployed validation rejects &gt; 30 ('This room holds up to 30 guests'), so 31 and 50 are rejected</t>
+          <t>31: rejected (This room holds up to 30 guests); 50: rejected (This room holds up to 30 guests)</t>
         </is>
       </c>
       <c r="P47" s="17" t="inlineStr">
@@ -5213,7 +5704,7 @@
       </c>
       <c r="Q47" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, guest)</t>
         </is>
       </c>
       <c r="R47" s="18" t="n">
@@ -5221,17 +5712,17 @@
       </c>
       <c r="S47" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T47" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
         </is>
       </c>
       <c r="U47" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -5304,13 +5795,13 @@
       </c>
       <c r="O48" s="17" t="inlineStr">
         <is>
-          <t>10 and 30 fall inside the deployed 1–30 rule and are accepted</t>
+          <t>10: accepted; 30: accepted</t>
         </is>
       </c>
       <c r="P48" s="17" t="n"/>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, guest)</t>
         </is>
       </c>
       <c r="R48" s="18" t="n">
@@ -5318,17 +5809,17 @@
       </c>
       <c r="S48" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T48" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
         </is>
       </c>
       <c r="U48" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -5401,13 +5892,13 @@
       </c>
       <c r="O49" s="17" t="inlineStr">
         <is>
-          <t>Event types match exactly: Birthday Celebration, Debut / 18th Birthday, Wedding Reception, Corporate Event, Family Reunion, Christmas Party, Seminar / Conference, Other</t>
+          <t>Options: Birthday Celebration, Debut / 18th Birthday, Wedding Reception, Corporate Event, Family Reunion, Christmas Party, Seminar / Conference, Other</t>
         </is>
       </c>
       <c r="P49" s="17" t="n"/>
       <c r="Q49" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, guest)</t>
         </is>
       </c>
       <c r="R49" s="18" t="n">
@@ -5415,17 +5906,17 @@
       </c>
       <c r="S49" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T49" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
         </is>
       </c>
       <c r="U49" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -5497,16 +5988,42 @@
       </c>
       <c r="N50" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O50" s="17" t="n"/>
-      <c r="P50" s="17" t="n"/>
-      <c r="Q50" s="17" t="n"/>
-      <c r="R50" s="18" t="n"/>
-      <c r="S50" s="16" t="n"/>
-      <c r="T50" s="17" t="n"/>
-      <c r="U50" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O50" s="17" t="inlineStr">
+        <is>
+          <t>+639171234567: accepted</t>
+        </is>
+      </c>
+      <c r="P50" s="17" t="inlineStr">
+        <is>
+          <t>F-19</t>
+        </is>
+      </c>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R50" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S50" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T50" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Passes as specified; documents the inconsistency with delivery (F-19)</t>
+        </is>
+      </c>
+      <c r="U50" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -5572,15 +6089,23 @@
       </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O51" s="17" t="n"/>
-      <c r="P51" s="17" t="n"/>
+      <c r="P51" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q51" s="17" t="n"/>
       <c r="R51" s="18" t="n"/>
       <c r="S51" s="16" t="n"/>
-      <c r="T51" s="17" t="n"/>
+      <c r="T51" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U51" s="17" t="n"/>
     </row>
     <row r="52">
@@ -5647,15 +6172,23 @@
       </c>
       <c r="N52" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O52" s="17" t="n"/>
-      <c r="P52" s="17" t="n"/>
+      <c r="P52" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q52" s="17" t="n"/>
       <c r="R52" s="18" t="n"/>
       <c r="S52" s="16" t="n"/>
-      <c r="T52" s="17" t="n"/>
+      <c r="T52" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U52" s="17" t="n"/>
     </row>
     <row r="53">
@@ -5722,15 +6255,23 @@
       </c>
       <c r="N53" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O53" s="17" t="n"/>
-      <c r="P53" s="17" t="n"/>
+      <c r="P53" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q53" s="17" t="n"/>
       <c r="R53" s="18" t="n"/>
       <c r="S53" s="16" t="n"/>
-      <c r="T53" s="17" t="n"/>
+      <c r="T53" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U53" s="17" t="n"/>
     </row>
     <row r="54">
@@ -5902,15 +6443,23 @@
       </c>
       <c r="N55" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O55" s="17" t="n"/>
-      <c r="P55" s="17" t="n"/>
+      <c r="P55" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q55" s="17" t="n"/>
       <c r="R55" s="18" t="n"/>
       <c r="S55" s="16" t="n"/>
-      <c r="T55" s="17" t="n"/>
+      <c r="T55" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U55" s="17" t="n"/>
     </row>
     <row r="56">
@@ -6196,7 +6745,7 @@
       </c>
       <c r="O58" s="17" t="inlineStr">
         <is>
-          <t>No consent checkbox: the only 'consent' strings in the bundle are Supabase OAuth library code</t>
+          <t>Checkboxes on form: 0; consent/privacy text: 0</t>
         </is>
       </c>
       <c r="P58" s="17" t="inlineStr">
@@ -6206,7 +6755,7 @@
       </c>
       <c r="Q58" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, guest)</t>
         </is>
       </c>
       <c r="R58" s="18" t="n">
@@ -6214,17 +6763,17 @@
       </c>
       <c r="S58" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T58" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
         </is>
       </c>
       <c r="U58" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -6502,16 +7051,38 @@
       </c>
       <c r="N61" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O61" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O61" s="17" t="inlineStr">
+        <is>
+          <t>All: 6 cards on page 1; Chicken: 6 cards, all Chicken true; Bilao cards: MikiBihon Bilao, Bihon Bilao, Chami Bilao, Canton Bilao, PataBihon Bilao, Canton-Bihon Bilao</t>
+        </is>
+      </c>
       <c r="P61" s="17" t="n"/>
-      <c r="Q61" s="17" t="n"/>
-      <c r="R61" s="18" t="n"/>
-      <c r="S61" s="16" t="n"/>
-      <c r="T61" s="17" t="n"/>
-      <c r="U61" s="17" t="n"/>
+      <c r="Q61" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R61" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S61" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T61" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U61" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -6577,16 +7148,38 @@
       </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O62" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O62" s="17" t="inlineStr">
+        <is>
+          <t>Variants: CHOOSE AN OPTION Bihon Bilao XS (3–5 pax) ₱430 Add Small (8–10 pax) ₱580 Add Med (12–15 pax) ₱780 Add Large (18–20 pax) … → 'Done · 3 selected' → 'Place order · ₱2,390'</t>
+        </is>
+      </c>
       <c r="P62" s="17" t="n"/>
-      <c r="Q62" s="17" t="n"/>
-      <c r="R62" s="18" t="n"/>
-      <c r="S62" s="16" t="n"/>
-      <c r="T62" s="17" t="n"/>
-      <c r="U62" s="17" t="n"/>
+      <c r="Q62" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R62" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S62" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T62" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Run as guest; the cart does not depend on sign-in</t>
+        </is>
+      </c>
+      <c r="U62" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -6652,16 +7245,38 @@
       </c>
       <c r="N63" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O63" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O63" s="17" t="inlineStr">
+        <is>
+          <t>Options: Half ₱210,Whole ₱420; Done disabled at 0: true, enabled at 1: true</t>
+        </is>
+      </c>
       <c r="P63" s="17" t="n"/>
-      <c r="Q63" s="17" t="n"/>
-      <c r="R63" s="18" t="n"/>
-      <c r="S63" s="16" t="n"/>
-      <c r="T63" s="17" t="n"/>
-      <c r="U63" s="17" t="n"/>
+      <c r="Q63" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R63" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S63" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T63" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U63" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -6727,16 +7342,38 @@
       </c>
       <c r="N64" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O64" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O64" s="17" t="inlineStr">
+        <is>
+          <t>+ disabled at quantity 20</t>
+        </is>
+      </c>
       <c r="P64" s="17" t="n"/>
-      <c r="Q64" s="17" t="n"/>
-      <c r="R64" s="18" t="n"/>
-      <c r="S64" s="16" t="n"/>
-      <c r="T64" s="17" t="n"/>
-      <c r="U64" s="17" t="n"/>
+      <c r="Q64" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R64" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S64" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T64" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U64" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -6802,15 +7439,23 @@
       </c>
       <c r="N65" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O65" s="17" t="n"/>
-      <c r="P65" s="17" t="n"/>
+      <c r="P65" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q65" s="17" t="n"/>
       <c r="R65" s="18" t="n"/>
       <c r="S65" s="16" t="n"/>
-      <c r="T65" s="17" t="n"/>
+      <c r="T65" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U65" s="17" t="n"/>
     </row>
     <row r="66">
@@ -6877,15 +7522,23 @@
       </c>
       <c r="N66" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O66" s="17" t="n"/>
-      <c r="P66" s="17" t="n"/>
+      <c r="P66" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q66" s="17" t="n"/>
       <c r="R66" s="18" t="n"/>
       <c r="S66" s="16" t="n"/>
-      <c r="T66" s="17" t="n"/>
+      <c r="T66" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U66" s="17" t="n"/>
     </row>
     <row r="67">
@@ -6952,16 +7605,38 @@
       </c>
       <c r="N67" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O67" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O67" s="17" t="inlineStr">
+        <is>
+          <t>Message shown: true; modal opened: false</t>
+        </is>
+      </c>
       <c r="P67" s="17" t="n"/>
-      <c r="Q67" s="17" t="n"/>
-      <c r="R67" s="18" t="n"/>
-      <c r="S67" s="16" t="n"/>
-      <c r="T67" s="17" t="n"/>
-      <c r="U67" s="17" t="n"/>
+      <c r="Q67" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R67" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S67" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T67" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Run as guest</t>
+        </is>
+      </c>
+      <c r="U67" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -7342,15 +8017,23 @@
       </c>
       <c r="N71" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O71" s="17" t="n"/>
-      <c r="P71" s="17" t="n"/>
+      <c r="P71" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q71" s="17" t="n"/>
       <c r="R71" s="18" t="n"/>
       <c r="S71" s="16" t="n"/>
-      <c r="T71" s="17" t="n"/>
+      <c r="T71" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U71" s="17" t="n"/>
     </row>
     <row r="72">
@@ -7417,16 +8100,38 @@
       </c>
       <c r="N72" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O72" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O72" s="17" t="inlineStr">
+        <is>
+          <t>0 cards: true; empty-state text: 'No dishes…'; JS errors: 0</t>
+        </is>
+      </c>
       <c r="P72" s="17" t="n"/>
-      <c r="Q72" s="17" t="n"/>
-      <c r="R72" s="18" t="n"/>
-      <c r="S72" s="16" t="n"/>
-      <c r="T72" s="17" t="n"/>
-      <c r="U72" s="17" t="n"/>
+      <c r="Q72" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R72" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S72" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T72" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U72" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -7501,7 +8206,7 @@
       </c>
       <c r="O73" s="17" t="inlineStr">
         <is>
-          <t>Items show category, price and description; no allergen or dietary tags exist in the bundle</t>
+          <t>Cards show name, price, category, description (Buttered Chicken from ₱200 CHICKEN Choice cuts only. Half good for 2–3 | Bihon Bilao from ₱430 PANCIT SA BILAO Tray good for 3–5 pax. Add | Adobong Kabayo ₱260 KABAYO Kabayo adobo. Good for 2–3 pax. Add). Allergen/dietary tags: 0. 'No image available' placeholders on last view: 3</t>
         </is>
       </c>
       <c r="P73" s="17" t="inlineStr">
@@ -7511,7 +8216,7 @@
       </c>
       <c r="Q73" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, guest)</t>
         </is>
       </c>
       <c r="R73" s="18" t="n">
@@ -7519,17 +8224,17 @@
       </c>
       <c r="S73" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T73" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
         </is>
       </c>
       <c r="U73" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -7702,15 +8407,23 @@
       </c>
       <c r="N75" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O75" s="17" t="n"/>
-      <c r="P75" s="17" t="n"/>
+      <c r="P75" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q75" s="17" t="n"/>
       <c r="R75" s="18" t="n"/>
       <c r="S75" s="16" t="n"/>
-      <c r="T75" s="17" t="n"/>
+      <c r="T75" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U75" s="17" t="n"/>
     </row>
     <row r="76">
@@ -7777,15 +8490,23 @@
       </c>
       <c r="N76" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O76" s="17" t="n"/>
-      <c r="P76" s="17" t="n"/>
+      <c r="P76" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q76" s="17" t="n"/>
       <c r="R76" s="18" t="n"/>
       <c r="S76" s="16" t="n"/>
-      <c r="T76" s="17" t="n"/>
+      <c r="T76" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U76" s="17" t="n"/>
     </row>
     <row r="77">
@@ -7852,15 +8573,23 @@
       </c>
       <c r="N77" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O77" s="17" t="n"/>
-      <c r="P77" s="17" t="n"/>
+      <c r="P77" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q77" s="17" t="n"/>
       <c r="R77" s="18" t="n"/>
       <c r="S77" s="16" t="n"/>
-      <c r="T77" s="17" t="n"/>
+      <c r="T77" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U77" s="17" t="n"/>
     </row>
     <row r="78">
@@ -7927,15 +8656,23 @@
       </c>
       <c r="N78" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O78" s="17" t="n"/>
-      <c r="P78" s="17" t="n"/>
+      <c r="P78" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q78" s="17" t="n"/>
       <c r="R78" s="18" t="n"/>
       <c r="S78" s="16" t="n"/>
-      <c r="T78" s="17" t="n"/>
+      <c r="T78" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U78" s="17" t="n"/>
     </row>
     <row r="79">
@@ -8002,15 +8739,23 @@
       </c>
       <c r="N79" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O79" s="17" t="n"/>
-      <c r="P79" s="17" t="n"/>
+      <c r="P79" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q79" s="17" t="n"/>
       <c r="R79" s="18" t="n"/>
       <c r="S79" s="16" t="n"/>
-      <c r="T79" s="17" t="n"/>
+      <c r="T79" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U79" s="17" t="n"/>
     </row>
     <row r="80">
@@ -8182,15 +8927,23 @@
       </c>
       <c r="N81" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O81" s="17" t="n"/>
-      <c r="P81" s="17" t="n"/>
+      <c r="P81" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q81" s="17" t="n"/>
       <c r="R81" s="18" t="n"/>
       <c r="S81" s="16" t="n"/>
-      <c r="T81" s="17" t="n"/>
+      <c r="T81" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U81" s="17" t="n"/>
     </row>
     <row r="82">
@@ -8362,15 +9115,23 @@
       </c>
       <c r="N83" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O83" s="17" t="n"/>
-      <c r="P83" s="17" t="n"/>
+      <c r="P83" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q83" s="17" t="n"/>
       <c r="R83" s="18" t="n"/>
       <c r="S83" s="16" t="n"/>
-      <c r="T83" s="17" t="n"/>
+      <c r="T83" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U83" s="17" t="n"/>
     </row>
     <row r="84">
@@ -8437,15 +9198,23 @@
       </c>
       <c r="N84" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O84" s="17" t="n"/>
-      <c r="P84" s="17" t="n"/>
+      <c r="P84" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q84" s="17" t="n"/>
       <c r="R84" s="18" t="n"/>
       <c r="S84" s="16" t="n"/>
-      <c r="T84" s="17" t="n"/>
+      <c r="T84" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U84" s="17" t="n"/>
     </row>
     <row r="85">
@@ -8617,15 +9386,23 @@
       </c>
       <c r="N86" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O86" s="17" t="n"/>
-      <c r="P86" s="17" t="n"/>
+      <c r="P86" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q86" s="17" t="n"/>
       <c r="R86" s="18" t="n"/>
       <c r="S86" s="16" t="n"/>
-      <c r="T86" s="17" t="n"/>
+      <c r="T86" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U86" s="17" t="n"/>
     </row>
     <row r="87">
@@ -8911,17 +9688,17 @@
       </c>
       <c r="O89" s="17" t="inlineStr">
         <is>
-          <t>Inquiries page has no sign-in check, and the server always saves user_id = null</t>
+          <t>Form is open to guests (no sign-in prompt: true). Real submit from the site → HTTP 403 'This website origin is not allowed.'; page shows: 'We couldn't send your inquiry. Unexpected token 'T', "This websi"... is not vali'</t>
         </is>
       </c>
       <c r="P89" s="17" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-07, F-33</t>
         </is>
       </c>
       <c r="Q89" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, guest)</t>
         </is>
       </c>
       <c r="R89" s="18" t="n">
@@ -8929,17 +9706,17 @@
       </c>
       <c r="S89" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T89" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Page loaded with the workaround; the POST kept its real Origin header, so this is what every customer gets. No row was created</t>
         </is>
       </c>
       <c r="U89" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -9007,16 +9784,38 @@
       </c>
       <c r="N90" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O90" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O90" s="17" t="inlineStr">
+        <is>
+          <t>Message field invalid (required): true; request sent: false</t>
+        </is>
+      </c>
       <c r="P90" s="17" t="n"/>
-      <c r="Q90" s="17" t="n"/>
-      <c r="R90" s="18" t="n"/>
-      <c r="S90" s="16" t="n"/>
-      <c r="T90" s="17" t="n"/>
-      <c r="U90" s="17" t="n"/>
+      <c r="Q90" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R90" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S90" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T90" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Run as guest</t>
+        </is>
+      </c>
+      <c r="U90" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
@@ -9175,15 +9974,23 @@
       </c>
       <c r="N92" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O92" s="17" t="n"/>
-      <c r="P92" s="17" t="n"/>
+      <c r="P92" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q92" s="17" t="n"/>
       <c r="R92" s="18" t="n"/>
       <c r="S92" s="16" t="n"/>
-      <c r="T92" s="17" t="n"/>
+      <c r="T92" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U92" s="17" t="n"/>
     </row>
     <row r="93">
@@ -9254,15 +10061,23 @@
       </c>
       <c r="N93" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O93" s="17" t="n"/>
-      <c r="P93" s="17" t="n"/>
+      <c r="P93" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q93" s="17" t="n"/>
       <c r="R93" s="18" t="n"/>
       <c r="S93" s="16" t="n"/>
-      <c r="T93" s="17" t="n"/>
+      <c r="T93" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U93" s="17" t="n"/>
     </row>
     <row r="94">
@@ -9329,15 +10144,23 @@
       </c>
       <c r="N94" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O94" s="17" t="n"/>
-      <c r="P94" s="17" t="n"/>
+      <c r="P94" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q94" s="17" t="n"/>
       <c r="R94" s="18" t="n"/>
       <c r="S94" s="16" t="n"/>
-      <c r="T94" s="17" t="n"/>
+      <c r="T94" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U94" s="17" t="n"/>
     </row>
     <row r="95">
@@ -9509,15 +10332,23 @@
       </c>
       <c r="N96" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O96" s="17" t="n"/>
-      <c r="P96" s="17" t="n"/>
+      <c r="P96" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q96" s="17" t="n"/>
       <c r="R96" s="18" t="n"/>
       <c r="S96" s="16" t="n"/>
-      <c r="T96" s="17" t="n"/>
+      <c r="T96" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U96" s="17" t="n"/>
     </row>
     <row r="97">
@@ -9584,15 +10415,23 @@
       </c>
       <c r="N97" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O97" s="17" t="n"/>
-      <c r="P97" s="17" t="n"/>
+      <c r="P97" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q97" s="17" t="n"/>
       <c r="R97" s="18" t="n"/>
       <c r="S97" s="16" t="n"/>
-      <c r="T97" s="17" t="n"/>
+      <c r="T97" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U97" s="17" t="n"/>
     </row>
     <row r="98">
@@ -9659,15 +10498,23 @@
       </c>
       <c r="N98" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O98" s="17" t="n"/>
-      <c r="P98" s="17" t="n"/>
+      <c r="P98" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q98" s="17" t="n"/>
       <c r="R98" s="18" t="n"/>
       <c r="S98" s="16" t="n"/>
-      <c r="T98" s="17" t="n"/>
+      <c r="T98" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U98" s="17" t="n"/>
     </row>
     <row r="99">
@@ -9734,15 +10581,23 @@
       </c>
       <c r="N99" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O99" s="17" t="n"/>
-      <c r="P99" s="17" t="n"/>
+      <c r="P99" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q99" s="17" t="n"/>
       <c r="R99" s="18" t="n"/>
       <c r="S99" s="16" t="n"/>
-      <c r="T99" s="17" t="n"/>
+      <c r="T99" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U99" s="17" t="n"/>
     </row>
     <row r="100">
@@ -9809,15 +10664,23 @@
       </c>
       <c r="N100" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O100" s="17" t="n"/>
-      <c r="P100" s="17" t="n"/>
+      <c r="P100" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q100" s="17" t="n"/>
       <c r="R100" s="18" t="n"/>
       <c r="S100" s="16" t="n"/>
-      <c r="T100" s="17" t="n"/>
+      <c r="T100" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U100" s="17" t="n"/>
     </row>
     <row r="101">
@@ -9884,15 +10747,23 @@
       </c>
       <c r="N101" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O101" s="17" t="n"/>
-      <c r="P101" s="17" t="n"/>
+      <c r="P101" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q101" s="17" t="n"/>
       <c r="R101" s="18" t="n"/>
       <c r="S101" s="16" t="n"/>
-      <c r="T101" s="17" t="n"/>
+      <c r="T101" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U101" s="17" t="n"/>
     </row>
     <row r="102">
@@ -9959,15 +10830,23 @@
       </c>
       <c r="N102" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O102" s="17" t="n"/>
-      <c r="P102" s="17" t="n"/>
+      <c r="P102" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q102" s="17" t="n"/>
       <c r="R102" s="18" t="n"/>
       <c r="S102" s="16" t="n"/>
-      <c r="T102" s="17" t="n"/>
+      <c r="T102" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U102" s="17" t="n"/>
     </row>
     <row r="103">
@@ -10034,15 +10913,23 @@
       </c>
       <c r="N103" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O103" s="17" t="n"/>
-      <c r="P103" s="17" t="n"/>
+      <c r="P103" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q103" s="17" t="n"/>
       <c r="R103" s="18" t="n"/>
       <c r="S103" s="16" t="n"/>
-      <c r="T103" s="17" t="n"/>
+      <c r="T103" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U103" s="17" t="n"/>
     </row>
     <row r="104">
@@ -10505,15 +11392,23 @@
       </c>
       <c r="N108" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O108" s="17" t="n"/>
-      <c r="P108" s="17" t="n"/>
+      <c r="P108" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q108" s="17" t="n"/>
       <c r="R108" s="18" t="n"/>
       <c r="S108" s="16" t="n"/>
-      <c r="T108" s="17" t="n"/>
+      <c r="T108" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U108" s="17" t="n"/>
     </row>
     <row r="109">
@@ -10580,15 +11475,23 @@
       </c>
       <c r="N109" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O109" s="17" t="n"/>
-      <c r="P109" s="17" t="n"/>
+      <c r="P109" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q109" s="17" t="n"/>
       <c r="R109" s="18" t="n"/>
       <c r="S109" s="16" t="n"/>
-      <c r="T109" s="17" t="n"/>
+      <c r="T109" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U109" s="17" t="n"/>
     </row>
     <row r="110">
@@ -10655,15 +11558,23 @@
       </c>
       <c r="N110" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O110" s="17" t="n"/>
-      <c r="P110" s="17" t="n"/>
+      <c r="P110" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q110" s="17" t="n"/>
       <c r="R110" s="18" t="n"/>
       <c r="S110" s="16" t="n"/>
-      <c r="T110" s="17" t="n"/>
+      <c r="T110" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U110" s="17" t="n"/>
     </row>
     <row r="111">
@@ -10730,15 +11641,23 @@
       </c>
       <c r="N111" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O111" s="17" t="n"/>
-      <c r="P111" s="17" t="n"/>
+      <c r="P111" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q111" s="17" t="n"/>
       <c r="R111" s="18" t="n"/>
       <c r="S111" s="16" t="n"/>
-      <c r="T111" s="17" t="n"/>
+      <c r="T111" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U111" s="17" t="n"/>
     </row>
     <row r="112">
@@ -10910,15 +11829,23 @@
       </c>
       <c r="N113" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O113" s="17" t="n"/>
-      <c r="P113" s="17" t="n"/>
+      <c r="P113" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q113" s="17" t="n"/>
       <c r="R113" s="18" t="n"/>
       <c r="S113" s="16" t="n"/>
-      <c r="T113" s="17" t="n"/>
+      <c r="T113" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U113" s="17" t="n"/>
     </row>
     <row r="114">
@@ -10985,15 +11912,23 @@
       </c>
       <c r="N114" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O114" s="17" t="n"/>
-      <c r="P114" s="17" t="n"/>
+      <c r="P114" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q114" s="17" t="n"/>
       <c r="R114" s="18" t="n"/>
       <c r="S114" s="16" t="n"/>
-      <c r="T114" s="17" t="n"/>
+      <c r="T114" s="17" t="inlineStr">
+        <is>
+          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U114" s="17" t="n"/>
     </row>
     <row r="115">
@@ -11060,16 +11995,38 @@
       </c>
       <c r="N115" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O115" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O115" s="17" t="inlineStr">
+        <is>
+          <t>Prompt: true; sign-in buttons: 2; account data shown: false</t>
+        </is>
+      </c>
       <c r="P115" s="17" t="n"/>
-      <c r="Q115" s="17" t="n"/>
-      <c r="R115" s="18" t="n"/>
-      <c r="S115" s="16" t="n"/>
-      <c r="T115" s="17" t="n"/>
-      <c r="U115" s="17" t="n"/>
+      <c r="Q115" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R115" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S115" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T115" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+        </is>
+      </c>
+      <c r="U115" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
@@ -11135,15 +12092,23 @@
       </c>
       <c r="N116" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O116" s="17" t="n"/>
-      <c r="P116" s="17" t="n"/>
+      <c r="P116" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q116" s="17" t="n"/>
       <c r="R116" s="18" t="n"/>
       <c r="S116" s="16" t="n"/>
-      <c r="T116" s="17" t="n"/>
+      <c r="T116" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U116" s="17" t="n"/>
     </row>
     <row r="117">
@@ -11210,15 +12175,23 @@
       </c>
       <c r="N117" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O117" s="17" t="n"/>
-      <c r="P117" s="17" t="n"/>
+      <c r="P117" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q117" s="17" t="n"/>
       <c r="R117" s="18" t="n"/>
       <c r="S117" s="16" t="n"/>
-      <c r="T117" s="17" t="n"/>
+      <c r="T117" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U117" s="17" t="n"/>
     </row>
     <row r="118">
@@ -11285,15 +12258,23 @@
       </c>
       <c r="N118" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O118" s="17" t="n"/>
-      <c r="P118" s="17" t="n"/>
+      <c r="P118" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q118" s="17" t="n"/>
       <c r="R118" s="18" t="n"/>
       <c r="S118" s="16" t="n"/>
-      <c r="T118" s="17" t="n"/>
+      <c r="T118" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U118" s="17" t="n"/>
     </row>
     <row r="119">
@@ -11360,15 +12341,23 @@
       </c>
       <c r="N119" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O119" s="17" t="n"/>
-      <c r="P119" s="17" t="n"/>
+      <c r="P119" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q119" s="17" t="n"/>
       <c r="R119" s="18" t="n"/>
       <c r="S119" s="16" t="n"/>
-      <c r="T119" s="17" t="n"/>
+      <c r="T119" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U119" s="17" t="n"/>
     </row>
     <row r="120">
@@ -11435,15 +12424,23 @@
       </c>
       <c r="N120" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O120" s="17" t="n"/>
-      <c r="P120" s="17" t="n"/>
+      <c r="P120" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q120" s="17" t="n"/>
       <c r="R120" s="18" t="n"/>
       <c r="S120" s="16" t="n"/>
-      <c r="T120" s="17" t="n"/>
+      <c r="T120" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U120" s="17" t="n"/>
     </row>
     <row r="121">
@@ -11510,15 +12507,23 @@
       </c>
       <c r="N121" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O121" s="17" t="n"/>
-      <c r="P121" s="17" t="n"/>
+      <c r="P121" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q121" s="17" t="n"/>
       <c r="R121" s="18" t="n"/>
       <c r="S121" s="16" t="n"/>
-      <c r="T121" s="17" t="n"/>
+      <c r="T121" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U121" s="17" t="n"/>
     </row>
     <row r="122">
@@ -11585,15 +12590,23 @@
       </c>
       <c r="N122" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O122" s="17" t="n"/>
-      <c r="P122" s="17" t="n"/>
+      <c r="P122" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q122" s="17" t="n"/>
       <c r="R122" s="18" t="n"/>
       <c r="S122" s="16" t="n"/>
-      <c r="T122" s="17" t="n"/>
+      <c r="T122" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U122" s="17" t="n"/>
     </row>
     <row r="123">
@@ -11660,15 +12673,23 @@
       </c>
       <c r="N123" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O123" s="17" t="n"/>
-      <c r="P123" s="17" t="n"/>
+      <c r="P123" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q123" s="17" t="n"/>
       <c r="R123" s="18" t="n"/>
       <c r="S123" s="16" t="n"/>
-      <c r="T123" s="17" t="n"/>
+      <c r="T123" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U123" s="17" t="n"/>
     </row>
     <row r="124">
@@ -11735,15 +12756,23 @@
       </c>
       <c r="N124" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O124" s="17" t="n"/>
-      <c r="P124" s="17" t="n"/>
+      <c r="P124" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q124" s="17" t="n"/>
       <c r="R124" s="18" t="n"/>
       <c r="S124" s="16" t="n"/>
-      <c r="T124" s="17" t="n"/>
+      <c r="T124" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U124" s="17" t="n"/>
     </row>
     <row r="125">
@@ -11810,15 +12839,23 @@
       </c>
       <c r="N125" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O125" s="17" t="n"/>
-      <c r="P125" s="17" t="n"/>
+      <c r="P125" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q125" s="17" t="n"/>
       <c r="R125" s="18" t="n"/>
       <c r="S125" s="16" t="n"/>
-      <c r="T125" s="17" t="n"/>
+      <c r="T125" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U125" s="17" t="n"/>
     </row>
     <row r="126">
@@ -11885,15 +12922,23 @@
       </c>
       <c r="N126" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O126" s="17" t="n"/>
-      <c r="P126" s="17" t="n"/>
+      <c r="P126" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q126" s="17" t="n"/>
       <c r="R126" s="18" t="n"/>
       <c r="S126" s="16" t="n"/>
-      <c r="T126" s="17" t="n"/>
+      <c r="T126" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U126" s="17" t="n"/>
     </row>
     <row r="127">
@@ -11960,15 +13005,23 @@
       </c>
       <c r="N127" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O127" s="17" t="n"/>
-      <c r="P127" s="17" t="n"/>
+      <c r="P127" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q127" s="17" t="n"/>
       <c r="R127" s="18" t="n"/>
       <c r="S127" s="16" t="n"/>
-      <c r="T127" s="17" t="n"/>
+      <c r="T127" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U127" s="17" t="n"/>
     </row>
     <row r="128">
@@ -12035,15 +13088,23 @@
       </c>
       <c r="N128" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O128" s="17" t="n"/>
-      <c r="P128" s="17" t="n"/>
+      <c r="P128" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q128" s="17" t="n"/>
       <c r="R128" s="18" t="n"/>
       <c r="S128" s="16" t="n"/>
-      <c r="T128" s="17" t="n"/>
+      <c r="T128" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U128" s="17" t="n"/>
     </row>
     <row r="129">
@@ -12320,20 +13381,42 @@
       </c>
       <c r="N131" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O131" s="17" t="n"/>
-      <c r="P131" s="17" t="n"/>
-      <c r="Q131" s="17" t="n"/>
-      <c r="R131" s="18" t="n"/>
-      <c r="S131" s="16" t="n"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O131" s="17" t="inlineStr">
+        <is>
+          <t>Cannot time a real page load: in Chrome without the workaround the page is blank (F-33). curl on broadband: HTML 0.48–0.55 s, JS bundle 1.04 MB in 0.93 s</t>
+        </is>
+      </c>
+      <c r="P131" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
+      <c r="Q131" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R131" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S131" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
       <c r="T131" s="17" t="inlineStr">
         <is>
-          <t>Partial evidence (curl, broadband): HTML 0.48–0.55 s; JS bundle 1.04 MB in 0.93 s. Still needs the Chrome DevTools Fast 4G measurement</t>
-        </is>
-      </c>
-      <c r="U131" s="17" t="n"/>
+          <t>Re-run with DevTools Fast 4G once F-33 is fixed</t>
+        </is>
+      </c>
+      <c r="U131" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -12399,15 +13482,23 @@
       </c>
       <c r="N132" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O132" s="17" t="n"/>
-      <c r="P132" s="17" t="n"/>
+      <c r="P132" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q132" s="17" t="n"/>
       <c r="R132" s="18" t="n"/>
       <c r="S132" s="16" t="n"/>
-      <c r="T132" s="17" t="n"/>
+      <c r="T132" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U132" s="17" t="n"/>
     </row>
     <row r="133">
@@ -12474,16 +13565,38 @@
       </c>
       <c r="N133" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="O133" s="17" t="n"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O133" s="17" t="inlineStr">
+        <is>
+          <t>Page width at 375 px viewport: / 375px, /catering/buffet 375px, /function-rooms/reserve 375px, /delivery/order 375px, /inquiries 375px. Horizontal overflow: none</t>
+        </is>
+      </c>
       <c r="P133" s="17" t="n"/>
-      <c r="Q133" s="17" t="n"/>
-      <c r="R133" s="18" t="n"/>
-      <c r="S133" s="16" t="n"/>
-      <c r="T133" s="17" t="n"/>
-      <c r="U133" s="17" t="n"/>
+      <c r="Q133" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, guest)</t>
+        </is>
+      </c>
+      <c r="R133" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S133" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
+      <c r="T133" s="17" t="inlineStr">
+        <is>
+          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Layout part done as guest; the step count needs a signed-in booking (S-07, S-09)</t>
+        </is>
+      </c>
+      <c r="U133" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
@@ -12549,15 +13662,23 @@
       </c>
       <c r="N134" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O134" s="17" t="n"/>
-      <c r="P134" s="17" t="n"/>
+      <c r="P134" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q134" s="17" t="n"/>
       <c r="R134" s="18" t="n"/>
       <c r="S134" s="16" t="n"/>
-      <c r="T134" s="17" t="n"/>
+      <c r="T134" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U134" s="17" t="n"/>
     </row>
     <row r="135">
@@ -12624,15 +13745,23 @@
       </c>
       <c r="N135" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O135" s="17" t="n"/>
-      <c r="P135" s="17" t="n"/>
+      <c r="P135" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q135" s="17" t="n"/>
       <c r="R135" s="18" t="n"/>
       <c r="S135" s="16" t="n"/>
-      <c r="T135" s="17" t="n"/>
+      <c r="T135" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U135" s="17" t="n"/>
     </row>
     <row r="136">
@@ -12699,15 +13828,23 @@
       </c>
       <c r="N136" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O136" s="17" t="n"/>
-      <c r="P136" s="17" t="n"/>
+      <c r="P136" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q136" s="17" t="n"/>
       <c r="R136" s="18" t="n"/>
       <c r="S136" s="16" t="n"/>
-      <c r="T136" s="17" t="n"/>
+      <c r="T136" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U136" s="17" t="n"/>
     </row>
     <row r="137">
@@ -12774,15 +13911,23 @@
       </c>
       <c r="N137" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O137" s="17" t="n"/>
-      <c r="P137" s="17" t="n"/>
+      <c r="P137" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q137" s="17" t="n"/>
       <c r="R137" s="18" t="n"/>
       <c r="S137" s="16" t="n"/>
-      <c r="T137" s="17" t="n"/>
+      <c r="T137" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U137" s="17" t="n"/>
     </row>
     <row r="138">
@@ -12849,15 +13994,23 @@
       </c>
       <c r="N138" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O138" s="17" t="n"/>
-      <c r="P138" s="17" t="n"/>
+      <c r="P138" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q138" s="17" t="n"/>
       <c r="R138" s="18" t="n"/>
       <c r="S138" s="16" t="n"/>
-      <c r="T138" s="17" t="n"/>
+      <c r="T138" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U138" s="17" t="n"/>
     </row>
     <row r="139">
@@ -12924,15 +14077,23 @@
       </c>
       <c r="N139" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O139" s="17" t="n"/>
-      <c r="P139" s="17" t="n"/>
+      <c r="P139" s="17" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
       <c r="Q139" s="17" t="n"/>
       <c r="R139" s="18" t="n"/>
       <c r="S139" s="16" t="n"/>
-      <c r="T139" s="17" t="n"/>
+      <c r="T139" s="17" t="inlineStr">
+        <is>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+        </is>
+      </c>
       <c r="U139" s="17" t="n"/>
     </row>
     <row r="140">
@@ -13286,7 +14447,7 @@
       </c>
       <c r="N143" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O143" s="17" t="n"/>
@@ -13294,7 +14455,11 @@
       <c r="Q143" s="17" t="n"/>
       <c r="R143" s="18" t="n"/>
       <c r="S143" s="16" t="n"/>
-      <c r="T143" s="17" t="n"/>
+      <c r="T143" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U143" s="17" t="n"/>
     </row>
     <row r="144">
@@ -13361,7 +14526,7 @@
       </c>
       <c r="N144" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O144" s="17" t="n"/>
@@ -13369,7 +14534,11 @@
       <c r="Q144" s="17" t="n"/>
       <c r="R144" s="18" t="n"/>
       <c r="S144" s="16" t="n"/>
-      <c r="T144" s="17" t="n"/>
+      <c r="T144" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U144" s="17" t="n"/>
     </row>
     <row r="145">
@@ -13440,7 +14609,7 @@
       </c>
       <c r="N145" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O145" s="17" t="n"/>
@@ -13448,7 +14617,11 @@
       <c r="Q145" s="17" t="n"/>
       <c r="R145" s="18" t="n"/>
       <c r="S145" s="16" t="n"/>
-      <c r="T145" s="17" t="n"/>
+      <c r="T145" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U145" s="17" t="n"/>
     </row>
     <row r="146">
@@ -13515,7 +14688,7 @@
       </c>
       <c r="N146" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O146" s="17" t="n"/>
@@ -13523,7 +14696,11 @@
       <c r="Q146" s="17" t="n"/>
       <c r="R146" s="18" t="n"/>
       <c r="S146" s="16" t="n"/>
-      <c r="T146" s="17" t="n"/>
+      <c r="T146" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U146" s="17" t="n"/>
     </row>
     <row r="147">
@@ -13594,7 +14771,7 @@
       </c>
       <c r="N147" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O147" s="17" t="n"/>
@@ -13602,7 +14779,11 @@
       <c r="Q147" s="17" t="n"/>
       <c r="R147" s="18" t="n"/>
       <c r="S147" s="16" t="n"/>
-      <c r="T147" s="17" t="n"/>
+      <c r="T147" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U147" s="17" t="n"/>
     </row>
     <row r="148">
@@ -13669,7 +14850,7 @@
       </c>
       <c r="N148" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O148" s="17" t="n"/>
@@ -13677,7 +14858,11 @@
       <c r="Q148" s="17" t="n"/>
       <c r="R148" s="18" t="n"/>
       <c r="S148" s="16" t="n"/>
-      <c r="T148" s="17" t="n"/>
+      <c r="T148" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U148" s="17" t="n"/>
     </row>
     <row r="149">
@@ -13748,7 +14933,7 @@
       </c>
       <c r="N149" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O149" s="17" t="n"/>
@@ -13756,7 +14941,11 @@
       <c r="Q149" s="17" t="n"/>
       <c r="R149" s="18" t="n"/>
       <c r="S149" s="16" t="n"/>
-      <c r="T149" s="17" t="n"/>
+      <c r="T149" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U149" s="17" t="n"/>
     </row>
     <row r="150">
@@ -13823,7 +15012,7 @@
       </c>
       <c r="N150" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O150" s="17" t="n"/>
@@ -13831,7 +15020,11 @@
       <c r="Q150" s="17" t="n"/>
       <c r="R150" s="18" t="n"/>
       <c r="S150" s="16" t="n"/>
-      <c r="T150" s="17" t="n"/>
+      <c r="T150" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U150" s="17" t="n"/>
     </row>
     <row r="151">
@@ -13898,7 +15091,7 @@
       </c>
       <c r="N151" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O151" s="17" t="n"/>
@@ -13906,7 +15099,11 @@
       <c r="Q151" s="17" t="n"/>
       <c r="R151" s="18" t="n"/>
       <c r="S151" s="16" t="n"/>
-      <c r="T151" s="17" t="n"/>
+      <c r="T151" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U151" s="17" t="n"/>
     </row>
     <row r="152">
@@ -13973,7 +15170,7 @@
       </c>
       <c r="N152" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O152" s="17" t="n"/>
@@ -13981,7 +15178,11 @@
       <c r="Q152" s="17" t="n"/>
       <c r="R152" s="18" t="n"/>
       <c r="S152" s="16" t="n"/>
-      <c r="T152" s="17" t="n"/>
+      <c r="T152" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U152" s="17" t="n"/>
     </row>
     <row r="153">
@@ -14052,7 +15253,7 @@
       </c>
       <c r="N153" s="16" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O153" s="17" t="n"/>
@@ -14060,7 +15261,11 @@
       <c r="Q153" s="17" t="n"/>
       <c r="R153" s="18" t="n"/>
       <c r="S153" s="16" t="n"/>
-      <c r="T153" s="17" t="n"/>
+      <c r="T153" s="17" t="inlineStr">
+        <is>
+          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+        </is>
+      </c>
       <c r="U153" s="17" t="n"/>
     </row>
     <row r="154">
@@ -14429,7 +15634,7 @@
       </c>
       <c r="G2" s="15" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-07, F-33</t>
         </is>
       </c>
       <c r="H2" s="9">
@@ -14457,7 +15662,7 @@
         <v/>
       </c>
       <c r="N2" s="10">
-        <f>IF(H2=0,0,(H2-M2)/H2)</f>
+        <f>IF(H2=0,0,(I2+J2+L2)/H2)</f>
         <v/>
       </c>
       <c r="O2" s="9">
@@ -14526,7 +15731,7 @@
         <v/>
       </c>
       <c r="N3" s="10">
-        <f>IF(H3=0,0,(H3-M3)/H3)</f>
+        <f>IF(H3=0,0,(I3+J3+L3)/H3)</f>
         <v/>
       </c>
       <c r="O3" s="9">
@@ -14595,7 +15800,7 @@
         <v/>
       </c>
       <c r="N4" s="10">
-        <f>IF(H4=0,0,(H4-M4)/H4)</f>
+        <f>IF(H4=0,0,(I4+J4+L4)/H4)</f>
         <v/>
       </c>
       <c r="O4" s="9">
@@ -14664,7 +15869,7 @@
         <v/>
       </c>
       <c r="N5" s="10">
-        <f>IF(H5=0,0,(H5-M5)/H5)</f>
+        <f>IF(H5=0,0,(I5+J5+L5)/H5)</f>
         <v/>
       </c>
       <c r="O5" s="9">
@@ -14733,7 +15938,7 @@
         <v/>
       </c>
       <c r="N6" s="10">
-        <f>IF(H6=0,0,(H6-M6)/H6)</f>
+        <f>IF(H6=0,0,(I6+J6+L6)/H6)</f>
         <v/>
       </c>
       <c r="O6" s="9">
@@ -14802,7 +16007,7 @@
         <v/>
       </c>
       <c r="N7" s="10">
-        <f>IF(H7=0,0,(H7-M7)/H7)</f>
+        <f>IF(H7=0,0,(I7+J7+L7)/H7)</f>
         <v/>
       </c>
       <c r="O7" s="9">
@@ -14871,7 +16076,7 @@
         <v/>
       </c>
       <c r="N8" s="10">
-        <f>IF(H8=0,0,(H8-M8)/H8)</f>
+        <f>IF(H8=0,0,(I8+J8+L8)/H8)</f>
         <v/>
       </c>
       <c r="O8" s="9">
@@ -14940,7 +16145,7 @@
         <v/>
       </c>
       <c r="N9" s="10">
-        <f>IF(H9=0,0,(H9-M9)/H9)</f>
+        <f>IF(H9=0,0,(I9+J9+L9)/H9)</f>
         <v/>
       </c>
       <c r="O9" s="9">
@@ -15009,7 +16214,7 @@
         <v/>
       </c>
       <c r="N10" s="10">
-        <f>IF(H10=0,0,(H10-M10)/H10)</f>
+        <f>IF(H10=0,0,(I10+J10+L10)/H10)</f>
         <v/>
       </c>
       <c r="O10" s="9">
@@ -15078,7 +16283,7 @@
         <v/>
       </c>
       <c r="N11" s="10">
-        <f>IF(H11=0,0,(H11-M11)/H11)</f>
+        <f>IF(H11=0,0,(I11+J11+L11)/H11)</f>
         <v/>
       </c>
       <c r="O11" s="9">
@@ -15147,7 +16352,7 @@
         <v/>
       </c>
       <c r="N12" s="10">
-        <f>IF(H12=0,0,(H12-M12)/H12)</f>
+        <f>IF(H12=0,0,(I12+J12+L12)/H12)</f>
         <v/>
       </c>
       <c r="O12" s="9">
@@ -15216,7 +16421,7 @@
         <v/>
       </c>
       <c r="N13" s="10">
-        <f>IF(H13=0,0,(H13-M13)/H13)</f>
+        <f>IF(H13=0,0,(I13+J13+L13)/H13)</f>
         <v/>
       </c>
       <c r="O13" s="9">
@@ -15285,7 +16490,7 @@
         <v/>
       </c>
       <c r="N14" s="10">
-        <f>IF(H14=0,0,(H14-M14)/H14)</f>
+        <f>IF(H14=0,0,(I14+J14+L14)/H14)</f>
         <v/>
       </c>
       <c r="O14" s="9">
@@ -15354,7 +16559,7 @@
         <v/>
       </c>
       <c r="N15" s="10">
-        <f>IF(H15=0,0,(H15-M15)/H15)</f>
+        <f>IF(H15=0,0,(I15+J15+L15)/H15)</f>
         <v/>
       </c>
       <c r="O15" s="9">
@@ -15423,7 +16628,7 @@
         <v/>
       </c>
       <c r="N16" s="10">
-        <f>IF(H16=0,0,(H16-M16)/H16)</f>
+        <f>IF(H16=0,0,(I16+J16+L16)/H16)</f>
         <v/>
       </c>
       <c r="O16" s="9">
@@ -15492,7 +16697,7 @@
         <v/>
       </c>
       <c r="N17" s="10">
-        <f>IF(H17=0,0,(H17-M17)/H17)</f>
+        <f>IF(H17=0,0,(I17+J17+L17)/H17)</f>
         <v/>
       </c>
       <c r="O17" s="9">
@@ -15561,7 +16766,7 @@
         <v/>
       </c>
       <c r="N18" s="10">
-        <f>IF(H18=0,0,(H18-M18)/H18)</f>
+        <f>IF(H18=0,0,(I18+J18+L18)/H18)</f>
         <v/>
       </c>
       <c r="O18" s="9">
@@ -15630,7 +16835,7 @@
         <v/>
       </c>
       <c r="N19" s="10">
-        <f>IF(H19=0,0,(H19-M19)/H19)</f>
+        <f>IF(H19=0,0,(I19+J19+L19)/H19)</f>
         <v/>
       </c>
       <c r="O19" s="9">
@@ -15699,7 +16904,7 @@
         <v/>
       </c>
       <c r="N20" s="10">
-        <f>IF(H20=0,0,(H20-M20)/H20)</f>
+        <f>IF(H20=0,0,(I20+J20+L20)/H20)</f>
         <v/>
       </c>
       <c r="O20" s="9">
@@ -15768,7 +16973,7 @@
         <v/>
       </c>
       <c r="N21" s="10">
-        <f>IF(H21=0,0,(H21-M21)/H21)</f>
+        <f>IF(H21=0,0,(I21+J21+L21)/H21)</f>
         <v/>
       </c>
       <c r="O21" s="9">
@@ -15837,7 +17042,7 @@
         <v/>
       </c>
       <c r="N22" s="10">
-        <f>IF(H22=0,0,(H22-M22)/H22)</f>
+        <f>IF(H22=0,0,(I22+J22+L22)/H22)</f>
         <v/>
       </c>
       <c r="O22" s="9">
@@ -15906,7 +17111,7 @@
         <v/>
       </c>
       <c r="N23" s="10">
-        <f>IF(H23=0,0,(H23-M23)/H23)</f>
+        <f>IF(H23=0,0,(I23+J23+L23)/H23)</f>
         <v/>
       </c>
       <c r="O23" s="9">
@@ -15975,7 +17180,7 @@
         <v/>
       </c>
       <c r="N24" s="10">
-        <f>IF(H24=0,0,(H24-M24)/H24)</f>
+        <f>IF(H24=0,0,(I24+J24+L24)/H24)</f>
         <v/>
       </c>
       <c r="O24" s="9">
@@ -16044,7 +17249,7 @@
         <v/>
       </c>
       <c r="N25" s="10">
-        <f>IF(H25=0,0,(H25-M25)/H25)</f>
+        <f>IF(H25=0,0,(I25+J25+L25)/H25)</f>
         <v/>
       </c>
       <c r="O25" s="9">
@@ -16113,7 +17318,7 @@
         <v/>
       </c>
       <c r="N26" s="10">
-        <f>IF(H26=0,0,(H26-M26)/H26)</f>
+        <f>IF(H26=0,0,(I26+J26+L26)/H26)</f>
         <v/>
       </c>
       <c r="O26" s="9">
@@ -16182,7 +17387,7 @@
         <v/>
       </c>
       <c r="N27" s="10">
-        <f>IF(H27=0,0,(H27-M27)/H27)</f>
+        <f>IF(H27=0,0,(I27+J27+L27)/H27)</f>
         <v/>
       </c>
       <c r="O27" s="9">
@@ -16251,7 +17456,7 @@
         <v/>
       </c>
       <c r="N28" s="10">
-        <f>IF(H28=0,0,(H28-M28)/H28)</f>
+        <f>IF(H28=0,0,(I28+J28+L28)/H28)</f>
         <v/>
       </c>
       <c r="O28" s="9">
@@ -16320,7 +17525,7 @@
         <v/>
       </c>
       <c r="N29" s="10">
-        <f>IF(H29=0,0,(H29-M29)/H29)</f>
+        <f>IF(H29=0,0,(I29+J29+L29)/H29)</f>
         <v/>
       </c>
       <c r="O29" s="9">
@@ -16389,7 +17594,7 @@
         <v/>
       </c>
       <c r="N30" s="10">
-        <f>IF(H30=0,0,(H30-M30)/H30)</f>
+        <f>IF(H30=0,0,(I30+J30+L30)/H30)</f>
         <v/>
       </c>
       <c r="O30" s="9">
@@ -16458,7 +17663,7 @@
         <v/>
       </c>
       <c r="N31" s="10">
-        <f>IF(H31=0,0,(H31-M31)/H31)</f>
+        <f>IF(H31=0,0,(I31+J31+L31)/H31)</f>
         <v/>
       </c>
       <c r="O31" s="9">
@@ -16527,7 +17732,7 @@
         <v/>
       </c>
       <c r="N32" s="10">
-        <f>IF(H32=0,0,(H32-M32)/H32)</f>
+        <f>IF(H32=0,0,(I32+J32+L32)/H32)</f>
         <v/>
       </c>
       <c r="O32" s="9">
@@ -16596,7 +17801,7 @@
         <v/>
       </c>
       <c r="N33" s="10">
-        <f>IF(H33=0,0,(H33-M33)/H33)</f>
+        <f>IF(H33=0,0,(I33+J33+L33)/H33)</f>
         <v/>
       </c>
       <c r="O33" s="9">
@@ -16665,7 +17870,7 @@
         <v/>
       </c>
       <c r="N34" s="10">
-        <f>IF(H34=0,0,(H34-M34)/H34)</f>
+        <f>IF(H34=0,0,(I34+J34+L34)/H34)</f>
         <v/>
       </c>
       <c r="O34" s="9">
@@ -16734,7 +17939,7 @@
         <v/>
       </c>
       <c r="N35" s="10">
-        <f>IF(H35=0,0,(H35-M35)/H35)</f>
+        <f>IF(H35=0,0,(I35+J35+L35)/H35)</f>
         <v/>
       </c>
       <c r="O35" s="9">
@@ -16803,7 +18008,7 @@
         <v/>
       </c>
       <c r="N36" s="10">
-        <f>IF(H36=0,0,(H36-M36)/H36)</f>
+        <f>IF(H36=0,0,(I36+J36+L36)/H36)</f>
         <v/>
       </c>
       <c r="O36" s="9">
@@ -16872,7 +18077,7 @@
         <v/>
       </c>
       <c r="N37" s="10">
-        <f>IF(H37=0,0,(H37-M37)/H37)</f>
+        <f>IF(H37=0,0,(I37+J37+L37)/H37)</f>
         <v/>
       </c>
       <c r="O37" s="9">
@@ -16941,7 +18146,7 @@
         <v/>
       </c>
       <c r="N38" s="10">
-        <f>IF(H38=0,0,(H38-M38)/H38)</f>
+        <f>IF(H38=0,0,(I38+J38+L38)/H38)</f>
         <v/>
       </c>
       <c r="O38" s="9">
@@ -17010,7 +18215,7 @@
         <v/>
       </c>
       <c r="N39" s="10">
-        <f>IF(H39=0,0,(H39-M39)/H39)</f>
+        <f>IF(H39=0,0,(I39+J39+L39)/H39)</f>
         <v/>
       </c>
       <c r="O39" s="9">
@@ -17079,7 +18284,7 @@
         <v/>
       </c>
       <c r="N40" s="10">
-        <f>IF(H40=0,0,(H40-M40)/H40)</f>
+        <f>IF(H40=0,0,(I40+J40+L40)/H40)</f>
         <v/>
       </c>
       <c r="O40" s="9">
@@ -17148,7 +18353,7 @@
         <v/>
       </c>
       <c r="N41" s="10">
-        <f>IF(H41=0,0,(H41-M41)/H41)</f>
+        <f>IF(H41=0,0,(I41+J41+L41)/H41)</f>
         <v/>
       </c>
       <c r="O41" s="9">
@@ -17192,7 +18397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18260,7 +19465,11 @@
       </c>
       <c r="J20" s="17" t="n"/>
       <c r="K20" s="18" t="n"/>
-      <c r="L20" s="17" t="n"/>
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t>Confirmed by inspection of the deployed build on 2026-10-07; still open (not fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -18939,21 +20148,74 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>F-33</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>P1 (blocker)</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>The live site is blank in every browser. The server's origin guard rejects the site's own origin, so the JS and CSS (loaded with an Origin header because Vite marks them crossorigin) return 403 "This website origin is not allowed.". The same guard rejects the inquiry form's POST, and the page then shows customers a raw parse error ("Unexpected token 'T'…"). Fix: add https://capitolrestaurant.up.railway.app to FRONTEND_ORIGINS on Railway, or let same-origin requests through the guard</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>webhook.js:39-50 (guard uses only FRONTEND_ORIGINS); live: curl -H 'Origin: https://capitolrestaurant.up.railway.app' …/assets/index-Bq1AsZVl.js → 403 on 2026-10-07</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>§5.1 Availability, REQ-INQ-001</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>REQ-INQ-001</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>IQ-01, NF-01, S-02</t>
+        </is>
+      </c>
+      <c r="H34" s="9">
+        <f>COUNTIFS('Test Cases'!$P$2:$P$155,"*"&amp;A34&amp;"*",'Test Cases'!$N$2:$N$155,"Fail")</f>
+        <v/>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="17" t="inlineStr">
+        <is>
+          <t>Found 2026-10-07 by the Playwright run (S-02). Live site blank for all browser users; urgent before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Failed Cases counts test cases whose Defect / Finding ID contains this finding and whose Status is Fail. Note: 'F-1' style partial matches are avoided because IDs are two digits (F-01 … F-31).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L33"/>
+  <autoFilter ref="A1:L34"/>
   <mergeCells count="1">
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:H36"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I2:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,In progress,Fixed,Verified,Won't fix,SRS to update"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/qa/Capitol-RTM.xlsx
+++ b/docs/qa/Capitol-RTM.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$U$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RTM'!$A$1:$O$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Findings'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Findings'!$A$1:$L$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>main @ 010694c</t>
+          <t>main @ 8990106 (010694c + the F-33 origin-guard fix)</t>
         </is>
       </c>
     </row>
@@ -1441,11 +1441,11 @@
         </is>
       </c>
       <c r="B34" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A34,Findings!$B$2:$B$34,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A34,Findings!$B$2:$B$35,"P1*")</f>
         <v/>
       </c>
       <c r="C34" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A34,Findings!$B$2:$B$34,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A34,Findings!$B$2:$B$35,"P2*")</f>
         <v/>
       </c>
       <c r="D34" s="9">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A35,Findings!$B$2:$B$34,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A35,Findings!$B$2:$B$35,"P1*")</f>
         <v/>
       </c>
       <c r="C35" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A35,Findings!$B$2:$B$34,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A35,Findings!$B$2:$B$35,"P2*")</f>
         <v/>
       </c>
       <c r="D35" s="9">
@@ -1479,11 +1479,11 @@
         </is>
       </c>
       <c r="B36" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A36,Findings!$B$2:$B$34,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A36,Findings!$B$2:$B$35,"P1*")</f>
         <v/>
       </c>
       <c r="C36" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A36,Findings!$B$2:$B$34,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A36,Findings!$B$2:$B$35,"P2*")</f>
         <v/>
       </c>
       <c r="D36" s="9">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A37,Findings!$B$2:$B$34,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A37,Findings!$B$2:$B$35,"P1*")</f>
         <v/>
       </c>
       <c r="C37" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A37,Findings!$B$2:$B$34,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A37,Findings!$B$2:$B$35,"P2*")</f>
         <v/>
       </c>
       <c r="D37" s="9">
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="B38" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A38,Findings!$B$2:$B$34,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A38,Findings!$B$2:$B$35,"P1*")</f>
         <v/>
       </c>
       <c r="C38" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A38,Findings!$B$2:$B$34,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A38,Findings!$B$2:$B$35,"P2*")</f>
         <v/>
       </c>
       <c r="D38" s="9">
@@ -1536,11 +1536,11 @@
         </is>
       </c>
       <c r="B39" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A39,Findings!$B$2:$B$34,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A39,Findings!$B$2:$B$35,"P1*")</f>
         <v/>
       </c>
       <c r="C39" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$34,A39,Findings!$B$2:$B$34,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$35,A39,Findings!$B$2:$B$35,"P2*")</f>
         <v/>
       </c>
       <c r="D39" s="9">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="S2" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T2" s="17" t="n"/>
@@ -1849,22 +1849,18 @@
       </c>
       <c r="N3" s="16" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O3" s="17" t="inlineStr">
         <is>
-          <t>Blank page in Chrome: the site's own assets return 403 'This website origin is not allowed.' (/assets/index-Cva6tJ4s.css, /assets/index-Bq1AsZVl.js)</t>
-        </is>
-      </c>
-      <c r="P3" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+          <t>Pages render</t>
+        </is>
+      </c>
+      <c r="P3" s="17" t="n"/>
       <c r="Q3" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R3" s="18" t="n">
@@ -1872,7 +1868,7 @@
       </c>
       <c r="S3" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T3" s="17" t="inlineStr">
@@ -1961,7 +1957,7 @@
       <c r="P4" s="17" t="n"/>
       <c r="Q4" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R4" s="18" t="n">
@@ -1969,12 +1965,12 @@
       </c>
       <c r="S4" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T4" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U4" s="17" t="inlineStr">
@@ -2058,7 +2054,7 @@
       <c r="P5" s="17" t="n"/>
       <c r="Q5" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R5" s="18" t="n">
@@ -2066,12 +2062,12 @@
       </c>
       <c r="S5" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T5" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U5" s="17" t="inlineStr">
@@ -2148,17 +2144,13 @@
         </is>
       </c>
       <c r="O6" s="17" t="n"/>
-      <c r="P6" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P6" s="17" t="n"/>
       <c r="Q6" s="17" t="n"/>
       <c r="R6" s="18" t="n"/>
       <c r="S6" s="16" t="n"/>
       <c r="T6" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U6" s="17" t="n"/>
@@ -2231,17 +2223,13 @@
         </is>
       </c>
       <c r="O7" s="17" t="n"/>
-      <c r="P7" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P7" s="17" t="n"/>
       <c r="Q7" s="17" t="n"/>
       <c r="R7" s="18" t="n"/>
       <c r="S7" s="16" t="n"/>
       <c r="T7" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U7" s="17" t="n"/>
@@ -2314,17 +2302,13 @@
         </is>
       </c>
       <c r="O8" s="17" t="n"/>
-      <c r="P8" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P8" s="17" t="n"/>
       <c r="Q8" s="17" t="n"/>
       <c r="R8" s="18" t="n"/>
       <c r="S8" s="16" t="n"/>
       <c r="T8" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U8" s="17" t="n"/>
@@ -2397,17 +2381,13 @@
         </is>
       </c>
       <c r="O9" s="17" t="n"/>
-      <c r="P9" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P9" s="17" t="n"/>
       <c r="Q9" s="17" t="n"/>
       <c r="R9" s="18" t="n"/>
       <c r="S9" s="16" t="n"/>
       <c r="T9" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U9" s="17" t="n"/>
@@ -2480,17 +2460,13 @@
         </is>
       </c>
       <c r="O10" s="17" t="n"/>
-      <c r="P10" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P10" s="17" t="n"/>
       <c r="Q10" s="17" t="n"/>
       <c r="R10" s="18" t="n"/>
       <c r="S10" s="16" t="n"/>
       <c r="T10" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U10" s="17" t="n"/>
@@ -2563,17 +2539,13 @@
         </is>
       </c>
       <c r="O11" s="17" t="n"/>
-      <c r="P11" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P11" s="17" t="n"/>
       <c r="Q11" s="17" t="n"/>
       <c r="R11" s="18" t="n"/>
       <c r="S11" s="16" t="n"/>
       <c r="T11" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U11" s="17" t="n"/>
@@ -2646,17 +2618,13 @@
         </is>
       </c>
       <c r="O12" s="17" t="n"/>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P12" s="17" t="n"/>
       <c r="Q12" s="17" t="n"/>
       <c r="R12" s="18" t="n"/>
       <c r="S12" s="16" t="n"/>
       <c r="T12" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U12" s="17" t="n"/>
@@ -2729,17 +2697,13 @@
         </is>
       </c>
       <c r="O13" s="17" t="n"/>
-      <c r="P13" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P13" s="17" t="n"/>
       <c r="Q13" s="17" t="n"/>
       <c r="R13" s="18" t="n"/>
       <c r="S13" s="16" t="n"/>
       <c r="T13" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U13" s="17" t="n"/>
@@ -2812,17 +2776,13 @@
         </is>
       </c>
       <c r="O14" s="17" t="n"/>
-      <c r="P14" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P14" s="17" t="n"/>
       <c r="Q14" s="17" t="n"/>
       <c r="R14" s="18" t="n"/>
       <c r="S14" s="16" t="n"/>
       <c r="T14" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U14" s="17" t="n"/>
@@ -2899,17 +2859,13 @@
         </is>
       </c>
       <c r="O15" s="17" t="n"/>
-      <c r="P15" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P15" s="17" t="n"/>
       <c r="Q15" s="17" t="n"/>
       <c r="R15" s="18" t="n"/>
       <c r="S15" s="16" t="n"/>
       <c r="T15" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U15" s="17" t="n"/>
@@ -2982,17 +2938,13 @@
         </is>
       </c>
       <c r="O16" s="17" t="n"/>
-      <c r="P16" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P16" s="17" t="n"/>
       <c r="Q16" s="17" t="n"/>
       <c r="R16" s="18" t="n"/>
       <c r="S16" s="16" t="n"/>
       <c r="T16" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U16" s="17" t="n"/>
@@ -3065,17 +3017,13 @@
         </is>
       </c>
       <c r="O17" s="17" t="n"/>
-      <c r="P17" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P17" s="17" t="n"/>
       <c r="Q17" s="17" t="n"/>
       <c r="R17" s="18" t="n"/>
       <c r="S17" s="16" t="n"/>
       <c r="T17" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U17" s="17" t="n"/>
@@ -3148,17 +3096,13 @@
         </is>
       </c>
       <c r="O18" s="17" t="n"/>
-      <c r="P18" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P18" s="17" t="n"/>
       <c r="Q18" s="17" t="n"/>
       <c r="R18" s="18" t="n"/>
       <c r="S18" s="16" t="n"/>
       <c r="T18" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U18" s="17" t="n"/>
@@ -3235,17 +3179,13 @@
         </is>
       </c>
       <c r="O19" s="17" t="n"/>
-      <c r="P19" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P19" s="17" t="n"/>
       <c r="Q19" s="17" t="n"/>
       <c r="R19" s="18" t="n"/>
       <c r="S19" s="16" t="n"/>
       <c r="T19" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U19" s="17" t="n"/>
@@ -3318,17 +3258,13 @@
         </is>
       </c>
       <c r="O20" s="17" t="n"/>
-      <c r="P20" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P20" s="17" t="n"/>
       <c r="Q20" s="17" t="n"/>
       <c r="R20" s="18" t="n"/>
       <c r="S20" s="16" t="n"/>
       <c r="T20" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U20" s="17" t="n"/>
@@ -3416,7 +3352,7 @@
       </c>
       <c r="S21" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T21" s="17" t="n"/>
@@ -3494,17 +3430,13 @@
         </is>
       </c>
       <c r="O22" s="17" t="n"/>
-      <c r="P22" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P22" s="17" t="n"/>
       <c r="Q22" s="17" t="n"/>
       <c r="R22" s="18" t="n"/>
       <c r="S22" s="16" t="n"/>
       <c r="T22" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U22" s="17" t="n"/>
@@ -3584,7 +3516,7 @@
       <c r="P23" s="17" t="n"/>
       <c r="Q23" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R23" s="18" t="n">
@@ -3592,12 +3524,12 @@
       </c>
       <c r="S23" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T23" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Used a non-existent email because CUST does not exist yet; Supabase returns the same message for a wrong password</t>
+          <t>Real Chrome (Playwright), no workaround. Used a non-existent email because CUST does not exist yet; Supabase returns the same message for a wrong password</t>
         </is>
       </c>
       <c r="U23" s="17" t="inlineStr">
@@ -3674,17 +3606,13 @@
         </is>
       </c>
       <c r="O24" s="17" t="n"/>
-      <c r="P24" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P24" s="17" t="n"/>
       <c r="Q24" s="17" t="n"/>
       <c r="R24" s="18" t="n"/>
       <c r="S24" s="16" t="n"/>
       <c r="T24" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U24" s="17" t="n"/>
@@ -3764,7 +3692,7 @@
       <c r="P25" s="17" t="n"/>
       <c r="Q25" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R25" s="18" t="n">
@@ -3772,12 +3700,12 @@
       </c>
       <c r="S25" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T25" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). The field is type=email + required, so the browser's own validation fires before the app's 'Enter your email address' and before Supabase; suite expectation corrected</t>
+          <t>Real Chrome (Playwright), no workaround. The field is type=email + required, so the browser's own validation fires before the app's 'Enter your email address' and before Supabase; suite expectation corrected</t>
         </is>
       </c>
       <c r="U25" s="17" t="inlineStr">
@@ -3854,17 +3782,13 @@
         </is>
       </c>
       <c r="O26" s="17" t="n"/>
-      <c r="P26" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P26" s="17" t="n"/>
       <c r="Q26" s="17" t="n"/>
       <c r="R26" s="18" t="n"/>
       <c r="S26" s="16" t="n"/>
       <c r="T26" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U26" s="17" t="n"/>
@@ -3937,17 +3861,13 @@
         </is>
       </c>
       <c r="O27" s="17" t="n"/>
-      <c r="P27" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P27" s="17" t="n"/>
       <c r="Q27" s="17" t="n"/>
       <c r="R27" s="18" t="n"/>
       <c r="S27" s="16" t="n"/>
       <c r="T27" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U27" s="17" t="n"/>
@@ -4020,17 +3940,13 @@
         </is>
       </c>
       <c r="O28" s="17" t="n"/>
-      <c r="P28" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P28" s="17" t="n"/>
       <c r="Q28" s="17" t="n"/>
       <c r="R28" s="18" t="n"/>
       <c r="S28" s="16" t="n"/>
       <c r="T28" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U28" s="17" t="n"/>
@@ -4103,17 +4019,13 @@
         </is>
       </c>
       <c r="O29" s="17" t="n"/>
-      <c r="P29" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P29" s="17" t="n"/>
       <c r="Q29" s="17" t="n"/>
       <c r="R29" s="18" t="n"/>
       <c r="S29" s="16" t="n"/>
       <c r="T29" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U29" s="17" t="n"/>
@@ -4186,17 +4098,13 @@
         </is>
       </c>
       <c r="O30" s="17" t="n"/>
-      <c r="P30" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P30" s="17" t="n"/>
       <c r="Q30" s="17" t="n"/>
       <c r="R30" s="18" t="n"/>
       <c r="S30" s="16" t="n"/>
       <c r="T30" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U30" s="17" t="n"/>
@@ -4269,17 +4177,13 @@
         </is>
       </c>
       <c r="O31" s="17" t="n"/>
-      <c r="P31" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P31" s="17" t="n"/>
       <c r="Q31" s="17" t="n"/>
       <c r="R31" s="18" t="n"/>
       <c r="S31" s="16" t="n"/>
       <c r="T31" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U31" s="17" t="n"/>
@@ -4352,17 +4256,13 @@
         </is>
       </c>
       <c r="O32" s="17" t="n"/>
-      <c r="P32" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P32" s="17" t="n"/>
       <c r="Q32" s="17" t="n"/>
       <c r="R32" s="18" t="n"/>
       <c r="S32" s="16" t="n"/>
       <c r="T32" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U32" s="17" t="n"/>
@@ -4442,7 +4342,7 @@
       <c r="P33" s="17" t="n"/>
       <c r="Q33" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R33" s="18" t="n">
@@ -4450,12 +4350,12 @@
       </c>
       <c r="S33" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T33" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U33" s="17" t="inlineStr">
@@ -4539,7 +4439,7 @@
       <c r="P34" s="17" t="n"/>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R34" s="18" t="n">
@@ -4547,12 +4447,12 @@
       </c>
       <c r="S34" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T34" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U34" s="17" t="inlineStr">
@@ -4629,17 +4529,13 @@
         </is>
       </c>
       <c r="O35" s="17" t="n"/>
-      <c r="P35" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P35" s="17" t="n"/>
       <c r="Q35" s="17" t="n"/>
       <c r="R35" s="18" t="n"/>
       <c r="S35" s="16" t="n"/>
       <c r="T35" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U35" s="17" t="n"/>
@@ -4712,17 +4608,13 @@
         </is>
       </c>
       <c r="O36" s="17" t="n"/>
-      <c r="P36" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P36" s="17" t="n"/>
       <c r="Q36" s="17" t="n"/>
       <c r="R36" s="18" t="n"/>
       <c r="S36" s="16" t="n"/>
       <c r="T36" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U36" s="17" t="n"/>
@@ -4795,17 +4687,13 @@
         </is>
       </c>
       <c r="O37" s="17" t="n"/>
-      <c r="P37" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P37" s="17" t="n"/>
       <c r="Q37" s="17" t="n"/>
       <c r="R37" s="18" t="n"/>
       <c r="S37" s="16" t="n"/>
       <c r="T37" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U37" s="17" t="n"/>
@@ -4878,17 +4766,13 @@
         </is>
       </c>
       <c r="O38" s="17" t="n"/>
-      <c r="P38" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P38" s="17" t="n"/>
       <c r="Q38" s="17" t="n"/>
       <c r="R38" s="18" t="n"/>
       <c r="S38" s="16" t="n"/>
       <c r="T38" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U38" s="17" t="n"/>
@@ -4968,7 +4852,7 @@
       <c r="P39" s="17" t="n"/>
       <c r="Q39" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R39" s="18" t="n">
@@ -4976,12 +4860,12 @@
       </c>
       <c r="S39" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T39" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U39" s="17" t="inlineStr">
@@ -5065,7 +4949,7 @@
       <c r="P40" s="17" t="n"/>
       <c r="Q40" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R40" s="18" t="n">
@@ -5073,12 +4957,12 @@
       </c>
       <c r="S40" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T40" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U40" s="17" t="inlineStr">
@@ -5155,17 +5039,13 @@
         </is>
       </c>
       <c r="O41" s="17" t="n"/>
-      <c r="P41" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P41" s="17" t="n"/>
       <c r="Q41" s="17" t="n"/>
       <c r="R41" s="18" t="n"/>
       <c r="S41" s="16" t="n"/>
       <c r="T41" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U41" s="17" t="n"/>
@@ -5238,17 +5118,13 @@
         </is>
       </c>
       <c r="O42" s="17" t="n"/>
-      <c r="P42" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P42" s="17" t="n"/>
       <c r="Q42" s="17" t="n"/>
       <c r="R42" s="18" t="n"/>
       <c r="S42" s="16" t="n"/>
       <c r="T42" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U42" s="17" t="n"/>
@@ -5321,17 +5197,13 @@
         </is>
       </c>
       <c r="O43" s="17" t="n"/>
-      <c r="P43" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P43" s="17" t="n"/>
       <c r="Q43" s="17" t="n"/>
       <c r="R43" s="18" t="n"/>
       <c r="S43" s="16" t="n"/>
       <c r="T43" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U43" s="17" t="n"/>
@@ -5404,17 +5276,13 @@
         </is>
       </c>
       <c r="O44" s="17" t="n"/>
-      <c r="P44" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P44" s="17" t="n"/>
       <c r="Q44" s="17" t="n"/>
       <c r="R44" s="18" t="n"/>
       <c r="S44" s="16" t="n"/>
       <c r="T44" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U44" s="17" t="n"/>
@@ -5494,7 +5362,7 @@
       <c r="P45" s="17" t="n"/>
       <c r="Q45" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R45" s="18" t="n">
@@ -5502,12 +5370,12 @@
       </c>
       <c r="S45" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T45" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U45" s="17" t="inlineStr">
@@ -5599,7 +5467,7 @@
       </c>
       <c r="Q46" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R46" s="18" t="n">
@@ -5607,12 +5475,12 @@
       </c>
       <c r="S46" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T46" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U46" s="17" t="inlineStr">
@@ -5704,7 +5572,7 @@
       </c>
       <c r="Q47" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R47" s="18" t="n">
@@ -5712,12 +5580,12 @@
       </c>
       <c r="S47" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T47" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U47" s="17" t="inlineStr">
@@ -5801,7 +5669,7 @@
       <c r="P48" s="17" t="n"/>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R48" s="18" t="n">
@@ -5809,12 +5677,12 @@
       </c>
       <c r="S48" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T48" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U48" s="17" t="inlineStr">
@@ -5898,7 +5766,7 @@
       <c r="P49" s="17" t="n"/>
       <c r="Q49" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R49" s="18" t="n">
@@ -5906,12 +5774,12 @@
       </c>
       <c r="S49" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T49" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U49" s="17" t="inlineStr">
@@ -6003,7 +5871,7 @@
       </c>
       <c r="Q50" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R50" s="18" t="n">
@@ -6011,12 +5879,12 @@
       </c>
       <c r="S50" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T50" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Passes as specified; documents the inconsistency with delivery (F-19)</t>
+          <t>Real Chrome (Playwright), no workaround. Passes as specified; documents the inconsistency with delivery (F-19)</t>
         </is>
       </c>
       <c r="U50" s="17" t="inlineStr">
@@ -6093,17 +5961,13 @@
         </is>
       </c>
       <c r="O51" s="17" t="n"/>
-      <c r="P51" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P51" s="17" t="n"/>
       <c r="Q51" s="17" t="n"/>
       <c r="R51" s="18" t="n"/>
       <c r="S51" s="16" t="n"/>
       <c r="T51" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U51" s="17" t="n"/>
@@ -6176,17 +6040,13 @@
         </is>
       </c>
       <c r="O52" s="17" t="n"/>
-      <c r="P52" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P52" s="17" t="n"/>
       <c r="Q52" s="17" t="n"/>
       <c r="R52" s="18" t="n"/>
       <c r="S52" s="16" t="n"/>
       <c r="T52" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U52" s="17" t="n"/>
@@ -6259,17 +6119,13 @@
         </is>
       </c>
       <c r="O53" s="17" t="n"/>
-      <c r="P53" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P53" s="17" t="n"/>
       <c r="Q53" s="17" t="n"/>
       <c r="R53" s="18" t="n"/>
       <c r="S53" s="16" t="n"/>
       <c r="T53" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U53" s="17" t="n"/>
@@ -6365,7 +6221,7 @@
       </c>
       <c r="S54" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T54" s="17" t="inlineStr">
@@ -6447,17 +6303,13 @@
         </is>
       </c>
       <c r="O55" s="17" t="n"/>
-      <c r="P55" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P55" s="17" t="n"/>
       <c r="Q55" s="17" t="n"/>
       <c r="R55" s="18" t="n"/>
       <c r="S55" s="16" t="n"/>
       <c r="T55" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U55" s="17" t="n"/>
@@ -6553,7 +6405,7 @@
       </c>
       <c r="S56" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T56" s="17" t="inlineStr">
@@ -6658,7 +6510,7 @@
       </c>
       <c r="S57" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T57" s="17" t="inlineStr">
@@ -6755,7 +6607,7 @@
       </c>
       <c r="Q58" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R58" s="18" t="n">
@@ -6763,12 +6615,12 @@
       </c>
       <c r="S58" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T58" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U58" s="17" t="inlineStr">
@@ -6868,7 +6720,7 @@
       </c>
       <c r="S59" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T59" s="17" t="inlineStr">
@@ -6973,7 +6825,7 @@
       </c>
       <c r="S60" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T60" s="17" t="inlineStr">
@@ -7062,7 +6914,7 @@
       <c r="P61" s="17" t="n"/>
       <c r="Q61" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R61" s="18" t="n">
@@ -7070,12 +6922,12 @@
       </c>
       <c r="S61" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T61" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U61" s="17" t="inlineStr">
@@ -7159,7 +7011,7 @@
       <c r="P62" s="17" t="n"/>
       <c r="Q62" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R62" s="18" t="n">
@@ -7167,12 +7019,12 @@
       </c>
       <c r="S62" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T62" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Run as guest; the cart does not depend on sign-in</t>
+          <t>Real Chrome (Playwright), no workaround. Run as guest; the cart does not depend on sign-in</t>
         </is>
       </c>
       <c r="U62" s="17" t="inlineStr">
@@ -7256,7 +7108,7 @@
       <c r="P63" s="17" t="n"/>
       <c r="Q63" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R63" s="18" t="n">
@@ -7264,12 +7116,12 @@
       </c>
       <c r="S63" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T63" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U63" s="17" t="inlineStr">
@@ -7353,7 +7205,7 @@
       <c r="P64" s="17" t="n"/>
       <c r="Q64" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R64" s="18" t="n">
@@ -7361,12 +7213,12 @@
       </c>
       <c r="S64" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T64" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U64" s="17" t="inlineStr">
@@ -7443,17 +7295,13 @@
         </is>
       </c>
       <c r="O65" s="17" t="n"/>
-      <c r="P65" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P65" s="17" t="n"/>
       <c r="Q65" s="17" t="n"/>
       <c r="R65" s="18" t="n"/>
       <c r="S65" s="16" t="n"/>
       <c r="T65" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U65" s="17" t="n"/>
@@ -7526,17 +7374,13 @@
         </is>
       </c>
       <c r="O66" s="17" t="n"/>
-      <c r="P66" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P66" s="17" t="n"/>
       <c r="Q66" s="17" t="n"/>
       <c r="R66" s="18" t="n"/>
       <c r="S66" s="16" t="n"/>
       <c r="T66" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U66" s="17" t="n"/>
@@ -7616,7 +7460,7 @@
       <c r="P67" s="17" t="n"/>
       <c r="Q67" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R67" s="18" t="n">
@@ -7624,12 +7468,12 @@
       </c>
       <c r="S67" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T67" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Run as guest</t>
+          <t>Real Chrome (Playwright), no workaround. Run as guest</t>
         </is>
       </c>
       <c r="U67" s="17" t="inlineStr">
@@ -7729,7 +7573,7 @@
       </c>
       <c r="S68" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T68" s="17" t="inlineStr">
@@ -7834,7 +7678,7 @@
       </c>
       <c r="S69" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T69" s="17" t="inlineStr">
@@ -7939,7 +7783,7 @@
       </c>
       <c r="S70" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T70" s="17" t="inlineStr">
@@ -8021,17 +7865,13 @@
         </is>
       </c>
       <c r="O71" s="17" t="n"/>
-      <c r="P71" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P71" s="17" t="n"/>
       <c r="Q71" s="17" t="n"/>
       <c r="R71" s="18" t="n"/>
       <c r="S71" s="16" t="n"/>
       <c r="T71" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U71" s="17" t="n"/>
@@ -8111,7 +7951,7 @@
       <c r="P72" s="17" t="n"/>
       <c r="Q72" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R72" s="18" t="n">
@@ -8119,12 +7959,12 @@
       </c>
       <c r="S72" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T72" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U72" s="17" t="inlineStr">
@@ -8216,7 +8056,7 @@
       </c>
       <c r="Q73" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R73" s="18" t="n">
@@ -8224,12 +8064,12 @@
       </c>
       <c r="S73" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T73" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U73" s="17" t="inlineStr">
@@ -8329,7 +8169,7 @@
       </c>
       <c r="S74" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T74" s="17" t="inlineStr">
@@ -8411,17 +8251,13 @@
         </is>
       </c>
       <c r="O75" s="17" t="n"/>
-      <c r="P75" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P75" s="17" t="n"/>
       <c r="Q75" s="17" t="n"/>
       <c r="R75" s="18" t="n"/>
       <c r="S75" s="16" t="n"/>
       <c r="T75" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U75" s="17" t="n"/>
@@ -8494,17 +8330,13 @@
         </is>
       </c>
       <c r="O76" s="17" t="n"/>
-      <c r="P76" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P76" s="17" t="n"/>
       <c r="Q76" s="17" t="n"/>
       <c r="R76" s="18" t="n"/>
       <c r="S76" s="16" t="n"/>
       <c r="T76" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U76" s="17" t="n"/>
@@ -8577,17 +8409,13 @@
         </is>
       </c>
       <c r="O77" s="17" t="n"/>
-      <c r="P77" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P77" s="17" t="n"/>
       <c r="Q77" s="17" t="n"/>
       <c r="R77" s="18" t="n"/>
       <c r="S77" s="16" t="n"/>
       <c r="T77" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U77" s="17" t="n"/>
@@ -8660,17 +8488,13 @@
         </is>
       </c>
       <c r="O78" s="17" t="n"/>
-      <c r="P78" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P78" s="17" t="n"/>
       <c r="Q78" s="17" t="n"/>
       <c r="R78" s="18" t="n"/>
       <c r="S78" s="16" t="n"/>
       <c r="T78" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U78" s="17" t="n"/>
@@ -8743,17 +8567,13 @@
         </is>
       </c>
       <c r="O79" s="17" t="n"/>
-      <c r="P79" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P79" s="17" t="n"/>
       <c r="Q79" s="17" t="n"/>
       <c r="R79" s="18" t="n"/>
       <c r="S79" s="16" t="n"/>
       <c r="T79" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U79" s="17" t="n"/>
@@ -8849,7 +8669,7 @@
       </c>
       <c r="S80" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T80" s="17" t="inlineStr">
@@ -8931,17 +8751,13 @@
         </is>
       </c>
       <c r="O81" s="17" t="n"/>
-      <c r="P81" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P81" s="17" t="n"/>
       <c r="Q81" s="17" t="n"/>
       <c r="R81" s="18" t="n"/>
       <c r="S81" s="16" t="n"/>
       <c r="T81" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U81" s="17" t="n"/>
@@ -9037,7 +8853,7 @@
       </c>
       <c r="S82" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T82" s="17" t="inlineStr">
@@ -9119,17 +8935,13 @@
         </is>
       </c>
       <c r="O83" s="17" t="n"/>
-      <c r="P83" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P83" s="17" t="n"/>
       <c r="Q83" s="17" t="n"/>
       <c r="R83" s="18" t="n"/>
       <c r="S83" s="16" t="n"/>
       <c r="T83" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U83" s="17" t="n"/>
@@ -9202,17 +9014,13 @@
         </is>
       </c>
       <c r="O84" s="17" t="n"/>
-      <c r="P84" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P84" s="17" t="n"/>
       <c r="Q84" s="17" t="n"/>
       <c r="R84" s="18" t="n"/>
       <c r="S84" s="16" t="n"/>
       <c r="T84" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U84" s="17" t="n"/>
@@ -9308,7 +9116,7 @@
       </c>
       <c r="S85" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T85" s="17" t="inlineStr">
@@ -9390,17 +9198,13 @@
         </is>
       </c>
       <c r="O86" s="17" t="n"/>
-      <c r="P86" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P86" s="17" t="n"/>
       <c r="Q86" s="17" t="n"/>
       <c r="R86" s="18" t="n"/>
       <c r="S86" s="16" t="n"/>
       <c r="T86" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U86" s="17" t="n"/>
@@ -9496,7 +9300,7 @@
       </c>
       <c r="S87" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T87" s="17" t="inlineStr">
@@ -9601,7 +9405,7 @@
       </c>
       <c r="S88" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T88" s="17" t="inlineStr">
@@ -9688,17 +9492,17 @@
       </c>
       <c r="O89" s="17" t="inlineStr">
         <is>
-          <t>Form is open to guests (no sign-in prompt: true). Real submit from the site → HTTP 403 'This website origin is not allowed.'; page shows: 'We couldn't send your inquiry. Unexpected token 'T', "This websi"... is not vali'</t>
+          <t>Signed out, no sign-in prompt (true); submit → HTTP 200 in 10.0 s; page shows: 'Thank you for your inquiry. Thank you for contacting Capitol Restaurant. Our team will follow up with you shortly.'. Accepted from a guest, contrary to REQ-INQ-001</t>
         </is>
       </c>
       <c r="P89" s="17" t="inlineStr">
         <is>
-          <t>F-07, F-33</t>
+          <t>F-07</t>
         </is>
       </c>
       <c r="Q89" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R89" s="18" t="n">
@@ -9706,12 +9510,12 @@
       </c>
       <c r="S89" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T89" s="17" t="inlineStr">
         <is>
-          <t>Page loaded with the workaround; the POST kept its real Origin header, so this is what every customer gets. No row was created</t>
+          <t>Real Chrome (Playwright), no workaround. Created one inquiry named 'QA Test (please ignore)' on production; AI reply in 10.0 s (covers the reply-time part of IQ-07). The reply shown is the code fallback text, not an AI answer, so the Gemini call likely failed; check Railway logs</t>
         </is>
       </c>
       <c r="U89" s="17" t="inlineStr">
@@ -9795,7 +9599,7 @@
       <c r="P90" s="17" t="n"/>
       <c r="Q90" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R90" s="18" t="n">
@@ -9803,12 +9607,12 @@
       </c>
       <c r="S90" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T90" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Run as guest</t>
+          <t>Real Chrome (Playwright), no workaround. Run as guest</t>
         </is>
       </c>
       <c r="U90" s="17" t="inlineStr">
@@ -9900,7 +9704,7 @@
       </c>
       <c r="S91" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T91" s="17" t="n"/>
@@ -9974,24 +9778,42 @@
       </c>
       <c r="N92" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O92" s="17" t="n"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O92" s="17" t="inlineStr">
+        <is>
+          <t>HTTP 202; page shows: 'Your request was sent to our staff. Your request was recorded, but the staff alert could not be delivered. Please call us to follow up.'. The request is saved (202), but the customer is told to call because the staff alert failed</t>
+        </is>
+      </c>
       <c r="P92" s="17" t="inlineStr">
         <is>
-          <t>F-33</t>
-        </is>
-      </c>
-      <c r="Q92" s="17" t="n"/>
-      <c r="R92" s="18" t="n"/>
-      <c r="S92" s="16" t="n"/>
+          <t>F-34</t>
+        </is>
+      </c>
+      <c r="Q92" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome, guest)</t>
+        </is>
+      </c>
+      <c r="R92" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S92" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+        </is>
+      </c>
       <c r="T92" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
-        </is>
-      </c>
-      <c r="U92" s="17" t="n"/>
+          <t>Real Chrome (Playwright), no workaround. Run as guest (the form does not need sign-in). Created one 'Manual Order Request' named 'QA Test (please ignore)'. DB type/status (Manual Order Request / New) follow webhook.js:845-847; confirm in IQ-05 with FOH</t>
+        </is>
+      </c>
+      <c r="U92" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -10065,17 +9887,13 @@
         </is>
       </c>
       <c r="O93" s="17" t="n"/>
-      <c r="P93" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P93" s="17" t="n"/>
       <c r="Q93" s="17" t="n"/>
       <c r="R93" s="18" t="n"/>
       <c r="S93" s="16" t="n"/>
       <c r="T93" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U93" s="17" t="n"/>
@@ -10148,17 +9966,13 @@
         </is>
       </c>
       <c r="O94" s="17" t="n"/>
-      <c r="P94" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P94" s="17" t="n"/>
       <c r="Q94" s="17" t="n"/>
       <c r="R94" s="18" t="n"/>
       <c r="S94" s="16" t="n"/>
       <c r="T94" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U94" s="17" t="n"/>
@@ -10236,7 +10050,7 @@
       </c>
       <c r="O95" s="17" t="inlineStr">
         <is>
-          <t>Server saves non-order web inquiries with status Resolved (webhook.js:827), not New</t>
+          <t>Server saves non-order web inquiries with status Resolved (webhook.js:847), not New. Reply time measured live in IQ-01: 10 s</t>
         </is>
       </c>
       <c r="P95" s="17" t="inlineStr">
@@ -10254,7 +10068,7 @@
       </c>
       <c r="S95" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T95" s="17" t="inlineStr">
@@ -10336,17 +10150,13 @@
         </is>
       </c>
       <c r="O96" s="17" t="n"/>
-      <c r="P96" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P96" s="17" t="n"/>
       <c r="Q96" s="17" t="n"/>
       <c r="R96" s="18" t="n"/>
       <c r="S96" s="16" t="n"/>
       <c r="T96" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U96" s="17" t="n"/>
@@ -10419,17 +10229,13 @@
         </is>
       </c>
       <c r="O97" s="17" t="n"/>
-      <c r="P97" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P97" s="17" t="n"/>
       <c r="Q97" s="17" t="n"/>
       <c r="R97" s="18" t="n"/>
       <c r="S97" s="16" t="n"/>
       <c r="T97" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U97" s="17" t="n"/>
@@ -10502,17 +10308,13 @@
         </is>
       </c>
       <c r="O98" s="17" t="n"/>
-      <c r="P98" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P98" s="17" t="n"/>
       <c r="Q98" s="17" t="n"/>
       <c r="R98" s="18" t="n"/>
       <c r="S98" s="16" t="n"/>
       <c r="T98" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U98" s="17" t="n"/>
@@ -10585,17 +10387,13 @@
         </is>
       </c>
       <c r="O99" s="17" t="n"/>
-      <c r="P99" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P99" s="17" t="n"/>
       <c r="Q99" s="17" t="n"/>
       <c r="R99" s="18" t="n"/>
       <c r="S99" s="16" t="n"/>
       <c r="T99" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U99" s="17" t="n"/>
@@ -10668,17 +10466,13 @@
         </is>
       </c>
       <c r="O100" s="17" t="n"/>
-      <c r="P100" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P100" s="17" t="n"/>
       <c r="Q100" s="17" t="n"/>
       <c r="R100" s="18" t="n"/>
       <c r="S100" s="16" t="n"/>
       <c r="T100" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U100" s="17" t="n"/>
@@ -10751,17 +10545,13 @@
         </is>
       </c>
       <c r="O101" s="17" t="n"/>
-      <c r="P101" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P101" s="17" t="n"/>
       <c r="Q101" s="17" t="n"/>
       <c r="R101" s="18" t="n"/>
       <c r="S101" s="16" t="n"/>
       <c r="T101" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U101" s="17" t="n"/>
@@ -10834,17 +10624,13 @@
         </is>
       </c>
       <c r="O102" s="17" t="n"/>
-      <c r="P102" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P102" s="17" t="n"/>
       <c r="Q102" s="17" t="n"/>
       <c r="R102" s="18" t="n"/>
       <c r="S102" s="16" t="n"/>
       <c r="T102" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U102" s="17" t="n"/>
@@ -10917,17 +10703,13 @@
         </is>
       </c>
       <c r="O103" s="17" t="n"/>
-      <c r="P103" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P103" s="17" t="n"/>
       <c r="Q103" s="17" t="n"/>
       <c r="R103" s="18" t="n"/>
       <c r="S103" s="16" t="n"/>
       <c r="T103" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U103" s="17" t="n"/>
@@ -11023,7 +10805,7 @@
       </c>
       <c r="S104" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T104" s="17" t="inlineStr">
@@ -11120,7 +10902,7 @@
       </c>
       <c r="S105" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T105" s="17" t="inlineStr">
@@ -11221,7 +11003,7 @@
       </c>
       <c r="S106" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T106" s="17" t="inlineStr">
@@ -11318,7 +11100,7 @@
       </c>
       <c r="S107" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T107" s="17" t="n"/>
@@ -11396,17 +11178,13 @@
         </is>
       </c>
       <c r="O108" s="17" t="n"/>
-      <c r="P108" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P108" s="17" t="n"/>
       <c r="Q108" s="17" t="n"/>
       <c r="R108" s="18" t="n"/>
       <c r="S108" s="16" t="n"/>
       <c r="T108" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U108" s="17" t="n"/>
@@ -11479,17 +11257,13 @@
         </is>
       </c>
       <c r="O109" s="17" t="n"/>
-      <c r="P109" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P109" s="17" t="n"/>
       <c r="Q109" s="17" t="n"/>
       <c r="R109" s="18" t="n"/>
       <c r="S109" s="16" t="n"/>
       <c r="T109" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U109" s="17" t="n"/>
@@ -11562,17 +11336,13 @@
         </is>
       </c>
       <c r="O110" s="17" t="n"/>
-      <c r="P110" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P110" s="17" t="n"/>
       <c r="Q110" s="17" t="n"/>
       <c r="R110" s="18" t="n"/>
       <c r="S110" s="16" t="n"/>
       <c r="T110" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U110" s="17" t="n"/>
@@ -11645,17 +11415,13 @@
         </is>
       </c>
       <c r="O111" s="17" t="n"/>
-      <c r="P111" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P111" s="17" t="n"/>
       <c r="Q111" s="17" t="n"/>
       <c r="R111" s="18" t="n"/>
       <c r="S111" s="16" t="n"/>
       <c r="T111" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U111" s="17" t="n"/>
@@ -11751,7 +11517,7 @@
       </c>
       <c r="S112" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T112" s="17" t="inlineStr">
@@ -11833,17 +11599,13 @@
         </is>
       </c>
       <c r="O113" s="17" t="n"/>
-      <c r="P113" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P113" s="17" t="n"/>
       <c r="Q113" s="17" t="n"/>
       <c r="R113" s="18" t="n"/>
       <c r="S113" s="16" t="n"/>
       <c r="T113" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U113" s="17" t="n"/>
@@ -11916,17 +11678,13 @@
         </is>
       </c>
       <c r="O114" s="17" t="n"/>
-      <c r="P114" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P114" s="17" t="n"/>
       <c r="Q114" s="17" t="n"/>
       <c r="R114" s="18" t="n"/>
       <c r="S114" s="16" t="n"/>
       <c r="T114" s="17" t="inlineStr">
         <is>
-          <t>Needs a Facebook test user messaging the Page Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs a Facebook test user messaging the Page</t>
         </is>
       </c>
       <c r="U114" s="17" t="n"/>
@@ -12006,7 +11764,7 @@
       <c r="P115" s="17" t="n"/>
       <c r="Q115" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R115" s="18" t="n">
@@ -12014,12 +11772,12 @@
       </c>
       <c r="S115" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T115" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header)</t>
+          <t>Real Chrome (Playwright), no workaround</t>
         </is>
       </c>
       <c r="U115" s="17" t="inlineStr">
@@ -12096,17 +11854,13 @@
         </is>
       </c>
       <c r="O116" s="17" t="n"/>
-      <c r="P116" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P116" s="17" t="n"/>
       <c r="Q116" s="17" t="n"/>
       <c r="R116" s="18" t="n"/>
       <c r="S116" s="16" t="n"/>
       <c r="T116" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U116" s="17" t="n"/>
@@ -12179,17 +11933,13 @@
         </is>
       </c>
       <c r="O117" s="17" t="n"/>
-      <c r="P117" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P117" s="17" t="n"/>
       <c r="Q117" s="17" t="n"/>
       <c r="R117" s="18" t="n"/>
       <c r="S117" s="16" t="n"/>
       <c r="T117" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U117" s="17" t="n"/>
@@ -12262,17 +12012,13 @@
         </is>
       </c>
       <c r="O118" s="17" t="n"/>
-      <c r="P118" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P118" s="17" t="n"/>
       <c r="Q118" s="17" t="n"/>
       <c r="R118" s="18" t="n"/>
       <c r="S118" s="16" t="n"/>
       <c r="T118" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U118" s="17" t="n"/>
@@ -12345,17 +12091,13 @@
         </is>
       </c>
       <c r="O119" s="17" t="n"/>
-      <c r="P119" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P119" s="17" t="n"/>
       <c r="Q119" s="17" t="n"/>
       <c r="R119" s="18" t="n"/>
       <c r="S119" s="16" t="n"/>
       <c r="T119" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U119" s="17" t="n"/>
@@ -12428,17 +12170,13 @@
         </is>
       </c>
       <c r="O120" s="17" t="n"/>
-      <c r="P120" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P120" s="17" t="n"/>
       <c r="Q120" s="17" t="n"/>
       <c r="R120" s="18" t="n"/>
       <c r="S120" s="16" t="n"/>
       <c r="T120" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U120" s="17" t="n"/>
@@ -12511,17 +12249,13 @@
         </is>
       </c>
       <c r="O121" s="17" t="n"/>
-      <c r="P121" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P121" s="17" t="n"/>
       <c r="Q121" s="17" t="n"/>
       <c r="R121" s="18" t="n"/>
       <c r="S121" s="16" t="n"/>
       <c r="T121" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U121" s="17" t="n"/>
@@ -12594,17 +12328,13 @@
         </is>
       </c>
       <c r="O122" s="17" t="n"/>
-      <c r="P122" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P122" s="17" t="n"/>
       <c r="Q122" s="17" t="n"/>
       <c r="R122" s="18" t="n"/>
       <c r="S122" s="16" t="n"/>
       <c r="T122" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U122" s="17" t="n"/>
@@ -12677,17 +12407,13 @@
         </is>
       </c>
       <c r="O123" s="17" t="n"/>
-      <c r="P123" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P123" s="17" t="n"/>
       <c r="Q123" s="17" t="n"/>
       <c r="R123" s="18" t="n"/>
       <c r="S123" s="16" t="n"/>
       <c r="T123" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U123" s="17" t="n"/>
@@ -12760,17 +12486,13 @@
         </is>
       </c>
       <c r="O124" s="17" t="n"/>
-      <c r="P124" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P124" s="17" t="n"/>
       <c r="Q124" s="17" t="n"/>
       <c r="R124" s="18" t="n"/>
       <c r="S124" s="16" t="n"/>
       <c r="T124" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U124" s="17" t="n"/>
@@ -12843,17 +12565,13 @@
         </is>
       </c>
       <c r="O125" s="17" t="n"/>
-      <c r="P125" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P125" s="17" t="n"/>
       <c r="Q125" s="17" t="n"/>
       <c r="R125" s="18" t="n"/>
       <c r="S125" s="16" t="n"/>
       <c r="T125" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U125" s="17" t="n"/>
@@ -12926,17 +12644,13 @@
         </is>
       </c>
       <c r="O126" s="17" t="n"/>
-      <c r="P126" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P126" s="17" t="n"/>
       <c r="Q126" s="17" t="n"/>
       <c r="R126" s="18" t="n"/>
       <c r="S126" s="16" t="n"/>
       <c r="T126" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U126" s="17" t="n"/>
@@ -13009,17 +12723,13 @@
         </is>
       </c>
       <c r="O127" s="17" t="n"/>
-      <c r="P127" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P127" s="17" t="n"/>
       <c r="Q127" s="17" t="n"/>
       <c r="R127" s="18" t="n"/>
       <c r="S127" s="16" t="n"/>
       <c r="T127" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U127" s="17" t="n"/>
@@ -13092,17 +12802,13 @@
         </is>
       </c>
       <c r="O128" s="17" t="n"/>
-      <c r="P128" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P128" s="17" t="n"/>
       <c r="Q128" s="17" t="n"/>
       <c r="R128" s="18" t="n"/>
       <c r="S128" s="16" t="n"/>
       <c r="T128" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U128" s="17" t="n"/>
@@ -13198,7 +12904,7 @@
       </c>
       <c r="S129" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T129" s="17" t="inlineStr">
@@ -13303,7 +13009,7 @@
       </c>
       <c r="S130" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 010694c</t>
+          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
         </is>
       </c>
       <c r="T130" s="17" t="inlineStr">
@@ -13381,22 +13087,18 @@
       </c>
       <c r="N131" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O131" s="17" t="inlineStr">
         <is>
-          <t>Cannot time a real page load: in Chrome without the workaround the page is blank (F-33). curl on broadband: HTML 0.48–0.55 s, JS bundle 1.04 MB in 0.93 s</t>
-        </is>
-      </c>
-      <c r="P131" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+          <t>Time to load event + first page heading visible, cache disabled. Broadband (unthrottled): / 2.2 s, /delivery/order 1.3 s, /function-rooms/reserve 1.5 s | 4G (Lighthouse mobile profile: 150 ms RTT, 1.6 Mbps down, 750 kbps up): / 3.3 s, /delivery/order 2.9 s, /function-rooms/reserve 3.0 s</t>
+        </is>
+      </c>
+      <c r="P131" s="17" t="n"/>
       <c r="Q131" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R131" s="18" t="n">
@@ -13404,12 +13106,12 @@
       </c>
       <c r="S131" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T131" s="17" t="inlineStr">
         <is>
-          <t>Re-run with DevTools Fast 4G once F-33 is fixed</t>
+          <t>Real Chrome. Used the Lighthouse mobile 4G profile, which is slower than DevTools "Fast 4G", so it is the stricter check</t>
         </is>
       </c>
       <c r="U131" s="17" t="inlineStr">
@@ -13486,17 +13188,13 @@
         </is>
       </c>
       <c r="O132" s="17" t="n"/>
-      <c r="P132" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P132" s="17" t="n"/>
       <c r="Q132" s="17" t="n"/>
       <c r="R132" s="18" t="n"/>
       <c r="S132" s="16" t="n"/>
       <c r="T132" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U132" s="17" t="n"/>
@@ -13576,7 +13274,7 @@
       <c r="P133" s="17" t="n"/>
       <c r="Q133" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, guest)</t>
+          <t>Claude (Playwright, real Chrome, guest)</t>
         </is>
       </c>
       <c r="R133" s="18" t="n">
@@ -13584,12 +13282,12 @@
       </c>
       <c r="S133" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
         </is>
       </c>
       <c r="T133" s="17" t="inlineStr">
         <is>
-          <t>Run with the F-33 workaround (test browser drops the same-site Origin header). Layout part done as guest; the step count needs a signed-in booking (S-07, S-09)</t>
+          <t>Real Chrome (Playwright), no workaround. Layout part done as guest; the step count needs a signed-in booking (S-07, S-09)</t>
         </is>
       </c>
       <c r="U133" s="17" t="inlineStr">
@@ -13666,17 +13364,13 @@
         </is>
       </c>
       <c r="O134" s="17" t="n"/>
-      <c r="P134" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P134" s="17" t="n"/>
       <c r="Q134" s="17" t="n"/>
       <c r="R134" s="18" t="n"/>
       <c r="S134" s="16" t="n"/>
       <c r="T134" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U134" s="17" t="n"/>
@@ -13749,17 +13443,13 @@
         </is>
       </c>
       <c r="O135" s="17" t="n"/>
-      <c r="P135" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P135" s="17" t="n"/>
       <c r="Q135" s="17" t="n"/>
       <c r="R135" s="18" t="n"/>
       <c r="S135" s="16" t="n"/>
       <c r="T135" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U135" s="17" t="n"/>
@@ -13832,17 +13522,13 @@
         </is>
       </c>
       <c r="O136" s="17" t="n"/>
-      <c r="P136" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P136" s="17" t="n"/>
       <c r="Q136" s="17" t="n"/>
       <c r="R136" s="18" t="n"/>
       <c r="S136" s="16" t="n"/>
       <c r="T136" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U136" s="17" t="n"/>
@@ -13915,17 +13601,13 @@
         </is>
       </c>
       <c r="O137" s="17" t="n"/>
-      <c r="P137" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P137" s="17" t="n"/>
       <c r="Q137" s="17" t="n"/>
       <c r="R137" s="18" t="n"/>
       <c r="S137" s="16" t="n"/>
       <c r="T137" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U137" s="17" t="n"/>
@@ -13998,17 +13680,13 @@
         </is>
       </c>
       <c r="O138" s="17" t="n"/>
-      <c r="P138" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P138" s="17" t="n"/>
       <c r="Q138" s="17" t="n"/>
       <c r="R138" s="18" t="n"/>
       <c r="S138" s="16" t="n"/>
       <c r="T138" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U138" s="17" t="n"/>
@@ -14081,17 +13759,13 @@
         </is>
       </c>
       <c r="O139" s="17" t="n"/>
-      <c r="P139" s="17" t="inlineStr">
-        <is>
-          <t>F-33</t>
-        </is>
-      </c>
+      <c r="P139" s="17" t="n"/>
       <c r="Q139" s="17" t="n"/>
       <c r="R139" s="18" t="n"/>
       <c r="S139" s="16" t="n"/>
       <c r="T139" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet Also blocked for real users by F-33 (site blank in browsers).</t>
+          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
         </is>
       </c>
       <c r="U139" s="17" t="n"/>
@@ -14179,7 +13853,7 @@
       </c>
       <c r="S140" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T140" s="17" t="n"/>
@@ -14272,7 +13946,7 @@
       </c>
       <c r="S141" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T141" s="17" t="inlineStr">
@@ -14369,7 +14043,7 @@
       </c>
       <c r="S142" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T142" s="17" t="inlineStr">
@@ -15359,7 +15033,7 @@
       </c>
       <c r="S154" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T154" s="17" t="n"/>
@@ -15452,7 +15126,7 @@
       </c>
       <c r="S155" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main); repo db90eeb</t>
+          <t>Live (Railway main @ 8990106)</t>
         </is>
       </c>
       <c r="T155" s="17" t="n"/>
@@ -15910,7 +15584,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-07, F-34</t>
         </is>
       </c>
       <c r="H6" s="9">
@@ -17980,7 +17654,7 @@
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>F-26, F-27</t>
+          <t>F-26, F-27, F-34</t>
         </is>
       </c>
       <c r="H36" s="9">
@@ -18397,7 +18071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18812,7 +18486,7 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Inquiries.tsx, webhook.js:820-828</t>
+          <t>Inquiries.tsx, webhook.js:840-848</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -19024,7 +18698,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>webhook.js:525, :950-953</t>
+          <t>webhook.js:545, :959-961</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -19383,7 +19057,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>webhook.js:75, :975. Confirmed live 2026-10-07: unsigned POST returns 200, and the verify token test-agent is accepted, so VERIFY_TOKEN is not set on Railway</t>
+          <t>webhook.js:95, :995. Confirmed live 2026-10-07: unsigned POST returns 200, and the verify token test-agent is accepted, so VERIFY_TOKEN is not set on Railway</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -20161,7 +19835,7 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>The live site is blank in every browser. The server's origin guard rejects the site's own origin, so the JS and CSS (loaded with an Origin header because Vite marks them crossorigin) return 403 "This website origin is not allowed.". The same guard rejects the inquiry form's POST, and the page then shows customers a raw parse error ("Unexpected token 'T'…"). Fix: add https://capitolrestaurant.up.railway.app to FRONTEND_ORIGINS on Railway, or let same-origin requests through the guard</t>
+          <t>The live site is blank in every browser. The server's origin guard rejects the site's own origin, so the JS and CSS (loaded with an Origin header because Vite marks them crossorigin) return 403 "This website origin is not allowed.". The same guard rejects the inquiry form's POST, and the page then shows customers a raw parse error ("Unexpected token 'T'…"). Fix: add https://capitolrestaurant.up.railway.app to FRONTEND_ORIGINS on Railway, or let same-origin requests through the guard. Fixed in 8990106 (same-origin requests now pass the guard); verified live 2026-10-07 (S-02 pass, IQ-01 submits)</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
@@ -20190,32 +19864,85 @@
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="J34" s="17" t="n"/>
       <c r="K34" s="18" t="n"/>
       <c r="L34" s="17" t="inlineStr">
         <is>
-          <t>Found 2026-10-07 by the Playwright run (S-02). Live site blank for all browser users; urgent before go-live</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+          <t>Found 2026-10-07 (S-02). Fixed in 8990106 (same-origin requests allowed by the guard). Verified live 2026-10-07: S-02 passes in real Chrome, IQ-01/IQ-04 submit, cross-site origin still gets 403 (DB-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>F-34</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Manual order requests never alert staff: the server posts to STAFF_NOTIFICATION_WEBHOOK_URL, which is unset or failing on Railway, so the customer sees "Your request was recorded, but the staff alert could not be delivered. Please call us to follow up." (HTTP 202). The request still appears on /operations, but nobody is notified</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>webhook.js:186-211 (notifyStaff), :863 (202 response); live 2026-10-07</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>§3.1 Real-time Alert Notifications, §4.1.2-2</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>IF-UI-01, SEQ-INQ</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>IQ-04, IQ-05</t>
+        </is>
+      </c>
+      <c r="H35" s="9">
+        <f>COUNTIFS('Test Cases'!$P$2:$P$155,"*"&amp;A35&amp;"*",'Test Cases'!$N$2:$N$155,"Fail")</f>
+        <v/>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="17" t="inlineStr">
+        <is>
+          <t>Found 2026-10-07 (IQ-04). Fix: set STAFF_NOTIFICATION_WEBHOOK_URL on Railway (or replace the alert channel), then re-run IQ-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Failed Cases counts test cases whose Defect / Finding ID contains this finding and whose Status is Fail. Note: 'F-1' style partial matches are avoided because IDs are two digits (F-01 … F-31).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
+  <autoFilter ref="A1:L35"/>
   <mergeCells count="1">
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I2:I35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,In progress,Fixed,Verified,Won't fix,SRS to update"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/qa/Capitol-RTM.xlsx
+++ b/docs/qa/Capitol-RTM.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$U$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RTM'!$A$1:$O$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Findings'!$A$1:$L$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Findings'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>main @ 8990106 (010694c + the F-33 origin-guard fix)</t>
+          <t>main @ 7652f11</t>
         </is>
       </c>
     </row>
@@ -1441,11 +1441,11 @@
         </is>
       </c>
       <c r="B34" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A34,Findings!$B$2:$B$35,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A34,Findings!$B$2:$B$38,"P1*")</f>
         <v/>
       </c>
       <c r="C34" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A34,Findings!$B$2:$B$35,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A34,Findings!$B$2:$B$38,"P2*")</f>
         <v/>
       </c>
       <c r="D34" s="9">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A35,Findings!$B$2:$B$35,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A35,Findings!$B$2:$B$38,"P1*")</f>
         <v/>
       </c>
       <c r="C35" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A35,Findings!$B$2:$B$35,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A35,Findings!$B$2:$B$38,"P2*")</f>
         <v/>
       </c>
       <c r="D35" s="9">
@@ -1479,11 +1479,11 @@
         </is>
       </c>
       <c r="B36" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A36,Findings!$B$2:$B$35,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A36,Findings!$B$2:$B$38,"P1*")</f>
         <v/>
       </c>
       <c r="C36" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A36,Findings!$B$2:$B$35,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A36,Findings!$B$2:$B$38,"P2*")</f>
         <v/>
       </c>
       <c r="D36" s="9">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A37,Findings!$B$2:$B$35,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A37,Findings!$B$2:$B$38,"P1*")</f>
         <v/>
       </c>
       <c r="C37" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A37,Findings!$B$2:$B$35,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A37,Findings!$B$2:$B$38,"P2*")</f>
         <v/>
       </c>
       <c r="D37" s="9">
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="B38" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A38,Findings!$B$2:$B$35,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A38,Findings!$B$2:$B$38,"P1*")</f>
         <v/>
       </c>
       <c r="C38" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A38,Findings!$B$2:$B$35,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A38,Findings!$B$2:$B$38,"P2*")</f>
         <v/>
       </c>
       <c r="D38" s="9">
@@ -1536,11 +1536,11 @@
         </is>
       </c>
       <c r="B39" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A39,Findings!$B$2:$B$35,"P1*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A39,Findings!$B$2:$B$38,"P1*")</f>
         <v/>
       </c>
       <c r="C39" s="9">
-        <f>COUNTIFS(Findings!$I$2:$I$35,A39,Findings!$B$2:$B$35,"P2*")</f>
+        <f>COUNTIFS(Findings!$I$2:$I$38,A39,Findings!$B$2:$B$38,"P2*")</f>
         <v/>
       </c>
       <c r="D39" s="9">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="S2" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T2" s="17" t="n"/>
@@ -1860,7 +1860,7 @@
       <c r="P3" s="17" t="n"/>
       <c r="Q3" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R3" s="18" t="n">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="S3" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T3" s="17" t="inlineStr">
@@ -1957,7 +1957,7 @@
       <c r="P4" s="17" t="n"/>
       <c r="Q4" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R4" s="18" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="S4" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T4" s="17" t="inlineStr">
@@ -2054,7 +2054,7 @@
       <c r="P5" s="17" t="n"/>
       <c r="Q5" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R5" s="18" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="S5" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T5" s="17" t="inlineStr">
@@ -2150,7 +2150,7 @@
       <c r="S6" s="16" t="n"/>
       <c r="T6" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U6" s="17" t="n"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>The confirmation screen shows the tracking reference CAP-1xxx. Note it as REF-D.</t>
+          <t>The confirmation screen shows the tracking reference CAP-1xxx (generated by the database sequence). Note it as REF-D.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -2229,7 +2229,7 @@
       <c r="S7" s="16" t="n"/>
       <c r="T7" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U7" s="17" t="n"/>
@@ -2308,7 +2308,7 @@
       <c r="S8" s="16" t="n"/>
       <c r="T8" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U8" s="17" t="n"/>
@@ -2387,7 +2387,7 @@
       <c r="S9" s="16" t="n"/>
       <c r="T9" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U9" s="17" t="n"/>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>Go to /function-rooms/reserve. Fill Name, 09171234567, email, Guests 20, Birthday Celebration. Click Check Availability →, pick FR at 6:00 PM, and confirm.</t>
+          <t>Go to /function-rooms/reserve. Fill Name, 09171234567, email, Function Room A, Guests 20, Birthday Celebration. Click Check Availability →, pick FR at 6:00 PM, and confirm.</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -2466,7 +2466,7 @@
       <c r="S10" s="16" t="n"/>
       <c r="T10" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U10" s="17" t="n"/>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>My bookings lists REF-B, the packed booking and REF-F, all Pending. The delivery tracker with REF-D shows Preparing.</t>
+          <t>My bookings lists REF-B, the packed booking and REF-F, all Pending. The delivery tracker with REF-D shows Pending Confirmation.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -2545,7 +2545,7 @@
       <c r="S11" s="16" t="n"/>
       <c r="T11" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U11" s="17" t="n"/>
@@ -2624,7 +2624,7 @@
       <c r="S12" s="16" t="n"/>
       <c r="T12" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U12" s="17" t="n"/>
@@ -2693,20 +2693,38 @@
       </c>
       <c r="N13" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="inlineStr">
+        <is>
+          <t>Lands on /operations; nav: Operations, Delivery, Inquiry Bot, Menu Items, Function Room Bookings, Catering Bookings</t>
+        </is>
+      </c>
       <c r="P13" s="17" t="n"/>
-      <c r="Q13" s="17" t="n"/>
-      <c r="R13" s="18" t="n"/>
-      <c r="S13" s="16" t="n"/>
+      <c r="Q13" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R13" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S13" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T13" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U13" s="17" t="n"/>
+          <t>Real Chrome (Playwright). 'Delivery' in the staff nav is the staff delivery page (/delivery/staff), not the customer menu</t>
+        </is>
+      </c>
+      <c r="U13" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -2772,20 +2790,38 @@
       </c>
       <c r="N14" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>Same flow as OP-02 on a QA booking (REF-F needs a customer): saved as Confirmed, timeline entry added, Function pending 6 → 5</t>
+        </is>
+      </c>
       <c r="P14" s="17" t="n"/>
-      <c r="Q14" s="17" t="n"/>
-      <c r="R14" s="18" t="n"/>
-      <c r="S14" s="16" t="n"/>
+      <c r="Q14" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R14" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S14" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T14" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U14" s="17" t="n"/>
+          <t>Real Chrome (Playwright); QA booking used instead of REF-F</t>
+        </is>
+      </c>
+      <c r="U14" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -2820,7 +2856,7 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>The inquiry is listed (status Resolved because it was auto-answered; see F-07).</t>
+          <t>The inquiry is listed (status Resolved because it was auto-answered; see F-07). Since d9610bc there is no Inquiries panel → F-37.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2840,7 +2876,7 @@
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-07, F-37</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -2855,20 +2891,42 @@
       </c>
       <c r="N15" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="n"/>
-      <c r="P15" s="17" t="n"/>
-      <c r="Q15" s="17" t="n"/>
-      <c r="R15" s="18" t="n"/>
-      <c r="S15" s="16" t="n"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>The web inquiry from the form is not listed anywhere in the staff UI</t>
+        </is>
+      </c>
+      <c r="P15" s="17" t="inlineStr">
+        <is>
+          <t>F-37</t>
+        </is>
+      </c>
+      <c r="Q15" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R15" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S15" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T15" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U15" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U15" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -2898,12 +2956,12 @@
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Go to /delivery/staff. On REF-D set Assign rider = Jun Reyes and Change status = Ready for pickup.</t>
+          <t>Go to /delivery/staff. On REF-D set Assign rider = Jun Reyes and Change status = Ready for pickup → Save.</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Both changes save instantly. The Jun Reyes rider card shows 1 active delivery.</t>
+          <t>The rider saves at once; the status saves on Save (since 7652f11). The Jun Reyes rider card shows 1 active delivery.</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -2934,20 +2992,38 @@
       </c>
       <c r="N16" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>QA order: rider rider-01, status Ready for pickup (status needed an explicit Save: true); rider card: 'Jun Reyes 0917 442 1188'</t>
+        </is>
+      </c>
       <c r="P16" s="17" t="n"/>
-      <c r="Q16" s="17" t="n"/>
-      <c r="R16" s="18" t="n"/>
-      <c r="S16" s="16" t="n"/>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R16" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S16" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T16" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U16" s="17" t="n"/>
+          <t>Real Chrome (Playwright); QA order instead of REF-D. Status now saves with an explicit Save button (7652f11), not instantly</t>
+        </is>
+      </c>
+      <c r="U16" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -3013,20 +3089,42 @@
       </c>
       <c r="N17" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>Loads with chips Needs reply
+0 · Requests
+0 · Resolved
+12 · All
+12; Needs reply pressed: null; message 'No questions waiting'</t>
+        </is>
+      </c>
       <c r="P17" s="17" t="n"/>
-      <c r="Q17" s="17" t="n"/>
-      <c r="R17" s="18" t="n"/>
-      <c r="S17" s="16" t="n"/>
+      <c r="Q17" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R17" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S17" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T17" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U17" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U17" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -3092,20 +3190,38 @@
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O18" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O18" s="17" t="inlineStr">
+        <is>
+          <t>On /delivery/rider; QA order (Ready for pickup) shows Start delivery: true</t>
+        </is>
+      </c>
       <c r="P18" s="17" t="n"/>
-      <c r="Q18" s="17" t="n"/>
-      <c r="R18" s="18" t="n"/>
-      <c r="S18" s="16" t="n"/>
+      <c r="Q18" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R18" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S18" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T18" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U18" s="17" t="n"/>
+          <t>Real Chrome (Playwright); QA order instead of REF-D. Header shows 'Delivery Rider', not 'Jun Reyes', because of the account's display name (F-13)</t>
+        </is>
+      </c>
+      <c r="U18" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -3175,20 +3291,38 @@
       </c>
       <c r="N19" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O19" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="inlineStr">
+        <is>
+          <t>Start delivery → Out for delivery; Mark delivered → Delivered (saved to DB); /operations → /delivery/rider</t>
+        </is>
+      </c>
       <c r="P19" s="17" t="n"/>
-      <c r="Q19" s="17" t="n"/>
-      <c r="R19" s="18" t="n"/>
-      <c r="S19" s="16" t="n"/>
+      <c r="Q19" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R19" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S19" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T19" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U19" s="17" t="n"/>
+          <t>Real Chrome (Playwright); QA order</t>
+        </is>
+      </c>
+      <c r="U19" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -3264,7 +3398,7 @@
       <c r="S20" s="16" t="n"/>
       <c r="T20" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U20" s="17" t="n"/>
@@ -3352,7 +3486,7 @@
       </c>
       <c r="S21" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T21" s="17" t="n"/>
@@ -3436,7 +3570,7 @@
       <c r="S22" s="16" t="n"/>
       <c r="T22" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U22" s="17" t="n"/>
@@ -3516,7 +3650,7 @@
       <c r="P23" s="17" t="n"/>
       <c r="Q23" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R23" s="18" t="n">
@@ -3524,7 +3658,7 @@
       </c>
       <c r="S23" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T23" s="17" t="inlineStr">
@@ -3612,7 +3746,7 @@
       <c r="S24" s="16" t="n"/>
       <c r="T24" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U24" s="17" t="n"/>
@@ -3692,7 +3826,7 @@
       <c r="P25" s="17" t="n"/>
       <c r="Q25" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R25" s="18" t="n">
@@ -3700,7 +3834,7 @@
       </c>
       <c r="S25" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T25" s="17" t="inlineStr">
@@ -3778,20 +3912,38 @@
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O26" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O26" s="17" t="inlineStr">
+        <is>
+          <t>Log In from /catering → /operations</t>
+        </is>
+      </c>
       <c r="P26" s="17" t="n"/>
-      <c r="Q26" s="17" t="n"/>
-      <c r="R26" s="18" t="n"/>
-      <c r="S26" s="16" t="n"/>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R26" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S26" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T26" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U26" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U26" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -3857,20 +4009,38 @@
       </c>
       <c r="N27" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O27" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O27" s="17" t="inlineStr">
+        <is>
+          <t>Log In from / → /delivery/rider</t>
+        </is>
+      </c>
       <c r="P27" s="17" t="n"/>
-      <c r="Q27" s="17" t="n"/>
-      <c r="R27" s="18" t="n"/>
-      <c r="S27" s="16" t="n"/>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R27" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S27" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T27" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U27" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U27" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -3936,20 +4106,38 @@
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O28" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O28" s="17" t="inlineStr">
+        <is>
+          <t>Confirm dialog 'Are you sure?': true; Cancel keeps session: true; Sign Out → /; /profile prompt: true</t>
+        </is>
+      </c>
       <c r="P28" s="17" t="n"/>
-      <c r="Q28" s="17" t="n"/>
-      <c r="R28" s="18" t="n"/>
-      <c r="S28" s="16" t="n"/>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R28" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S28" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T28" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U28" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Run as FOH (no customer account); the logout flow is the same for every role</t>
+        </is>
+      </c>
+      <c r="U28" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -4015,20 +4203,38 @@
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O29" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O29" s="17" t="inlineStr">
+        <is>
+          <t>After hard reload: /operations; paths seen: /operations</t>
+        </is>
+      </c>
       <c r="P29" s="17" t="n"/>
-      <c r="Q29" s="17" t="n"/>
-      <c r="R29" s="18" t="n"/>
-      <c r="S29" s="16" t="n"/>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R29" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S29" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T29" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U29" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U29" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -4104,7 +4310,7 @@
       <c r="S30" s="16" t="n"/>
       <c r="T30" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U30" s="17" t="n"/>
@@ -4183,7 +4389,7 @@
       <c r="S31" s="16" t="n"/>
       <c r="T31" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U31" s="17" t="n"/>
@@ -4262,7 +4468,7 @@
       <c r="S32" s="16" t="n"/>
       <c r="T32" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U32" s="17" t="n"/>
@@ -4342,7 +4548,7 @@
       <c r="P33" s="17" t="n"/>
       <c r="Q33" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R33" s="18" t="n">
@@ -4350,7 +4556,7 @@
       </c>
       <c r="S33" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T33" s="17" t="inlineStr">
@@ -4439,7 +4645,7 @@
       <c r="P34" s="17" t="n"/>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R34" s="18" t="n">
@@ -4447,7 +4653,7 @@
       </c>
       <c r="S34" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T34" s="17" t="inlineStr">
@@ -4535,7 +4741,7 @@
       <c r="S35" s="16" t="n"/>
       <c r="T35" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U35" s="17" t="n"/>
@@ -4614,7 +4820,7 @@
       <c r="S36" s="16" t="n"/>
       <c r="T36" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U36" s="17" t="n"/>
@@ -4693,7 +4899,7 @@
       <c r="S37" s="16" t="n"/>
       <c r="T37" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U37" s="17" t="n"/>
@@ -4772,7 +4978,7 @@
       <c r="S38" s="16" t="n"/>
       <c r="T38" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U38" s="17" t="n"/>
@@ -4852,7 +5058,7 @@
       <c r="P39" s="17" t="n"/>
       <c r="Q39" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R39" s="18" t="n">
@@ -4860,7 +5066,7 @@
       </c>
       <c r="S39" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T39" s="17" t="inlineStr">
@@ -4949,7 +5155,7 @@
       <c r="P40" s="17" t="n"/>
       <c r="Q40" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R40" s="18" t="n">
@@ -4957,7 +5163,7 @@
       </c>
       <c r="S40" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T40" s="17" t="inlineStr">
@@ -4999,12 +5205,12 @@
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>Both pick 10:00 AM. CUST confirms first, then CUST-B confirms</t>
+          <t>Both pick date COL (any time; availability is per date since e9b5e7c). CUST confirms first, then CUST-B confirms</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>CUST succeeds. CUST-B gets "That time was just booked. Choose another available time." and the 10:00 AM option becomes disabled</t>
+          <t>CUST succeeds. CUST-B gets "That date was just booked. Choose another available date." and COL is crossed out on the calendar</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -5045,7 +5251,7 @@
       <c r="S41" s="16" t="n"/>
       <c r="T41" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U41" s="17" t="n"/>
@@ -5073,17 +5279,17 @@
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>A buffet booking exists at BUF 12:00 PM</t>
+          <t>A delivered buffet booking exists on BUF</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>Packed booking at BUF 12:00 PM</t>
+          <t>Packed booking on BUF</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
         <is>
-          <t>Succeeds: buffet and packed have separate slot inventories (kind is part of the unique key)</t>
+          <t>Succeeds: buffet and packed have separate slot inventories (the delivered-catering pool is per kind and date)</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -5124,7 +5330,7 @@
       <c r="S42" s="16" t="n"/>
       <c r="T42" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U42" s="17" t="n"/>
@@ -5196,17 +5402,35 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O43" s="17" t="n"/>
+      <c r="O43" s="17" t="inlineStr">
+        <is>
+          <t>Staff half: Special requests '&lt;script&gt;alert(1)&lt;/script&gt;' shown as plain text, JS alerts: 0. Customer half (name '&lt;script&gt;' rejected on the buffet form) needs a customer account</t>
+        </is>
+      </c>
       <c r="P43" s="17" t="n"/>
-      <c r="Q43" s="17" t="n"/>
-      <c r="R43" s="18" t="n"/>
-      <c r="S43" s="16" t="n"/>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R43" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S43" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T43" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U43" s="17" t="n"/>
+          <t>Real Chrome (Playwright); staff half passes</t>
+        </is>
+      </c>
+      <c r="U43" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -5282,7 +5506,7 @@
       <c r="S44" s="16" t="n"/>
       <c r="T44" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U44" s="17" t="n"/>
@@ -5356,13 +5580,13 @@
       </c>
       <c r="O45" s="17" t="inlineStr">
         <is>
-          <t>5 errors: Letters only, min. 3 characters (e.g. Juan dela Cruz) / Enter a valid PH mobile number (e.g. 09XX XXX XXXX) / Enter a valid email address (e.g. juan@example.com) / Enter a whole-number guest count / Please select an even; calendar/sign-in opened: false</t>
+          <t>5 errors: Letters only, min. 3 characters (e.g. Juan dela Cruz) / Enter a valid PH mobile number (e.g. 09XX XXX XXXX) / Enter a valid email address (e.g. juan@example.com) / Minimum 10 guests required / Please select an event type; calendar/sign-in opened: false</t>
         </is>
       </c>
       <c r="P45" s="17" t="n"/>
       <c r="Q45" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R45" s="18" t="n">
@@ -5370,7 +5594,7 @@
       </c>
       <c r="S45" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T45" s="17" t="inlineStr">
@@ -5452,22 +5676,18 @@
       </c>
       <c r="N46" s="16" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O46" s="17" t="inlineStr">
         <is>
-          <t>9: accepted</t>
-        </is>
-      </c>
-      <c r="P46" s="17" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
+          <t>9: rejected (Minimum 10 guests required)</t>
+        </is>
+      </c>
+      <c r="P46" s="17" t="n"/>
       <c r="Q46" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R46" s="18" t="n">
@@ -5475,7 +5695,7 @@
       </c>
       <c r="S46" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T46" s="17" t="inlineStr">
@@ -5557,22 +5777,18 @@
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O47" s="17" t="inlineStr">
         <is>
-          <t>31: rejected (This room holds up to 30 guests); 50: rejected (This room holds up to 30 guests)</t>
-        </is>
-      </c>
-      <c r="P47" s="17" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
+          <t>31: accepted; 50: accepted; 51: rejected (Each room holds up to 50 guests)</t>
+        </is>
+      </c>
+      <c r="P47" s="17" t="n"/>
       <c r="Q47" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R47" s="18" t="n">
@@ -5580,7 +5796,7 @@
       </c>
       <c r="S47" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T47" s="17" t="inlineStr">
@@ -5669,7 +5885,7 @@
       <c r="P48" s="17" t="n"/>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R48" s="18" t="n">
@@ -5677,7 +5893,7 @@
       </c>
       <c r="S48" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T48" s="17" t="inlineStr">
@@ -5766,7 +5982,7 @@
       <c r="P49" s="17" t="n"/>
       <c r="Q49" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R49" s="18" t="n">
@@ -5774,7 +5990,7 @@
       </c>
       <c r="S49" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T49" s="17" t="inlineStr">
@@ -5871,7 +6087,7 @@
       </c>
       <c r="Q50" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R50" s="18" t="n">
@@ -5879,7 +6095,7 @@
       </c>
       <c r="S50" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T50" s="17" t="inlineStr">
@@ -5967,7 +6183,7 @@
       <c r="S51" s="16" t="n"/>
       <c r="T51" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U51" s="17" t="n"/>
@@ -6000,12 +6216,12 @@
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>Both pick 2:00 PM. Confirm in A, then in B within 5 s</t>
+          <t>Both pick Function Room A on COL (any time). Confirm in A, then in B within 5 s</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>A succeeds. B gets "That time was just booked…". In B, without a refresh, 2:00 PM is greyed out (Realtime)</t>
+          <t>A succeeds. B gets "That date was just booked…". In B, without a refresh, COL is crossed out for Room A (Realtime)</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -6046,7 +6262,7 @@
       <c r="S52" s="16" t="n"/>
       <c r="T52" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U52" s="17" t="n"/>
@@ -6074,7 +6290,7 @@
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>All 22 slots of a date taken (do it on staging, or reuse the DB-08 script)</t>
+          <t>A date already has an active booking for Room A</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr">
@@ -6084,7 +6300,7 @@
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>That date is shown as reserved/disabled</t>
+          <t>That date is crossed out for Room A and still open for Room B</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -6125,7 +6341,7 @@
       <c r="S53" s="16" t="n"/>
       <c r="T53" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U53" s="17" t="n"/>
@@ -6221,7 +6437,7 @@
       </c>
       <c r="S54" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T54" s="17" t="inlineStr">
@@ -6299,20 +6515,38 @@
       </c>
       <c r="N55" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O55" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O55" s="17" t="inlineStr">
+        <is>
+          <t>FOH cancelled the QA booking in Operations; new booking for Room A on the same date → 201</t>
+        </is>
+      </c>
       <c r="P55" s="17" t="n"/>
-      <c r="Q55" s="17" t="n"/>
-      <c r="R55" s="18" t="n"/>
-      <c r="S55" s="16" t="n"/>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R55" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S55" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T55" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U55" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Second booking made through the API as Manager (no CUST-B account)</t>
+        </is>
+      </c>
+      <c r="U55" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -6405,7 +6639,7 @@
       </c>
       <c r="S56" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T56" s="17" t="inlineStr">
@@ -6492,7 +6726,7 @@
       </c>
       <c r="O57" s="17" t="inlineStr">
         <is>
-          <t>No blockout UI: reserved_dates is only read (select + realtime), never written, in the deployed bundle</t>
+          <t>Block-out controls on /operations and /operations/function-bookings: 0, 0</t>
         </is>
       </c>
       <c r="P57" s="17" t="inlineStr">
@@ -6502,7 +6736,7 @@
       </c>
       <c r="Q57" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R57" s="18" t="n">
@@ -6510,17 +6744,17 @@
       </c>
       <c r="S57" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T57" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Real Chrome (Playwright)</t>
         </is>
       </c>
       <c r="U57" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6841,7 @@
       </c>
       <c r="Q58" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R58" s="18" t="n">
@@ -6615,7 +6849,7 @@
       </c>
       <c r="S58" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T58" s="17" t="inlineStr">
@@ -6662,7 +6896,7 @@
       </c>
       <c r="G59" s="15" t="inlineStr">
         <is>
-          <t>SRS: the customer chooses a duration; the status is Pending Deposit until paid; collisions show "Already Reserved". App: no duration (fixed slot); status Pending; message "That time was just booked…" → F-28</t>
+          <t>SRS: the customer chooses a duration; the status is Pending Deposit until paid; collisions show "Already Reserved". App: no duration (fixed slot); status Pending; message "That date was just booked…" → F-28</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -6702,7 +6936,7 @@
       </c>
       <c r="O59" s="17" t="inlineStr">
         <is>
-          <t>No duration field; statuses are Pending/Confirmed/Completed/Cancelled (no 'Pending Deposit'); collision text is 'That time was just booked…' (no 'Already Reserved')</t>
+          <t>No duration field; statuses are Pending/Confirmed/Completed/Cancelled (no 'Pending Deposit'); collision text is 'That date was just booked…' (no 'Already Reserved')</t>
         </is>
       </c>
       <c r="P59" s="17" t="inlineStr">
@@ -6720,7 +6954,7 @@
       </c>
       <c r="S59" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T59" s="17" t="inlineStr">
@@ -6825,7 +7059,7 @@
       </c>
       <c r="S60" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T60" s="17" t="inlineStr">
@@ -6914,7 +7148,7 @@
       <c r="P61" s="17" t="n"/>
       <c r="Q61" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R61" s="18" t="n">
@@ -6922,7 +7156,7 @@
       </c>
       <c r="S61" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T61" s="17" t="inlineStr">
@@ -7011,7 +7245,7 @@
       <c r="P62" s="17" t="n"/>
       <c r="Q62" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R62" s="18" t="n">
@@ -7019,7 +7253,7 @@
       </c>
       <c r="S62" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T62" s="17" t="inlineStr">
@@ -7108,7 +7342,7 @@
       <c r="P63" s="17" t="n"/>
       <c r="Q63" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R63" s="18" t="n">
@@ -7116,7 +7350,7 @@
       </c>
       <c r="S63" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T63" s="17" t="inlineStr">
@@ -7205,7 +7439,7 @@
       <c r="P64" s="17" t="n"/>
       <c r="Q64" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R64" s="18" t="n">
@@ -7213,7 +7447,7 @@
       </c>
       <c r="S64" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T64" s="17" t="inlineStr">
@@ -7301,7 +7535,7 @@
       <c r="S65" s="16" t="n"/>
       <c r="T65" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U65" s="17" t="n"/>
@@ -7380,7 +7614,7 @@
       <c r="S66" s="16" t="n"/>
       <c r="T66" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U66" s="17" t="n"/>
@@ -7460,7 +7694,7 @@
       <c r="P67" s="17" t="n"/>
       <c r="Q67" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R67" s="18" t="n">
@@ -7468,7 +7702,7 @@
       </c>
       <c r="S67" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T67" s="17" t="inlineStr">
@@ -7550,42 +7784,20 @@
       </c>
       <c r="N68" s="16" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="O68" s="17" t="inlineStr">
-        <is>
-          <t>Orders are saved to browser localStorage only; the deployed bundle never queries delivery_orders</t>
-        </is>
-      </c>
-      <c r="P68" s="17" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="Q68" s="17" t="inlineStr">
-        <is>
-          <t>Claude (inspection)</t>
-        </is>
-      </c>
-      <c r="R68" s="18" t="n">
-        <v>46302</v>
-      </c>
-      <c r="S68" s="16" t="inlineStr">
-        <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
-        </is>
-      </c>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O68" s="17" t="n"/>
+      <c r="P68" s="17" t="n"/>
+      <c r="Q68" s="17" t="n"/>
+      <c r="R68" s="18" t="n"/>
+      <c r="S68" s="16" t="n"/>
       <c r="T68" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
-        </is>
-      </c>
-      <c r="U68" s="17" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
+        </is>
+      </c>
+      <c r="U68" s="17" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -7655,42 +7867,20 @@
       </c>
       <c r="N69" s="16" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="O69" s="17" t="inlineStr">
-        <is>
-          <t>Reference is CAP-${1050 + local order count}; two clean browsers both produce CAP-1050</t>
-        </is>
-      </c>
-      <c r="P69" s="17" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="Q69" s="17" t="inlineStr">
-        <is>
-          <t>Claude (inspection)</t>
-        </is>
-      </c>
-      <c r="R69" s="18" t="n">
-        <v>46302</v>
-      </c>
-      <c r="S69" s="16" t="inlineStr">
-        <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
-        </is>
-      </c>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O69" s="17" t="n"/>
+      <c r="P69" s="17" t="n"/>
+      <c r="Q69" s="17" t="n"/>
+      <c r="R69" s="18" t="n"/>
+      <c r="S69" s="16" t="n"/>
       <c r="T69" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
-        </is>
-      </c>
-      <c r="U69" s="17" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
+        </is>
+      </c>
+      <c r="U69" s="17" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -7783,7 +7973,7 @@
       </c>
       <c r="S70" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T70" s="17" t="inlineStr">
@@ -7871,7 +8061,7 @@
       <c r="S71" s="16" t="n"/>
       <c r="T71" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U71" s="17" t="n"/>
@@ -7951,7 +8141,7 @@
       <c r="P72" s="17" t="n"/>
       <c r="Q72" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R72" s="18" t="n">
@@ -7959,7 +8149,7 @@
       </c>
       <c r="S72" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T72" s="17" t="inlineStr">
@@ -8056,7 +8246,7 @@
       </c>
       <c r="Q73" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R73" s="18" t="n">
@@ -8064,7 +8254,7 @@
       </c>
       <c r="S73" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T73" s="17" t="inlineStr">
@@ -8169,7 +8359,7 @@
       </c>
       <c r="S74" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T74" s="17" t="inlineStr">
@@ -8247,20 +8437,38 @@
       </c>
       <c r="N75" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O75" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O75" s="17" t="inlineStr">
+        <is>
+          <t>Preparing chip 2; rows shown 2; all Preparing: true</t>
+        </is>
+      </c>
       <c r="P75" s="17" t="n"/>
-      <c r="Q75" s="17" t="n"/>
-      <c r="R75" s="18" t="n"/>
-      <c r="S75" s="16" t="n"/>
+      <c r="Q75" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R75" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S75" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T75" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U75" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U75" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -8329,17 +8537,35 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O76" s="17" t="n"/>
+      <c r="O76" s="17" t="inlineStr">
+        <is>
+          <t>Staff half works: status saved to the database (Preparing). Customer-tracker half needs a customer account</t>
+        </is>
+      </c>
       <c r="P76" s="17" t="n"/>
-      <c r="Q76" s="17" t="n"/>
-      <c r="R76" s="18" t="n"/>
-      <c r="S76" s="16" t="n"/>
+      <c r="Q76" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R76" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S76" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T76" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U76" s="17" t="n"/>
+          <t>Real Chrome (Playwright); QA order</t>
+        </is>
+      </c>
+      <c r="U76" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -8405,20 +8631,38 @@
       </c>
       <c r="N77" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O77" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O77" s="17" t="inlineStr">
+        <is>
+          <t>Duplicate 'Jun Reyes' → message shown: true</t>
+        </is>
+      </c>
       <c r="P77" s="17" t="n"/>
-      <c r="Q77" s="17" t="n"/>
-      <c r="R77" s="18" t="n"/>
-      <c r="S77" s="16" t="n"/>
+      <c r="Q77" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R77" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S77" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T77" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U77" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Riders are stored in this browser only</t>
+        </is>
+      </c>
+      <c r="U77" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
@@ -8484,20 +8728,38 @@
       </c>
       <c r="N78" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O78" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O78" s="17" t="inlineStr">
+        <is>
+          <t>After deleting Ana Lim the QA order shows 'Unassigned' (DB rider_id: rider-1791354804365)</t>
+        </is>
+      </c>
       <c r="P78" s="17" t="n"/>
-      <c r="Q78" s="17" t="n"/>
-      <c r="R78" s="18" t="n"/>
-      <c r="S78" s="16" t="n"/>
+      <c r="Q78" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R78" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S78" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T78" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U78" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U78" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -8563,20 +8825,38 @@
       </c>
       <c r="N79" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O79" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O79" s="17" t="inlineStr">
+        <is>
+          <t>Signed out, same browser: on /delivery/order; other chips present: true; Kabayo chip shown: false</t>
+        </is>
+      </c>
       <c r="P79" s="17" t="n"/>
-      <c r="Q79" s="17" t="n"/>
-      <c r="R79" s="18" t="n"/>
-      <c r="S79" s="16" t="n"/>
+      <c r="Q79" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R79" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S79" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T79" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U79" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Checked as a guest in the same browser instead of CUST</t>
+        </is>
+      </c>
+      <c r="U79" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -8651,7 +8931,7 @@
       </c>
       <c r="O80" s="17" t="inlineStr">
         <is>
-          <t>Menu manager edits are stored in localStorage only, so BrB never sees them</t>
+          <t>A second, fresh browser still shows the Kabayo category: true</t>
         </is>
       </c>
       <c r="P80" s="17" t="inlineStr">
@@ -8661,7 +8941,7 @@
       </c>
       <c r="Q80" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R80" s="18" t="n">
@@ -8669,17 +8949,17 @@
       </c>
       <c r="S80" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T80" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Real Chrome (Playwright)</t>
         </is>
       </c>
       <c r="U80" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -8747,20 +9027,38 @@
       </c>
       <c r="N81" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O81" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O81" s="17" t="inlineStr">
+        <is>
+          <t>Price 0 → modal still open: true; item added: false; message: 'PRICE (₱)'</t>
+        </is>
+      </c>
       <c r="P81" s="17" t="n"/>
-      <c r="Q81" s="17" t="n"/>
-      <c r="R81" s="18" t="n"/>
-      <c r="S81" s="16" t="n"/>
+      <c r="Q81" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R81" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S81" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T81" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U81" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Menu edits are stored in this browser only</t>
+        </is>
+      </c>
+      <c r="U81" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
@@ -8835,7 +9133,7 @@
       </c>
       <c r="O82" s="17" t="inlineStr">
         <is>
-          <t>/delivery/items is in front_of_house's allowed routes and the menu manager has no role check, so FOH has full edit access</t>
+          <t>FOH on /delivery/items: Add item 1, Edit buttons 93, Delete buttons 93</t>
         </is>
       </c>
       <c r="P82" s="17" t="inlineStr">
@@ -8845,7 +9143,7 @@
       </c>
       <c r="Q82" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R82" s="18" t="n">
@@ -8853,17 +9151,17 @@
       </c>
       <c r="S82" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T82" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Real Chrome (Playwright)</t>
         </is>
       </c>
       <c r="U82" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -8931,20 +9229,38 @@
       </c>
       <c r="N83" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O83" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O83" s="17" t="inlineStr">
+        <is>
+          <t>QA order (Preparing) listed: true; action buttons: 0</t>
+        </is>
+      </c>
       <c r="P83" s="17" t="n"/>
-      <c r="Q83" s="17" t="n"/>
-      <c r="R83" s="18" t="n"/>
-      <c r="S83" s="16" t="n"/>
+      <c r="Q83" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R83" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S83" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T83" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U83" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U83" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -9010,20 +9326,38 @@
       </c>
       <c r="N84" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O84" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O84" s="17" t="inlineStr">
+        <is>
+          <t>chip / rows: Out for delivery 1/1, Delivered 1/1</t>
+        </is>
+      </c>
       <c r="P84" s="17" t="n"/>
-      <c r="Q84" s="17" t="n"/>
-      <c r="R84" s="18" t="n"/>
-      <c r="S84" s="16" t="n"/>
+      <c r="Q84" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R84" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S84" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T84" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U84" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U84" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -9098,7 +9432,7 @@
       </c>
       <c r="O85" s="17" t="inlineStr">
         <is>
-          <t>Rider page matches by display name and falls back to the first rider (riders[0]) when there is no match</t>
+          <t>Account display name 'Delivery Rider' matches no rider record; header 'SINCE 1940 · PASAY CITY Catering Function Rooms Delivery Del'; page shows Jun Reyes's orders (QA order for rider-01 visible: true)</t>
         </is>
       </c>
       <c r="P85" s="17" t="inlineStr">
@@ -9108,7 +9442,7 @@
       </c>
       <c r="Q85" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R85" s="18" t="n">
@@ -9116,17 +9450,17 @@
       </c>
       <c r="S85" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T85" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Real Chrome (Playwright)</t>
         </is>
       </c>
       <c r="U85" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -9194,20 +9528,38 @@
       </c>
       <c r="N86" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O86" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O86" s="17" t="inlineStr">
+        <is>
+          <t>With no orders for the resolved rider: 0 rows; message 'No deliveries assigned yet. New assignments from the team will appear here.'</t>
+        </is>
+      </c>
       <c r="P86" s="17" t="n"/>
-      <c r="Q86" s="17" t="n"/>
-      <c r="R86" s="18" t="n"/>
-      <c r="S86" s="16" t="n"/>
+      <c r="Q86" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R86" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S86" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T86" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U86" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Cleared this browser's sample orders and unassigned the QA order to create the precondition</t>
+        </is>
+      </c>
+      <c r="U86" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -9282,7 +9634,7 @@
       </c>
       <c r="O87" s="17" t="inlineStr">
         <is>
-          <t>Rider actions: Ready for pickup → Start delivery (Out for delivery) → Mark delivered</t>
+          <t>Rider actions offered at Ready for pickup: Start delivery; the SRS allows only setting Delivered</t>
         </is>
       </c>
       <c r="P87" s="17" t="inlineStr">
@@ -9292,7 +9644,7 @@
       </c>
       <c r="Q87" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R87" s="18" t="n">
@@ -9300,17 +9652,17 @@
       </c>
       <c r="S87" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T87" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Real Chrome (Playwright)</t>
         </is>
       </c>
       <c r="U87" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9739,7 @@
       </c>
       <c r="O88" s="17" t="inlineStr">
         <is>
-          <t>No audio code in the bundle; /delivery/staff has no polling or storage listener, so new orders need a reload</t>
+          <t>No audio code in the bundle (no chime). Live refresh now exists: /delivery/staff subscribes to delivery_orders since d9610bc</t>
         </is>
       </c>
       <c r="P88" s="17" t="inlineStr">
@@ -9405,7 +9757,7 @@
       </c>
       <c r="S88" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T88" s="17" t="inlineStr">
@@ -9502,7 +9854,7 @@
       </c>
       <c r="Q89" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R89" s="18" t="n">
@@ -9510,12 +9862,12 @@
       </c>
       <c r="S89" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T89" s="17" t="inlineStr">
         <is>
-          <t>Real Chrome (Playwright), no workaround. Created one inquiry named 'QA Test (please ignore)' on production; AI reply in 10.0 s (covers the reply-time part of IQ-07). The reply shown is the code fallback text, not an AI answer, so the Gemini call likely failed; check Railway logs</t>
+          <t>Real Chrome (Playwright), no workaround. Created one inquiry named 'QA Test (please ignore)' on production; AI reply in 10.0 s (covers the reply-time part of IQ-07). The reply shown is the code fallback text, not an AI answer, so the Gemini call likely failed; check Railway logs. Run on 8990106; the inquiry page and server code are unchanged in 7652f11, so it was not re-submitted</t>
         </is>
       </c>
       <c r="U89" s="17" t="inlineStr">
@@ -9599,7 +9951,7 @@
       <c r="P90" s="17" t="n"/>
       <c r="Q90" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R90" s="18" t="n">
@@ -9607,7 +9959,7 @@
       </c>
       <c r="S90" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T90" s="17" t="inlineStr">
@@ -9704,7 +10056,7 @@
       </c>
       <c r="S91" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T91" s="17" t="n"/>
@@ -9783,7 +10135,7 @@
       </c>
       <c r="O92" s="17" t="inlineStr">
         <is>
-          <t>HTTP 202; page shows: 'Your request was sent to our staff. Your request was recorded, but the staff alert could not be delivered. Please call us to follow up.'. The request is saved (202), but the customer is told to call because the staff alert failed</t>
+          <t>HTTP 202; page shows: 'Your request was sent to our staff. Your request was recorded, but the staff alert could not be delivered. Please call us to follow up.'</t>
         </is>
       </c>
       <c r="P92" s="17" t="inlineStr">
@@ -9793,7 +10145,7 @@
       </c>
       <c r="Q92" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R92" s="18" t="n">
@@ -9801,7 +10153,7 @@
       </c>
       <c r="S92" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T92" s="17" t="inlineStr">
@@ -9843,12 +10195,12 @@
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>/operations → Inquiries panel (wait ≤ 10 s, no refresh)</t>
+          <t>/operations and /inquiry-bot: find the IQ-04 request (wait ≤ 10 s, no refresh)</t>
         </is>
       </c>
       <c r="G93" s="15" t="inlineStr">
         <is>
-          <t>The row appears with the Manual reply needed badge. New inquiries is incremented. (Arrives by 10-s polling; the SRS asks for push → F-27)</t>
+          <t>The row appears with the Manual reply needed badge. Open inquiries is incremented. Since d9610bc the Inquiries panel is gone and the Inquiry Bot lists Messenger only → F-37. (Arrives by 10-s polling; the SRS asks for push → F-27)</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
@@ -9868,7 +10220,7 @@
       </c>
       <c r="K93" s="9" t="inlineStr">
         <is>
-          <t>F-27</t>
+          <t>F-27, F-37</t>
         </is>
       </c>
       <c r="L93" s="9" t="inlineStr">
@@ -9883,20 +10235,42 @@
       </c>
       <c r="N93" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O93" s="17" t="n"/>
-      <c r="P93" s="17" t="n"/>
-      <c r="Q93" s="17" t="n"/>
-      <c r="R93" s="18" t="n"/>
-      <c r="S93" s="16" t="n"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O93" s="17" t="inlineStr">
+        <is>
+          <t>Operations has no Inquiries panel (0) and no 'Manual reply needed' badge (0); 'Open inquiries' card = 2. The QA Manual Order Request is not listed in Operations (0) or the Inquiry Bot (0), which loads Messenger inquiries only</t>
+        </is>
+      </c>
+      <c r="P93" s="17" t="inlineStr">
+        <is>
+          <t>F-37, F-34</t>
+        </is>
+      </c>
+      <c r="Q93" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R93" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S93" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T93" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U93" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U93" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -9931,7 +10305,7 @@
       </c>
       <c r="G94" s="15" t="inlineStr">
         <is>
-          <t>The status persists after the refresh. The badge disappears after leaving New</t>
+          <t>The status persists after the refresh. The badge disappears after leaving New. Not possible for web inquiries since d9610bc → F-37</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
@@ -9949,10 +10323,14 @@
           <t>REQ-INQ-004, SEQ-INQ</t>
         </is>
       </c>
-      <c r="K94" s="9" t="inlineStr"/>
+      <c r="K94" s="9" t="inlineStr">
+        <is>
+          <t>F-37</t>
+        </is>
+      </c>
       <c r="L94" s="9" t="inlineStr">
         <is>
-          <t>Expected to pass</t>
+          <t>Known deviation</t>
         </is>
       </c>
       <c r="M94" s="9" t="inlineStr">
@@ -9962,20 +10340,42 @@
       </c>
       <c r="N94" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O94" s="17" t="n"/>
-      <c r="P94" s="17" t="n"/>
-      <c r="Q94" s="17" t="n"/>
-      <c r="R94" s="18" t="n"/>
-      <c r="S94" s="16" t="n"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O94" s="17" t="inlineStr">
+        <is>
+          <t>No UI anywhere lists web inquiries, so their status cannot be changed (Operations panel removed in 7652f11; Inquiry Bot filters to Messenger)</t>
+        </is>
+      </c>
+      <c r="P94" s="17" t="inlineStr">
+        <is>
+          <t>F-37</t>
+        </is>
+      </c>
+      <c r="Q94" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S94" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T94" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U94" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U94" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
@@ -10068,7 +10468,7 @@
       </c>
       <c r="S95" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T95" s="17" t="inlineStr">
@@ -10156,7 +10556,7 @@
       <c r="S96" s="16" t="n"/>
       <c r="T96" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U96" s="17" t="n"/>
@@ -10304,20 +10704,38 @@
       </c>
       <c r="N98" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O98" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O98" s="17" t="inlineStr">
+        <is>
+          <t>chip count / cards shown: Needs reply 0/0, Requests 0/0, Resolved 12/12, All 12/12</t>
+        </is>
+      </c>
       <c r="P98" s="17" t="n"/>
-      <c r="Q98" s="17" t="n"/>
-      <c r="R98" s="18" t="n"/>
-      <c r="S98" s="16" t="n"/>
+      <c r="Q98" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S98" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T98" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U98" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Counted by reply buttons, one per card</t>
+        </is>
+      </c>
+      <c r="U98" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
@@ -10383,20 +10801,38 @@
       </c>
       <c r="N99" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O99" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O99" s="17" t="inlineStr">
+        <is>
+          <t>Search 'Messenger User' → 12 matching cards; nonsense search → empty message: true</t>
+        </is>
+      </c>
       <c r="P99" s="17" t="n"/>
-      <c r="Q99" s="17" t="n"/>
-      <c r="R99" s="18" t="n"/>
-      <c r="S99" s="16" t="n"/>
+      <c r="Q99" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R99" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S99" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T99" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U99" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Searched an existing term (no 'halal' inquiry exists)</t>
+        </is>
+      </c>
+      <c r="U99" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
@@ -10630,7 +11066,7 @@
       <c r="S102" s="16" t="n"/>
       <c r="T102" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U102" s="17" t="n"/>
@@ -10699,20 +11135,38 @@
       </c>
       <c r="N103" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O103" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O103" s="17" t="inlineStr">
+        <is>
+          <t>Reply modal with empty text → Send disabled: true</t>
+        </is>
+      </c>
       <c r="P103" s="17" t="n"/>
-      <c r="Q103" s="17" t="n"/>
-      <c r="R103" s="18" t="n"/>
-      <c r="S103" s="16" t="n"/>
+      <c r="Q103" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S103" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T103" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U103" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Nothing was sent</t>
+        </is>
+      </c>
+      <c r="U103" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
@@ -10787,7 +11241,7 @@
       </c>
       <c r="O104" s="17" t="inlineStr">
         <is>
-          <t>No AI draft shown: the Inquiry Bot page has no draft field ('draft'/'suggested_reply' absent from the bundle)</t>
+          <t>Reply box opens empty; no AI-drafted reply shown on the card or in the modal</t>
         </is>
       </c>
       <c r="P104" s="17" t="inlineStr">
@@ -10797,7 +11251,7 @@
       </c>
       <c r="Q104" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R104" s="18" t="n">
@@ -10805,17 +11259,17 @@
       </c>
       <c r="S104" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T104" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Real Chrome (Playwright)</t>
         </is>
       </c>
       <c r="U104" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -10883,18 +11337,18 @@
       </c>
       <c r="N105" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O105" s="17" t="inlineStr">
         <is>
-          <t>No token → 401 'Sign in required.' (as expected). Bogus token → 401 'Session expired…'</t>
+          <t>No token → 401; RIDER JWT → 403 {"error":"Only staff, managers, or admins can manage inquiries."}</t>
         </is>
       </c>
       <c r="P105" s="17" t="n"/>
       <c r="Q105" s="17" t="inlineStr">
         <is>
-          <t>Claude (automated, no account)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R105" s="18" t="n">
@@ -10902,12 +11356,12 @@
       </c>
       <c r="S105" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T105" s="17" t="inlineStr">
         <is>
-          <t>403 half needs a CUST JWT; QA accounts not created yet</t>
+          <t>Used a RIDER JWT for the non-staff half (no customer account); the server check is the same: role not in STAFF_ROLES</t>
         </is>
       </c>
       <c r="U105" s="17" t="inlineStr">
@@ -11003,7 +11457,7 @@
       </c>
       <c r="S106" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T106" s="17" t="inlineStr">
@@ -11100,7 +11554,7 @@
       </c>
       <c r="S107" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T107" s="17" t="n"/>
@@ -11517,7 +11971,7 @@
       </c>
       <c r="S112" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live bundle index-C9Ni0iVe.js; source 7652f11</t>
         </is>
       </c>
       <c r="T112" s="17" t="inlineStr">
@@ -11764,7 +12218,7 @@
       <c r="P115" s="17" t="n"/>
       <c r="Q115" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R115" s="18" t="n">
@@ -11772,7 +12226,7 @@
       </c>
       <c r="S115" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T115" s="17" t="inlineStr">
@@ -11860,7 +12314,7 @@
       <c r="S116" s="16" t="n"/>
       <c r="T116" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U116" s="17" t="n"/>
@@ -11939,7 +12393,7 @@
       <c r="S117" s="16" t="n"/>
       <c r="T117" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U117" s="17" t="n"/>
@@ -12018,7 +12472,7 @@
       <c r="S118" s="16" t="n"/>
       <c r="T118" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U118" s="17" t="n"/>
@@ -12097,7 +12551,7 @@
       <c r="S119" s="16" t="n"/>
       <c r="T119" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U119" s="17" t="n"/>
@@ -12176,7 +12630,7 @@
       <c r="S120" s="16" t="n"/>
       <c r="T120" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U120" s="17" t="n"/>
@@ -12255,7 +12709,7 @@
       <c r="S121" s="16" t="n"/>
       <c r="T121" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U121" s="17" t="n"/>
@@ -12324,20 +12778,38 @@
       </c>
       <c r="N122" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O122" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O122" s="17" t="inlineStr">
+        <is>
+          <t>QA catering booking inserted (201); row appeared without reload: true after 0.5 s; Catering pending 1 → 2</t>
+        </is>
+      </c>
       <c r="P122" s="17" t="n"/>
-      <c r="Q122" s="17" t="n"/>
-      <c r="R122" s="18" t="n"/>
-      <c r="S122" s="16" t="n"/>
+      <c r="Q122" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R122" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S122" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T122" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U122" s="17" t="n"/>
+          <t>Real Chrome (Playwright). Booking inserted through the API as FOH because there is no customer account; the realtime path is the same</t>
+        </is>
+      </c>
+      <c r="U122" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -12403,20 +12875,38 @@
       </c>
       <c r="N123" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O123" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O123" s="17" t="inlineStr">
+        <is>
+          <t>Pending → Confirmed saved (DB: Confirmed); Timeline shows Confirmed: true; Function pending 6 → 5</t>
+        </is>
+      </c>
       <c r="P123" s="17" t="n"/>
-      <c r="Q123" s="17" t="n"/>
-      <c r="R123" s="18" t="n"/>
-      <c r="S123" s="16" t="n"/>
+      <c r="Q123" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R123" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S123" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T123" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U123" s="17" t="n"/>
+          <t>Real Chrome (Playwright); QA booking. Customer-profile half needs a customer account</t>
+        </is>
+      </c>
+      <c r="U123" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
@@ -12482,20 +12972,38 @@
       </c>
       <c r="N124" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O124" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O124" s="17" t="inlineStr">
+        <is>
+          <t>A saved 21 guests while B had an unsaved edit (22). B shows 'changed in another session' without reloading: true; B's Save disabled: true; DB guests: 21</t>
+        </is>
+      </c>
       <c r="P124" s="17" t="n"/>
-      <c r="Q124" s="17" t="n"/>
-      <c r="R124" s="18" t="n"/>
-      <c r="S124" s="16" t="n"/>
+      <c r="Q124" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R124" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S124" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T124" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U124" s="17" t="n"/>
+          <t>Real Chrome (Playwright); two FOH sessions on a QA booking. B is warned in real time, before it tries to save</t>
+        </is>
+      </c>
+      <c r="U124" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
@@ -12520,12 +13028,12 @@
       </c>
       <c r="E125" s="15" t="inlineStr">
         <is>
-          <t>Two bookings: X at COL 3:00 PM, Y at COL 3:30 PM</t>
+          <t>Two Room A bookings: X on COL, Y on COL + 1 day</t>
         </is>
       </c>
       <c r="F125" s="15" t="inlineStr">
         <is>
-          <t>Edit Y → time 3:00 PM → Save</t>
+          <t>Edit Y → Date = COL → Save</t>
         </is>
       </c>
       <c r="G125" s="15" t="inlineStr">
@@ -12561,20 +13069,38 @@
       </c>
       <c r="N125" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O125" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O125" s="17" t="inlineStr">
+        <is>
+          <t>Moved Y (Room A, 12-18) onto X's date (Room A, 12-17) → alert: 'That date is already reserved. Choose another date.'; Y date in DB: 2026-12-18</t>
+        </is>
+      </c>
       <c r="P125" s="17" t="n"/>
-      <c r="Q125" s="17" t="n"/>
-      <c r="R125" s="18" t="n"/>
-      <c r="S125" s="16" t="n"/>
+      <c r="Q125" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R125" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S125" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T125" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U125" s="17" t="n"/>
+          <t>Real Chrome (Playwright); adapted to the whole-date rule (one active booking per room per date)</t>
+        </is>
+      </c>
+      <c r="U125" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -12640,20 +13166,38 @@
       </c>
       <c r="N126" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O126" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O126" s="17" t="inlineStr">
+        <is>
+          <t>QA booking opened; Save changes disabled with no edits: true</t>
+        </is>
+      </c>
       <c r="P126" s="17" t="n"/>
-      <c r="Q126" s="17" t="n"/>
-      <c r="R126" s="18" t="n"/>
-      <c r="S126" s="16" t="n"/>
+      <c r="Q126" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R126" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S126" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T126" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U126" s="17" t="n"/>
+          <t>Real Chrome (Playwright); QA booking</t>
+        </is>
+      </c>
+      <c r="U126" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
@@ -12719,20 +13263,38 @@
       </c>
       <c r="N127" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O127" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O127" s="17" t="inlineStr">
+        <is>
+          <t>Reference search 'QA-OP' → QA-OP-Y, QA-OP-X, QA-OP-A; name search → 3 rows; nonsense search → 0 rows, empty state 'No function bookings match your filters.'</t>
+        </is>
+      </c>
       <c r="P127" s="17" t="n"/>
-      <c r="Q127" s="17" t="n"/>
-      <c r="R127" s="18" t="n"/>
-      <c r="S127" s="16" t="n"/>
+      <c r="Q127" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R127" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S127" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T127" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U127" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U127" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
@@ -12798,20 +13360,38 @@
       </c>
       <c r="N128" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O128" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O128" s="17" t="inlineStr">
+        <is>
+          <t>Cancelled → Pending saved (DB: Pending); Room A 2026-12-16 occupied again: true</t>
+        </is>
+      </c>
       <c r="P128" s="17" t="n"/>
-      <c r="Q128" s="17" t="n"/>
-      <c r="R128" s="18" t="n"/>
-      <c r="S128" s="16" t="n"/>
+      <c r="Q128" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R128" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S128" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T128" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U128" s="17" t="n"/>
+          <t>Real Chrome (Playwright); QA booking</t>
+        </is>
+      </c>
+      <c r="U128" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
@@ -12841,7 +13421,7 @@
       </c>
       <c r="F129" s="15" t="inlineStr">
         <is>
-          <t>Stat cards: Active deliveries, Function pending, Catering pending, New inquiries, Total orders</t>
+          <t>Stat cards: Active deliveries, Function pending, Catering pending, Open inquiries, Total orders</t>
         </is>
       </c>
       <c r="G129" s="15" t="inlineStr">
@@ -12886,17 +13466,17 @@
       </c>
       <c r="O129" s="17" t="inlineStr">
         <is>
-          <t>Stat cards are Active deliveries, Function pending, Catering pending, New inquiries, Total orders; no Room Occupancy, revenue only as a hint</t>
+          <t>Function pending 6 = chip 6: true; Catering pending 1 = chip 1: true. Cards: Active deliveries, Function pending, Catering pending, Open inquiries, Total orders. No Room Occupancy card; revenue only as a hint; 'Open inquiries' has no list behind it (F-37)</t>
         </is>
       </c>
       <c r="P129" s="17" t="inlineStr">
         <is>
-          <t>F-30</t>
+          <t>F-30, F-37</t>
         </is>
       </c>
       <c r="Q129" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R129" s="18" t="n">
@@ -12904,17 +13484,17 @@
       </c>
       <c r="S129" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T129" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Real Chrome (Playwright)</t>
         </is>
       </c>
       <c r="U129" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -12991,7 +13571,7 @@
       </c>
       <c r="O130" s="17" t="inlineStr">
         <is>
-          <t>Dashboard has charts only (Orders by Source, Service Breakdown, Order Volume, Inquiry Tracking); no sales-value or utilisation report and no export</t>
+          <t>Dashboard panels: Orders by Source, Service Breakdown by Source, Order Volume Over Time, Inquiry Tracking; export/download controls: 0; sales or utilisation figures: 0</t>
         </is>
       </c>
       <c r="P130" s="17" t="inlineStr">
@@ -13001,7 +13581,7 @@
       </c>
       <c r="Q130" s="17" t="inlineStr">
         <is>
-          <t>Claude (inspection)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R130" s="18" t="n">
@@ -13009,17 +13589,17 @@
       </c>
       <c r="S130" s="16" t="inlineStr">
         <is>
-          <t>Live bundle index-Bq1AsZVl.js; source 8990106</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T130" s="17" t="inlineStr">
         <is>
-          <t>Inspection result; re-confirm in the manual run</t>
+          <t>Real Chrome (Playwright)</t>
         </is>
       </c>
       <c r="U130" s="17" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -13092,13 +13672,13 @@
       </c>
       <c r="O131" s="17" t="inlineStr">
         <is>
-          <t>Time to load event + first page heading visible, cache disabled. Broadband (unthrottled): / 2.2 s, /delivery/order 1.3 s, /function-rooms/reserve 1.5 s | 4G (Lighthouse mobile profile: 150 ms RTT, 1.6 Mbps down, 750 kbps up): / 3.3 s, /delivery/order 2.9 s, /function-rooms/reserve 3.0 s</t>
+          <t>Time to load event + first page heading visible, cache disabled. Broadband (unthrottled): / 2.4 s, /delivery/order 1.8 s, /function-rooms/reserve 1.2 s | 4G (Lighthouse mobile profile: 150 ms RTT, 1.6 Mbps down, 750 kbps up): / 3.1 s, /delivery/order 2.8 s, /function-rooms/reserve 2.7 s</t>
         </is>
       </c>
       <c r="P131" s="17" t="n"/>
       <c r="Q131" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R131" s="18" t="n">
@@ -13106,7 +13686,7 @@
       </c>
       <c r="S131" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T131" s="17" t="inlineStr">
@@ -13194,7 +13774,7 @@
       <c r="S132" s="16" t="n"/>
       <c r="T132" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U132" s="17" t="n"/>
@@ -13274,7 +13854,7 @@
       <c r="P133" s="17" t="n"/>
       <c r="Q133" s="17" t="inlineStr">
         <is>
-          <t>Claude (Playwright, real Chrome, guest)</t>
+          <t>Claude (Playwright, real Chrome)</t>
         </is>
       </c>
       <c r="R133" s="18" t="n">
@@ -13282,7 +13862,7 @@
       </c>
       <c r="S133" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106); bundle index-Bq1AsZVl.js</t>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
         </is>
       </c>
       <c r="T133" s="17" t="inlineStr">
@@ -13370,7 +13950,7 @@
       <c r="S134" s="16" t="n"/>
       <c r="T134" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
+          <t>Needs a customer account (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U134" s="17" t="n"/>
@@ -13439,20 +14019,38 @@
       </c>
       <c r="N135" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O135" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O135" s="17" t="inlineStr">
+        <is>
+          <t>/dashboard→/operations, /delivery/rider→/operations, /→/operations, /profile→/operations</t>
+        </is>
+      </c>
       <c r="P135" s="17" t="n"/>
-      <c r="Q135" s="17" t="n"/>
-      <c r="R135" s="18" t="n"/>
-      <c r="S135" s="16" t="n"/>
+      <c r="Q135" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R135" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S135" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T135" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U135" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U135" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
@@ -13518,20 +14116,38 @@
       </c>
       <c r="N136" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O136" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O136" s="17" t="inlineStr">
+        <is>
+          <t>/operations→/delivery/rider, /delivery/items→/delivery/rider, /catering→/delivery/rider</t>
+        </is>
+      </c>
       <c r="P136" s="17" t="n"/>
-      <c r="Q136" s="17" t="n"/>
-      <c r="R136" s="18" t="n"/>
-      <c r="S136" s="16" t="n"/>
+      <c r="Q136" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R136" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S136" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T136" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U136" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U136" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
@@ -13597,20 +14213,38 @@
       </c>
       <c r="N137" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O137" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O137" s="17" t="inlineStr">
+        <is>
+          <t>/OPERATIONS/ → /OPERATIONS/; Operations rendered: true</t>
+        </is>
+      </c>
       <c r="P137" s="17" t="n"/>
-      <c r="Q137" s="17" t="n"/>
-      <c r="R137" s="18" t="n"/>
-      <c r="S137" s="16" t="n"/>
+      <c r="Q137" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R137" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S137" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T137" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U137" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U137" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
@@ -13676,20 +14310,38 @@
       </c>
       <c r="N138" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O138" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O138" s="17" t="inlineStr">
+        <is>
+          <t>Login → /operations; /dashboard renders: true; /delivery/rider → /operations</t>
+        </is>
+      </c>
       <c r="P138" s="17" t="n"/>
-      <c r="Q138" s="17" t="n"/>
-      <c r="R138" s="18" t="n"/>
-      <c r="S138" s="16" t="n"/>
+      <c r="Q138" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R138" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S138" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T138" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U138" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U138" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -13755,20 +14407,38 @@
       </c>
       <c r="N139" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O139" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O139" s="17" t="inlineStr">
+        <is>
+          <t>Login → /dashboard; /delivery/rider renders: true; / → /dashboard</t>
+        </is>
+      </c>
       <c r="P139" s="17" t="n"/>
-      <c r="Q139" s="17" t="n"/>
-      <c r="R139" s="18" t="n"/>
-      <c r="S139" s="16" t="n"/>
+      <c r="Q139" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R139" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S139" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T139" s="17" t="inlineStr">
         <is>
-          <t>Needs QA accounts (CUST, CUST-B, FOH, RIDER per §0.1); not created yet</t>
-        </is>
-      </c>
-      <c r="U139" s="17" t="n"/>
+          <t>Real Chrome (Playwright)</t>
+        </is>
+      </c>
+      <c r="U139" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
@@ -13853,7 +14523,7 @@
       </c>
       <c r="S140" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T140" s="17" t="n"/>
@@ -13946,7 +14616,7 @@
       </c>
       <c r="S141" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T141" s="17" t="inlineStr">
@@ -14043,7 +14713,7 @@
       </c>
       <c r="S142" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T142" s="17" t="inlineStr">
@@ -14131,7 +14801,7 @@
       <c r="S143" s="16" t="n"/>
       <c r="T143" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+          <t>Needs a customer JWT (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U143" s="17" t="n"/>
@@ -14210,7 +14880,7 @@
       <c r="S144" s="16" t="n"/>
       <c r="T144" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+          <t>Needs a customer JWT (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U144" s="17" t="n"/>
@@ -14293,7 +14963,7 @@
       <c r="S145" s="16" t="n"/>
       <c r="T145" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+          <t>Needs a customer JWT (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U145" s="17" t="n"/>
@@ -14362,20 +15032,42 @@
       </c>
       <c r="N146" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O146" s="17" t="n"/>
-      <c r="P146" s="17" t="n"/>
-      <c r="Q146" s="17" t="n"/>
-      <c r="R146" s="18" t="n"/>
-      <c r="S146" s="16" t="n"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O146" s="17" t="inlineStr">
+        <is>
+          <t>PATCH own profile role → 200 1 row updated (role column writable)</t>
+        </is>
+      </c>
+      <c r="P146" s="17" t="inlineStr">
+        <is>
+          <t>F-35</t>
+        </is>
+      </c>
+      <c r="Q146" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R146" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S146" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T146" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
-        </is>
-      </c>
-      <c r="U146" s="17" t="n"/>
+          <t>Ran as RIDER (any authenticated user has the same profiles grants as a customer). Sent the current role, so even a successful write would change nothing</t>
+        </is>
+      </c>
+      <c r="U146" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
@@ -14405,12 +15097,12 @@
       </c>
       <c r="F147" s="15" t="inlineStr">
         <is>
-          <t>Fire two POSTs for the same room_id=private_dining, date=COL, time=16:00, status=Pending concurrently (two shells, CUST and CUST-B JWTs, &amp; and then wait)</t>
+          <t>Fire two POSTs for the same room_id=room_a, date=COL (times 10:00 and 16:00), status=Pending concurrently (two shells, CUST and CUST-B JWTs, &amp; and then wait)</t>
         </is>
       </c>
       <c r="G147" s="15" t="inlineStr">
         <is>
-          <t>Exactly one 201. The other returns 409 / 23505 function_bookings_active_slot_unique. booking_availability has exactly one row for that slot. (The outcome meets REQ-RES-002, but the mechanism is a unique index, not SELECT FOR UPDATE → F-31)</t>
+          <t>Exactly one 201. The other returns 409 / 23505 function_bookings_active_date_unique. booking_availability has exactly one row for Room A on COL. (The outcome meets REQ-RES-002, but the mechanism is a unique index, not SELECT FOR UPDATE → F-31)</t>
         </is>
       </c>
       <c r="H147" s="9" t="inlineStr">
@@ -14445,20 +15137,42 @@
       </c>
       <c r="N147" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O147" s="17" t="n"/>
-      <c r="P147" s="17" t="n"/>
-      <c r="Q147" s="17" t="n"/>
-      <c r="R147" s="18" t="n"/>
-      <c r="S147" s="16" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O147" s="17" t="inlineStr">
+        <is>
+          <t>Concurrent POSTs, Room A, same date, 10:00 vs 16:00 → 409 / 201; loser 23505 duplicate key value violates unique constraint "function_bookings_acti; booking_availability rows for Room A on the date: 1 (before: 0)</t>
+        </is>
+      </c>
+      <c r="P147" s="17" t="inlineStr">
+        <is>
+          <t>F-31</t>
+        </is>
+      </c>
+      <c r="Q147" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R147" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S147" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T147" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
-        </is>
-      </c>
-      <c r="U147" s="17" t="n"/>
+          <t>Ran as FOH + Manager (two different users) because no customer accounts exist; the unique index applies to every role. Mechanism is a unique index, not SELECT FOR UPDATE (F-31)</t>
+        </is>
+      </c>
+      <c r="U147" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
@@ -14524,20 +15238,38 @@
       </c>
       <c r="N148" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O148" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O148" s="17" t="inlineStr">
+        <is>
+          <t>20:00 → 400 23514 new row for relation "function_bookings" violates check cons; 12:15 → 400 23514</t>
+        </is>
+      </c>
       <c r="P148" s="17" t="n"/>
-      <c r="Q148" s="17" t="n"/>
-      <c r="R148" s="18" t="n"/>
-      <c r="S148" s="16" t="n"/>
+      <c r="Q148" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R148" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S148" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T148" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
-        </is>
-      </c>
-      <c r="U148" s="17" t="n"/>
+          <t>Ran as FOH (insert allowed for staff)</t>
+        </is>
+      </c>
+      <c r="U148" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
@@ -14617,7 +15349,7 @@
       <c r="S149" s="16" t="n"/>
       <c r="T149" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
+          <t>Needs a customer JWT (CUST / CUST-B). Customer sign-in is by magic link or Google, and no customer account with a password was provided</t>
         </is>
       </c>
       <c r="U149" s="17" t="n"/>
@@ -14650,12 +15382,12 @@
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>FOH: set the DB-08 booking to Cancelled → query booking_availability for that slot</t>
+          <t>FOH: set the DB-08 booking to Cancelled → query booking_availability for Room A on COL</t>
         </is>
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Row gone. A new booking for the slot succeeds</t>
+          <t>Row gone. A new booking for Room A on COL succeeds</t>
         </is>
       </c>
       <c r="H150" s="9" t="inlineStr">
@@ -14686,20 +15418,38 @@
       </c>
       <c r="N150" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O150" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O150" s="17" t="inlineStr">
+        <is>
+          <t>FOH cancel → 200 (1 row); date row gone: true; new booking for the same room/date → 201</t>
+        </is>
+      </c>
       <c r="P150" s="17" t="n"/>
-      <c r="Q150" s="17" t="n"/>
-      <c r="R150" s="18" t="n"/>
-      <c r="S150" s="16" t="n"/>
+      <c r="Q150" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R150" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S150" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T150" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
-        </is>
-      </c>
-      <c r="U150" s="17" t="n"/>
+          <t>Ran on QA rows only</t>
+        </is>
+      </c>
+      <c r="U150" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
@@ -14765,20 +15515,38 @@
       </c>
       <c r="N151" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O151" s="17" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="O151" s="17" t="inlineStr">
+        <is>
+          <t>FOH GET inquiries → 200, 19 rows (15 with user_id = null)</t>
+        </is>
+      </c>
       <c r="P151" s="17" t="n"/>
-      <c r="Q151" s="17" t="n"/>
-      <c r="R151" s="18" t="n"/>
-      <c r="S151" s="16" t="n"/>
+      <c r="Q151" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R151" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S151" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T151" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
-        </is>
-      </c>
-      <c r="U151" s="17" t="n"/>
+          <t>Every row has user_id = null (web and Messenger), so "rows from other users" cannot be shown; see F-07</t>
+        </is>
+      </c>
+      <c r="U151" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -14844,20 +15612,42 @@
       </c>
       <c r="N152" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O152" s="17" t="n"/>
-      <c r="P152" s="17" t="n"/>
-      <c r="Q152" s="17" t="n"/>
-      <c r="R152" s="18" t="n"/>
-      <c r="S152" s="16" t="n"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O152" s="17" t="inlineStr">
+        <is>
+          <t>RIDER GET delivery_orders → 200, 2 rows (all customers' orders). QA order with no rider assigned (insert 201): rider can read it true, rider PATCH → 200 1 row; cleaned up 1. function_bookings → 200 0 rows; inquiries → 200 0 rows</t>
+        </is>
+      </c>
+      <c r="P152" s="17" t="inlineStr">
+        <is>
+          <t>F-36</t>
+        </is>
+      </c>
+      <c r="Q152" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R152" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S152" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T152" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
-        </is>
-      </c>
-      <c r="U152" s="17" t="n"/>
+          <t>SRS §2.3: riders see assigned orders only</t>
+        </is>
+      </c>
+      <c r="U152" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
@@ -14927,20 +15717,42 @@
       </c>
       <c r="N153" s="16" t="inlineStr">
         <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="O153" s="17" t="n"/>
-      <c r="P153" s="17" t="n"/>
-      <c r="Q153" s="17" t="n"/>
-      <c r="R153" s="18" t="n"/>
-      <c r="S153" s="16" t="n"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="O153" s="17" t="inlineStr">
+        <is>
+          <t>Admin PATCH on QA inquiry → 200, 0 rows updated; status still 'New'</t>
+        </is>
+      </c>
+      <c r="P153" s="17" t="inlineStr">
+        <is>
+          <t>F-17</t>
+        </is>
+      </c>
+      <c r="Q153" s="17" t="inlineStr">
+        <is>
+          <t>Claude (Playwright, real Chrome)</t>
+        </is>
+      </c>
+      <c r="R153" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="S153" s="16" t="inlineStr">
+        <is>
+          <t>Live (Railway main @ 7652f11); bundle index-C9Ni0iVe.js</t>
+        </is>
+      </c>
       <c r="T153" s="17" t="inlineStr">
         <is>
-          <t>Needs a signed-in JWT (CUST / CUST-B / FOH / RIDER / admin); QA accounts not created yet</t>
-        </is>
-      </c>
-      <c r="U153" s="17" t="n"/>
+          <t>SRS expects full admin access; run on the QA Manual Order Request row only</t>
+        </is>
+      </c>
+      <c r="U153" s="17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
@@ -15033,7 +15845,7 @@
       </c>
       <c r="S154" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T154" s="17" t="n"/>
@@ -15126,7 +15938,7 @@
       </c>
       <c r="S155" s="16" t="inlineStr">
         <is>
-          <t>Live (Railway main @ 8990106)</t>
+          <t>Live (Railway main @ 7652f11)</t>
         </is>
       </c>
       <c r="T155" s="17" t="n"/>
@@ -15308,7 +16120,7 @@
       </c>
       <c r="G2" s="15" t="inlineStr">
         <is>
-          <t>F-07, F-33</t>
+          <t>F-07, F-33, F-37</t>
         </is>
       </c>
       <c r="H2" s="9">
@@ -15515,7 +16327,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-37</t>
         </is>
       </c>
       <c r="H5" s="9">
@@ -16412,7 +17224,7 @@
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>F-17</t>
+          <t>F-17, F-35</t>
         </is>
       </c>
       <c r="H18" s="9">
@@ -16481,7 +17293,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-01, F-37</t>
         </is>
       </c>
       <c r="H19" s="9">
@@ -16826,7 +17638,7 @@
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>F-13, F-25</t>
+          <t>F-13, F-25, F-36</t>
         </is>
       </c>
       <c r="H24" s="9">
@@ -17447,7 +18259,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>F-15</t>
+          <t>F-15, F-36</t>
         </is>
       </c>
       <c r="H33" s="9">
@@ -17516,7 +18328,7 @@
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>F-12, F-18</t>
+          <t>F-12, F-18, F-35</t>
         </is>
       </c>
       <c r="H34" s="9">
@@ -18071,7 +18883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18158,7 +18970,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 · Fixed in e9b5e7c</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
@@ -18192,14 +19004,14 @@
       </c>
       <c r="I2" s="16" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J2" s="17" t="n"/>
       <c r="K2" s="18" t="n"/>
       <c r="L2" s="17" t="inlineStr">
         <is>
-          <t>Confirmed by inspection of the deployed build on 2026-10-07; still open (not fixed)</t>
+          <t>Fixed in e9b5e7c: orders saved to Supabase (live delivery_orders rows exist; staff and rider pages read them). Customer-side confirmation (DO-08) needs a customer account</t>
         </is>
       </c>
     </row>
@@ -18211,7 +19023,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 · Fixed in e9b5e7c, d9610bc</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18245,14 +19057,14 @@
       </c>
       <c r="I3" s="16" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J3" s="17" t="n"/>
       <c r="K3" s="18" t="n"/>
       <c r="L3" s="17" t="inlineStr">
         <is>
-          <t>Confirmed by inspection of the deployed build on 2026-10-07; still open (not fixed)</t>
+          <t>Fixed in e9b5e7c/d9610bc: references come from next_delivery_reference() (security definer). DO-09 needs two customer accounts</t>
         </is>
       </c>
     </row>
@@ -18264,12 +19076,12 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 · Fixed in e9b5e7c</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Function room accepts 1–30 guests. The SRS says 10–50</t>
+          <t>Function room accepted 1–30 guests; the SRS says 10–50. Now 10–50 with Rooms A/B (verified live: FR-02, FR-03 pass)</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
@@ -18298,14 +19110,14 @@
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="J4" s="17" t="n"/>
       <c r="K4" s="18" t="n"/>
       <c r="L4" s="17" t="inlineStr">
         <is>
-          <t>Confirmed by inspection of the deployed build on 2026-10-07; still open (not fixed)</t>
+          <t>Fixed in e9b5e7c (10–50 guests, Rooms A/B). Verified live 2026-10-07: FR-02 and FR-03 pass</t>
         </is>
       </c>
     </row>
@@ -18428,7 +19240,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>No confirmation email or self-cancel link</t>
+          <t>No confirmation email or self-cancel link. Partly addressed in e9b5e7c: customers can request a cancellation or move from their profile, and staff then act on it; there is still no email and no self-service cancellation</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
@@ -18464,7 +19276,7 @@
       <c r="K7" s="18" t="n"/>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t>Confirmed by inspection of the deployed build on 2026-10-07; still open (not fixed)</t>
+          <t>Partly addressed in e9b5e7c: customers can request a cancellation or move from their profile. Still no email and no self-service cancellation</t>
         </is>
       </c>
     </row>
@@ -18800,7 +19612,7 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>DeliveryRider.tsx:26-34</t>
+          <t>DeliveryRider.tsx:33-39</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -19037,7 +19849,11 @@
       </c>
       <c r="J18" s="17" t="n"/>
       <c r="K18" s="18" t="n"/>
-      <c r="L18" s="17" t="n"/>
+      <c r="L18" s="17" t="inlineStr">
+        <is>
+          <t>Confirmed by inspection of the deployed build on 2026-10-07; still open (not fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -19110,7 +19926,7 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>FunctionRoomReservation.tsx:16 vs DeliveryOrder.tsx:46</t>
+          <t>FunctionRoomReservation.tsx:20 vs DeliveryOrder.tsx:46, Profile.tsx:15</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
@@ -19158,12 +19974,12 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>The delivery status flow differs: the SRS has Received → Preparing → Out for Delivery → Delivered; the app has Preparing → Ready for pickup → Out for delivery → Delivered</t>
+          <t>The delivery status flow differs: the SRS has Received → Preparing → Out for Delivery → Delivered; the app has Pending Confirmation → Preparing → Ready for pickup → Out for delivery → Delivered (+ Cancelled). Pending Confirmation now plays the role of Received; Ready for pickup is extra</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>delivery.ts:49</t>
+          <t>delivery.ts:51-58</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -19202,17 +20018,17 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 · Fixed in e9b5e7c</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Packed-meal bookings are saved with email = "", so staff cannot email the customer</t>
+          <t>Packed-meal bookings were saved with email = "", so staff cannot email the customer</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>CateringPacked.tsx:292</t>
+          <t>CateringPacked.tsx:292 (now email: user.email)</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
@@ -19236,12 +20052,16 @@
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J22" s="17" t="n"/>
       <c r="K22" s="18" t="n"/>
-      <c r="L22" s="17" t="n"/>
+      <c r="L22" s="17" t="inlineStr">
+        <is>
+          <t>Fixed in e9b5e7c: packed bookings save user.email. Confirm with a customer booking (CT-12)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -19928,21 +20748,180 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>F-35</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>P1 (critical)</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Any signed-in user can change their own role, including to system_admin. Migration 20261007044317_customer_booking_fixes_part1 grants UPDATE on the whole profiles table, and profiles_update_own only checks auth.uid() = id, so the role column is writable. Customers can self-register by magic link, so anyone can make themselves an administrator. Fix: revoke update on public.profiles from authenticated; grant update (phone, addresses, display_name) on public.profiles to authenticated; (or a trigger that rejects role changes)</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Migration 20261007044317 lines 1-12; live 2026-10-07: RIDER PATCH profiles {role: &lt;current value&gt;} → 200, 1 row (no value changed)</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>REQ-ADM-001, §5.3</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>REQ-ADM-001, NFR-SEC-02</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>DB-07</t>
+        </is>
+      </c>
+      <c r="H36" s="9">
+        <f>COUNTIFS('Test Cases'!$P$2:$P$155,"*"&amp;A36&amp;"*",'Test Cases'!$N$2:$N$155,"Fail")</f>
+        <v/>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>Found 2026-10-07 (DB-07): migration 20261007044317 grants UPDATE on profiles to every user. Fix immediately: column-level grant (phone, addresses, display_name) or a trigger rejecting role changes</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>F-36</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Riders can read and update every delivery order, not only the ones assigned to them: delivery_orders_rider_select and _update check the role but not rider_id. A rider sees every customer's name, phone and address and can change any order</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Migration 20261007044349 lines 1-20; live 2026-10-07: RIDER read and updated an unassigned QA order</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>§2.3 Delivery Rider, §5.3 Data Privacy</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>NFR-SEC-01, UR-RIDER</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>DB-13</t>
+        </is>
+      </c>
+      <c r="H37" s="9">
+        <f>COUNTIFS('Test Cases'!$P$2:$P$155,"*"&amp;A37&amp;"*",'Test Cases'!$N$2:$N$155,"Fail")</f>
+        <v/>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>Found 2026-10-07 (DB-13): rider policies check the role only. Fix: add rider_id = &lt;rider's id&gt; to delivery_orders_rider_select/_update (needs a rider-to-auth-user link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>F-37</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Web inquiries are no longer visible to staff. d9610bc removed the Operations Inquiries panel ("InquiryBot covers it"), but /inquiry-bot loads only rows whose email matches messenger%@placeholder.com. Web-form inquiries and Manual Order Requests are counted (Open inquiries card) but cannot be read, answered or closed anywhere</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>InquiryBot.tsx:83-85; Operations.tsx:104-106 and :259-261 (count only); live: the QA Manual Order Request is not listed</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>REQ-INQ-001, REQ-INQ-004, REQ-ADM-002</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>REQ-INQ-001, REQ-INQ-004, REQ-ADM-002</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>IQ-05, IQ-06, S-14</t>
+        </is>
+      </c>
+      <c r="H38" s="9">
+        <f>COUNTIFS('Test Cases'!$P$2:$P$155,"*"&amp;A38&amp;"*",'Test Cases'!$N$2:$N$155,"Fail")</f>
+        <v/>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="17" t="inlineStr">
+        <is>
+          <t>Found 2026-10-07 (IQ-05): restore a staff list for web inquiries (Operations panel or remove the Messenger-only filter in InquiryBot.tsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Failed Cases counts test cases whose Defect / Finding ID contains this finding and whose Status is Fail. Note: 'F-1' style partial matches are avoided because IDs are two digits (F-01 … F-31).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L35"/>
+  <autoFilter ref="A1:L38"/>
   <mergeCells count="1">
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I2:I38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,In progress,Fixed,Verified,Won't fix,SRS to update"</formula1>
     </dataValidation>
   </dataValidations>
